--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661B023C-A240-492C-BE9E-A409245C6E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -937,7 +937,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1008,6 +1008,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1797,7 +1798,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M3:W22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -3665,7 +3666,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3683,7 +3684,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -3721,7 +3722,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -3759,7 +3760,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3797,7 +3798,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -3835,7 +3836,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="41" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3865,7 +3866,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="41" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -3895,7 +3896,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -3925,7 +3926,7 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="41" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -3955,7 +3956,7 @@
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="41" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -3993,7 +3994,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="41" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -4031,7 +4032,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="41" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -4069,7 +4070,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="41" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4143,7 +4144,7 @@
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -4161,7 +4162,7 @@
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -4199,7 +4200,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -4237,7 +4238,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -4275,7 +4276,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -4313,7 +4314,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -4331,7 +4332,7 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -4369,7 +4370,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -4387,7 +4388,7 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -4417,7 +4418,7 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -4473,7 +4474,7 @@
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -4511,7 +4512,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -4541,7 +4542,7 @@
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -4567,7 +4568,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="41" t="s">
         <v>26</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -4605,7 +4606,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="41" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -4631,7 +4632,7 @@
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="41" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -4669,7 +4670,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="41" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -4707,7 +4708,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="41" t="s">
         <v>27</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -4737,7 +4738,7 @@
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="41" t="s">
         <v>27</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -4763,7 +4764,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="41" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -4801,7 +4802,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="41" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4827,7 +4828,7 @@
       <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="41" t="s">
         <v>29</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -4865,7 +4866,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="41" t="s">
         <v>29</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -4891,7 +4892,7 @@
       <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="40" t="s">
+      <c r="A41" s="41" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -4929,7 +4930,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="40" t="s">
+      <c r="A42" s="41" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -4967,7 +4968,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="40" t="s">
+      <c r="A43" s="41" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -4985,7 +4986,7 @@
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="40" t="s">
+      <c r="A44" s="41" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -5023,7 +5024,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="40" t="s">
+      <c r="A45" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -5041,7 +5042,7 @@
       <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -5079,7 +5080,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -5117,7 +5118,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -5155,7 +5156,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="40" t="s">
+      <c r="A49" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -5193,7 +5194,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -5211,7 +5212,7 @@
       <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -5229,7 +5230,7 @@
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -5247,7 +5248,7 @@
       <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -5285,7 +5286,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="41" t="s">
         <v>33</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -5323,7 +5324,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="40" t="s">
+      <c r="A55" s="41" t="s">
         <v>33</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -5361,7 +5362,7 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="41" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -5399,7 +5400,7 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="40" t="s">
+      <c r="A57" s="41" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -5437,7 +5438,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="40" t="s">
+      <c r="A58" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -5475,7 +5476,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -5513,7 +5514,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="40" t="s">
+      <c r="A60" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -5551,7 +5552,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="40" t="s">
+      <c r="A61" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -5571,7 +5572,7 @@
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="40" t="s">
+      <c r="A62" s="41" t="s">
         <v>35</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -5609,7 +5610,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="41" t="s">
         <v>35</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -5647,7 +5648,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="40" t="s">
+      <c r="A64" s="41" t="s">
         <v>35</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -5685,7 +5686,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="40" t="s">
+      <c r="A65" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -5703,7 +5704,7 @@
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="40" t="s">
+      <c r="A66" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -5741,7 +5742,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="40" t="s">
+      <c r="A67" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -5779,7 +5780,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -5817,7 +5818,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -5855,7 +5856,7 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="40" t="s">
+      <c r="A70" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -5873,7 +5874,7 @@
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -5911,7 +5912,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="40" t="s">
+      <c r="A72" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -5929,7 +5930,7 @@
       <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -5959,7 +5960,7 @@
       <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="40" t="s">
+      <c r="A74" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -5997,7 +5998,7 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="40" t="s">
+      <c r="A75" s="41" t="s">
         <v>38</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -6027,7 +6028,7 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="41" t="s">
         <v>38</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -6091,7 +6092,7 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="40" t="s">
+      <c r="A78" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -6129,7 +6130,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="40" t="s">
+      <c r="A79" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -6167,7 +6168,7 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="40" t="s">
+      <c r="A80" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -6205,7 +6206,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="40" t="s">
+      <c r="A81" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -6243,7 +6244,7 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="40" t="s">
+      <c r="A82" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -6281,7 +6282,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="40" t="s">
+      <c r="A83" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -6319,7 +6320,7 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="40" t="s">
+      <c r="A84" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -6357,7 +6358,7 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="40" t="s">
+      <c r="A85" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -6395,7 +6396,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="40" t="s">
+      <c r="A86" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -6433,7 +6434,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="40" t="s">
+      <c r="A87" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -6451,7 +6452,7 @@
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="40" t="s">
+      <c r="A88" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -6489,7 +6490,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="40" t="s">
+      <c r="A89" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -6527,7 +6528,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="41" t="s">
+      <c r="A90" s="42" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -6545,7 +6546,7 @@
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="42" t="s">
+      <c r="A91" s="43" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -6583,7 +6584,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="42" t="s">
+      <c r="A92" s="43" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -6621,7 +6622,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="42" t="s">
+      <c r="A93" s="43" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -6659,7 +6660,7 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="43" t="s">
+      <c r="A94" s="44" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -6697,7 +6698,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="40" t="s">
+      <c r="A95" s="41" t="s">
         <v>44</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -6735,7 +6736,7 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="40" t="s">
+      <c r="A96" s="41" t="s">
         <v>44</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -6773,7 +6774,7 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="40" t="s">
+      <c r="A97" s="41" t="s">
         <v>44</v>
       </c>
       <c r="B97" s="4" t="s">
@@ -6811,7 +6812,7 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="40" t="s">
+      <c r="A98" s="41" t="s">
         <v>45</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -6841,7 +6842,7 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="40" t="s">
+      <c r="A99" s="41" t="s">
         <v>45</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -6859,7 +6860,7 @@
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="40" t="s">
+      <c r="A100" s="41" t="s">
         <v>45</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -6885,7 +6886,7 @@
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="40" t="s">
+      <c r="A101" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -6923,7 +6924,7 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="40" t="s">
+      <c r="A102" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B102" s="4" t="s">
@@ -6941,7 +6942,7 @@
       <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="40" t="s">
+      <c r="A103" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -6967,7 +6968,7 @@
       <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="40" t="s">
+      <c r="A104" s="41" t="s">
         <v>47</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -6997,7 +6998,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="40" t="s">
+      <c r="A105" s="41" t="s">
         <v>47</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -7025,7 +7026,7 @@
       <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="40" t="s">
+      <c r="A106" s="41" t="s">
         <v>47</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -7061,7 +7062,7 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="40" t="s">
+      <c r="A107" s="41" t="s">
         <v>48</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -7099,7 +7100,7 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="40" t="s">
+      <c r="A108" s="41" t="s">
         <v>48</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -7137,7 +7138,7 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="40" t="s">
+      <c r="A109" s="41" t="s">
         <v>48</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -7155,7 +7156,7 @@
       <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="40" t="s">
+      <c r="A110" s="41" t="s">
         <v>49</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -7193,7 +7194,7 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="40" t="s">
+      <c r="A111" s="41" t="s">
         <v>49</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -7231,7 +7232,7 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="40" t="s">
+      <c r="A112" s="41" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="4" t="s">
@@ -7267,7 +7268,7 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="40" t="s">
+      <c r="A113" s="41" t="s">
         <v>49</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -7305,7 +7306,7 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="40" t="s">
+      <c r="A114" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B114" s="4" t="s">
@@ -7343,7 +7344,7 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" s="40" t="s">
+      <c r="A115" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -7381,7 +7382,7 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" s="40" t="s">
+      <c r="A116" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B116" s="4" t="s">
@@ -7419,7 +7420,7 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="40" t="s">
+      <c r="A117" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -7457,7 +7458,7 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="40" t="s">
+      <c r="A118" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -7531,7 +7532,7 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="40" t="s">
+      <c r="A120" s="41" t="s">
         <v>52</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -7549,7 +7550,7 @@
       <c r="L120" s="6"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" s="40" t="s">
+      <c r="A121" s="41" t="s">
         <v>52</v>
       </c>
       <c r="B121" s="4" t="s">
@@ -7581,7 +7582,7 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="40" t="s">
+      <c r="A122" s="41" t="s">
         <v>52</v>
       </c>
       <c r="B122" s="4" t="s">
@@ -7619,7 +7620,7 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="40" t="s">
+      <c r="A123" s="41" t="s">
         <v>53</v>
       </c>
       <c r="B123" s="4" t="s">
@@ -7657,7 +7658,7 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="40" t="s">
+      <c r="A124" s="41" t="s">
         <v>53</v>
       </c>
       <c r="B124" s="4" t="s">
@@ -7695,7 +7696,7 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="40" t="s">
+      <c r="A125" s="41" t="s">
         <v>53</v>
       </c>
       <c r="B125" s="4" t="s">
@@ -7733,7 +7734,7 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="40" t="s">
+      <c r="A126" s="41" t="s">
         <v>54</v>
       </c>
       <c r="B126" s="4" t="s">
@@ -7751,7 +7752,7 @@
       <c r="L126" s="6"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="40" t="s">
+      <c r="A127" s="41" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -7769,7 +7770,7 @@
       <c r="L127" s="6"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="40" t="s">
+      <c r="A128" s="41" t="s">
         <v>54</v>
       </c>
       <c r="B128" s="4" t="s">
@@ -7787,7 +7788,7 @@
       <c r="L128" s="6"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="40" t="s">
+      <c r="A129" s="41" t="s">
         <v>54</v>
       </c>
       <c r="B129" s="4" t="s">
@@ -7807,7 +7808,7 @@
       <c r="L129" s="6"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="40" t="s">
+      <c r="A130" s="41" t="s">
         <v>55</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -7825,7 +7826,7 @@
       <c r="L130" s="6"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="40" t="s">
+      <c r="A131" s="41" t="s">
         <v>55</v>
       </c>
       <c r="B131" s="4" t="s">
@@ -7863,7 +7864,7 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="40" t="s">
+      <c r="A132" s="41" t="s">
         <v>55</v>
       </c>
       <c r="B132" s="4" t="s">
@@ -7901,7 +7902,7 @@
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" s="40" t="s">
+      <c r="A133" s="41" t="s">
         <v>55</v>
       </c>
       <c r="B133" s="4" t="s">
@@ -7939,7 +7940,7 @@
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" s="40" t="s">
+      <c r="A134" s="41" t="s">
         <v>55</v>
       </c>
       <c r="B134" s="4" t="s">
@@ -7977,7 +7978,7 @@
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="40" t="s">
+      <c r="A135" s="41" t="s">
         <v>56</v>
       </c>
       <c r="B135" s="4" t="s">
@@ -8015,7 +8016,7 @@
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="40" t="s">
+      <c r="A136" s="41" t="s">
         <v>56</v>
       </c>
       <c r="B136" s="4" t="s">
@@ -8053,7 +8054,7 @@
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="40" t="s">
+      <c r="A137" s="41" t="s">
         <v>57</v>
       </c>
       <c r="B137" s="4" t="s">
@@ -8091,7 +8092,7 @@
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="40" t="s">
+      <c r="A138" s="41" t="s">
         <v>57</v>
       </c>
       <c r="B138" s="4" t="s">
@@ -8129,7 +8130,7 @@
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" s="40" t="s">
+      <c r="A139" s="41" t="s">
         <v>57</v>
       </c>
       <c r="B139" s="4" t="s">
@@ -8167,7 +8168,7 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" s="40" t="s">
+      <c r="A140" s="41" t="s">
         <v>57</v>
       </c>
       <c r="B140" s="4" t="s">
@@ -8243,7 +8244,7 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" s="40" t="s">
+      <c r="A142" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B142" s="4" t="s">
@@ -8281,7 +8282,7 @@
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" s="40" t="s">
+      <c r="A143" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B143" s="4" t="s">
@@ -8319,7 +8320,7 @@
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" s="40" t="s">
+      <c r="A144" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B144" s="4" t="s">
@@ -8357,7 +8358,7 @@
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" s="40" t="s">
+      <c r="A145" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B145" s="4" t="s">
@@ -8385,7 +8386,7 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" s="40" t="s">
+      <c r="A146" s="41" t="s">
         <v>60</v>
       </c>
       <c r="B146" s="4" t="s">
@@ -8423,7 +8424,7 @@
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" s="40" t="s">
+      <c r="A147" s="41" t="s">
         <v>60</v>
       </c>
       <c r="B147" s="4" t="s">
@@ -8461,7 +8462,7 @@
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="40" t="s">
+      <c r="A148" s="41" t="s">
         <v>60</v>
       </c>
       <c r="B148" s="4" t="s">
@@ -8499,7 +8500,7 @@
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" s="40" t="s">
+      <c r="A149" s="41" t="s">
         <v>60</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -8537,7 +8538,7 @@
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" s="40" t="s">
+      <c r="A150" s="41" t="s">
         <v>61</v>
       </c>
       <c r="B150" s="4" t="s">
@@ -8575,7 +8576,7 @@
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" s="40" t="s">
+      <c r="A151" s="41" t="s">
         <v>61</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -8613,7 +8614,7 @@
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A152" s="40" t="s">
+      <c r="A152" s="41" t="s">
         <v>61</v>
       </c>
       <c r="B152" s="4" t="s">
@@ -8651,7 +8652,7 @@
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A153" s="40" t="s">
+      <c r="A153" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -8689,7 +8690,7 @@
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A154" s="40" t="s">
+      <c r="A154" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B154" s="4" t="s">
@@ -8727,7 +8728,7 @@
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" s="40" t="s">
+      <c r="A155" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -8765,7 +8766,7 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" s="40" t="s">
+      <c r="A156" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B156" s="4" t="s">
@@ -8803,7 +8804,7 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" s="40" t="s">
+      <c r="A157" s="41" t="s">
         <v>63</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -8829,7 +8830,7 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" s="40" t="s">
+      <c r="A158" s="41" t="s">
         <v>63</v>
       </c>
       <c r="B158" s="4" t="s">
@@ -8855,7 +8856,7 @@
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" s="40" t="s">
+      <c r="A159" s="41" t="s">
         <v>63</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -8883,7 +8884,7 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" s="40" t="s">
+      <c r="A160" s="41" t="s">
         <v>63</v>
       </c>
       <c r="B160" s="4" t="s">
@@ -8911,7 +8912,7 @@
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" s="40" t="s">
+      <c r="A161" s="41" t="s">
         <v>64</v>
       </c>
       <c r="B161" s="4" t="s">
@@ -8929,7 +8930,7 @@
       <c r="L161" s="6"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A162" s="40" t="s">
+      <c r="A162" s="41" t="s">
         <v>64</v>
       </c>
       <c r="B162" s="4" t="s">
@@ -8947,7 +8948,7 @@
       <c r="L162" s="6"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" s="40" t="s">
+      <c r="A163" s="41" t="s">
         <v>64</v>
       </c>
       <c r="B163" s="4" t="s">
@@ -8967,7 +8968,7 @@
       <c r="L163" s="6"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" s="40" t="s">
+      <c r="A164" s="41" t="s">
         <v>65</v>
       </c>
       <c r="B164" s="4" t="s">
@@ -8995,7 +8996,7 @@
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A165" s="40" t="s">
+      <c r="A165" s="41" t="s">
         <v>65</v>
       </c>
       <c r="B165" s="4" t="s">
@@ -9033,7 +9034,7 @@
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A166" s="40" t="s">
+      <c r="A166" s="41" t="s">
         <v>65</v>
       </c>
       <c r="B166" s="4" t="s">
@@ -9071,7 +9072,7 @@
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A167" s="40" t="s">
+      <c r="A167" s="41" t="s">
         <v>65</v>
       </c>
       <c r="B167" s="4" t="s">
@@ -9109,7 +9110,7 @@
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A168" s="40" t="s">
+      <c r="A168" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B168" s="4" t="s">
@@ -9127,7 +9128,7 @@
       <c r="L168" s="6"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A169" s="40" t="s">
+      <c r="A169" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B169" s="4" t="s">
@@ -9165,7 +9166,7 @@
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A170" s="40" t="s">
+      <c r="A170" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B170" s="4" t="s">
@@ -9203,7 +9204,7 @@
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A171" s="40" t="s">
+      <c r="A171" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B171" s="4" t="s">
@@ -9241,7 +9242,7 @@
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A172" s="40" t="s">
+      <c r="A172" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B172" s="4" t="s">
@@ -9279,7 +9280,7 @@
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A173" s="40" t="s">
+      <c r="A173" s="41" t="s">
         <v>67</v>
       </c>
       <c r="B173" s="4" t="s">
@@ -9317,7 +9318,7 @@
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A174" s="40" t="s">
+      <c r="A174" s="41" t="s">
         <v>67</v>
       </c>
       <c r="B174" s="4" t="s">
@@ -9335,7 +9336,7 @@
       <c r="L174" s="6"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A175" s="40" t="s">
+      <c r="A175" s="41" t="s">
         <v>67</v>
       </c>
       <c r="B175" s="4" t="s">
@@ -9353,7 +9354,7 @@
       <c r="L175" s="6"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A176" s="40" t="s">
+      <c r="A176" s="41" t="s">
         <v>68</v>
       </c>
       <c r="B176" s="4" t="s">
@@ -9391,7 +9392,7 @@
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A177" s="40" t="s">
+      <c r="A177" s="41" t="s">
         <v>68</v>
       </c>
       <c r="B177" s="4" t="s">
@@ -9423,7 +9424,7 @@
       <c r="L177" s="6"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A178" s="40" t="s">
+      <c r="A178" s="41" t="s">
         <v>68</v>
       </c>
       <c r="B178" s="4" t="s">
@@ -9461,7 +9462,7 @@
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A179" s="40" t="s">
+      <c r="A179" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B179" s="4" t="s">
@@ -9499,7 +9500,7 @@
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A180" s="40" t="s">
+      <c r="A180" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B180" s="4" t="s">
@@ -9525,7 +9526,7 @@
       <c r="L180" s="6"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A181" s="40" t="s">
+      <c r="A181" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B181" s="4" t="s">
@@ -9563,7 +9564,7 @@
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A182" s="40" t="s">
+      <c r="A182" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B182" s="4" t="s">
@@ -9581,7 +9582,7 @@
       <c r="L182" s="6"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A183" s="40" t="s">
+      <c r="A183" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B183" s="4" t="s">
@@ -9599,7 +9600,7 @@
       <c r="L183" s="6"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A184" s="40" t="s">
+      <c r="A184" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B184" s="4" t="s">
@@ -9617,7 +9618,7 @@
       <c r="L184" s="6"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A185" s="40" t="s">
+      <c r="A185" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B185" s="4" t="s">
@@ -9635,7 +9636,7 @@
       <c r="L185" s="6"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A186" s="40" t="s">
+      <c r="A186" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B186" s="4" t="s">
@@ -9653,7 +9654,7 @@
       <c r="L186" s="6"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A187" s="40" t="s">
+      <c r="A187" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B187" s="4" t="s">
@@ -9671,7 +9672,7 @@
       <c r="L187" s="6"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A188" s="40" t="s">
+      <c r="A188" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B188" s="4" t="s">
@@ -9709,7 +9710,7 @@
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A189" s="40" t="s">
+      <c r="A189" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B189" s="4" t="s">
@@ -9747,7 +9748,7 @@
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A190" s="40" t="s">
+      <c r="A190" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B190" s="4" t="s">
@@ -9773,7 +9774,7 @@
       <c r="L190" s="6"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A191" s="40" t="s">
+      <c r="A191" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B191" s="4" t="s">
@@ -9811,7 +9812,7 @@
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A192" s="40" t="s">
+      <c r="A192" s="41" t="s">
         <v>72</v>
       </c>
       <c r="B192" s="4" t="s">
@@ -9829,7 +9830,7 @@
       <c r="L192" s="6"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A193" s="40" t="s">
+      <c r="A193" s="41" t="s">
         <v>72</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -9867,7 +9868,7 @@
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A194" s="40" t="s">
+      <c r="A194" s="41" t="s">
         <v>72</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -9897,7 +9898,7 @@
       <c r="L194" s="6"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A195" s="40" t="s">
+      <c r="A195" s="41" t="s">
         <v>72</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -9935,7 +9936,7 @@
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A196" s="40" t="s">
+      <c r="A196" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B196" s="4" t="s">
@@ -9973,7 +9974,7 @@
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A197" s="40" t="s">
+      <c r="A197" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B197" s="4" t="s">
@@ -9991,7 +9992,7 @@
       <c r="L197" s="6"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A198" s="40" t="s">
+      <c r="A198" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B198" s="4" t="s">
@@ -10029,7 +10030,7 @@
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A199" s="40" t="s">
+      <c r="A199" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -10067,7 +10068,7 @@
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A200" s="40" t="s">
+      <c r="A200" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -10105,7 +10106,7 @@
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A201" s="40" t="s">
+      <c r="A201" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B201" s="4" t="s">
@@ -10143,7 +10144,7 @@
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A202" s="40" t="s">
+      <c r="A202" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -10181,7 +10182,7 @@
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A203" s="40" t="s">
+      <c r="A203" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B203" s="4" t="s">
@@ -19237,7 +19238,7 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>

--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{318C915B-7EBB-4C2E-AB54-76CE7BB3ECDA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -27,9 +27,9 @@
     <definedName name="GAVI_countries" localSheetId="0">#REF!</definedName>
     <definedName name="GAVI_countries">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="4" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1798,7 +1798,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M3:W22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -1957,9 +1957,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1997,7 +1997,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2103,7 +2103,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2245,7 +2245,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2306,14 +2306,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3694F37-B2B5-4F9D-9ACD-67519624FADB}">
   <dimension ref="A1:T54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="91.109375" customWidth="1"/>
-    <col min="2" max="18" width="15.6640625" customWidth="1"/>
-    <col min="20" max="20" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="91.140625" customWidth="1"/>
+    <col min="2" max="18" width="15.7109375" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
@@ -2403,7 +2403,7 @@
       <c r="S2" s="34"/>
       <c r="T2" s="34"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>92</v>
       </c>
@@ -2431,7 +2431,7 @@
       <c r="S3" s="34"/>
       <c r="T3" s="34"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>93</v>
       </c>
@@ -2459,7 +2459,7 @@
       <c r="S4" s="34"/>
       <c r="T4" s="34"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>94</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>95</v>
       </c>
@@ -2519,7 +2519,7 @@
       <c r="S6" s="34"/>
       <c r="T6" s="34"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>96</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="S7" s="34"/>
       <c r="T7" s="34"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>157</v>
       </c>
@@ -2583,7 +2583,7 @@
       <c r="S8" s="34"/>
       <c r="T8" s="34"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>97</v>
       </c>
@@ -2611,7 +2611,7 @@
       <c r="S9" s="34"/>
       <c r="T9" s="34"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>98</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="S10" s="34"/>
       <c r="T10" s="34"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>99</v>
       </c>
@@ -2671,7 +2671,7 @@
       <c r="S11" s="34"/>
       <c r="T11" s="34"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>100</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="S12" s="34"/>
       <c r="T12" s="34"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>101</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="S13" s="34"/>
       <c r="T13" s="34"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>102</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="S14" s="34"/>
       <c r="T14" s="34"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>103</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>104</v>
       </c>
@@ -2829,7 +2829,7 @@
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>105</v>
       </c>
@@ -2859,7 +2859,7 @@
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>158</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>155</v>
       </c>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="T19" s="10"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2939,7 +2939,7 @@
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2958,7 +2958,7 @@
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2977,7 +2977,7 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -2996,7 +2996,7 @@
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3015,7 +3015,7 @@
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -3034,7 +3034,7 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -3053,7 +3053,7 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -3072,7 +3072,7 @@
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -3091,7 +3091,7 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3110,7 +3110,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -3129,7 +3129,7 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3148,7 +3148,7 @@
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3167,7 +3167,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3186,7 +3186,7 @@
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3205,7 +3205,7 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3224,7 +3224,7 @@
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3243,7 +3243,7 @@
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3262,7 +3262,7 @@
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3281,7 +3281,7 @@
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3300,7 +3300,7 @@
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3319,7 +3319,7 @@
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3338,7 +3338,7 @@
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3357,7 +3357,7 @@
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3376,7 +3376,7 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3395,7 +3395,7 @@
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3414,7 +3414,7 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3433,7 +3433,7 @@
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3452,7 +3452,7 @@
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3471,7 +3471,7 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3490,7 +3490,7 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3509,7 +3509,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -3528,7 +3528,7 @@
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -3547,7 +3547,7 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3566,7 +3566,7 @@
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3617,17 +3617,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7054496A-AF4B-4EC1-B368-49C550220A1C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L301"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="94.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="12" width="18" style="2" customWidth="1"/>
     <col min="13" max="13" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>12</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>12</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>26819200.996155463</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>12</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>56018232.597976193</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>12</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>170565705.92964286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>12</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>79877180.657261893</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>18</v>
       </c>
@@ -3865,7 +3865,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>18</v>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
         <v>18</v>
       </c>
@@ -3925,7 +3925,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>18</v>
       </c>
@@ -3955,7 +3955,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
         <v>19</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>1403270410.0475006</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>19</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>43232783.299999997</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
         <v>19</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>789204932.27500033</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>19</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>500814543.58749998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -4143,7 +4143,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
         <v>22</v>
       </c>
@@ -4161,7 +4161,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>22</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>12788293.736842105</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>22</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>863986.71500000008</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>22</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>5370201.9115789467</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>22</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>4313357.7878842624</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>23</v>
       </c>
@@ -4331,7 +4331,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
         <v>23</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>44326790.909789473</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>23</v>
       </c>
@@ -4387,7 +4387,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="s">
         <v>23</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>23</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>430931.20894736843</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -4473,7 +4473,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>25</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>24359.106315789475</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
         <v>25</v>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="41" t="s">
         <v>25</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>29653.105263157893</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="41" t="s">
         <v>26</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>22700002.013999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="41" t="s">
         <v>26</v>
       </c>
@@ -4631,7 +4631,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="s">
         <v>26</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>9708542.1121710539</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="41" t="s">
         <v>27</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>2385352.0408421056</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="41" t="s">
         <v>27</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="41" t="s">
         <v>27</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>6987.9032894736847</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="41" t="s">
         <v>28</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>3753257.1406578948</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="41" t="s">
         <v>28</v>
       </c>
@@ -4827,7 +4827,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="41" t="s">
         <v>29</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>17711618.430631582</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="41" t="s">
         <v>29</v>
       </c>
@@ -4891,7 +4891,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="41" t="s">
         <v>29</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>8274488.3427631576</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="41" t="s">
         <v>30</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>12708293.497763159</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
         <v>30</v>
       </c>
@@ -4985,7 +4985,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
         <v>30</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>129709.70407894738</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="41" t="s">
         <v>31</v>
       </c>
@@ -5041,7 +5041,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="41" t="s">
         <v>31</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>4366498.504999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="41" t="s">
         <v>31</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>924903.77499999991</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="41" t="s">
         <v>31</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>56671594.19749999</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="41" t="s">
         <v>31</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>28451376.886823118</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="41" t="s">
         <v>32</v>
       </c>
@@ -5211,7 +5211,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
         <v>32</v>
       </c>
@@ -5229,7 +5229,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="41" t="s">
         <v>32</v>
       </c>
@@ -5247,7 +5247,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="41" t="s">
         <v>32</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>1371371.7111111111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="41" t="s">
         <v>33</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>4588112.7602708973</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="41" t="s">
         <v>33</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>68258991.188157901</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
         <v>33</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>202310628.16776317</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
         <v>33</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>61534344.793815792</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
         <v>34</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>99151.439999999988</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
         <v>34</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>3781590.8850000007</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
         <v>34</v>
       </c>
@@ -5551,7 +5551,7 @@
         <v>2364272.5157894739</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
         <v>34</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="41" t="s">
         <v>35</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>42709218.048947372</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="41" t="s">
         <v>35</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>585519.70234210533</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="41" t="s">
         <v>35</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>6391844.9436842091</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
         <v>36</v>
       </c>
@@ -5703,7 +5703,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
         <v>36</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>71135570.336828187</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="41" t="s">
         <v>36</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>8918362.7869736832</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="41" t="s">
         <v>36</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>56037443.403815791</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="41" t="s">
         <v>36</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>26078721.471578948</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="41" t="s">
         <v>37</v>
       </c>
@@ -5873,7 +5873,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="41" t="s">
         <v>37</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>13285092.037631579</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
         <v>37</v>
       </c>
@@ -5929,7 +5929,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
         <v>37</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
         <v>37</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>7212690.1784210531</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="41" t="s">
         <v>38</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>3143161.6294736844</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
         <v>38</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>694846.97368421056</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
         <v>40</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>31169164.653893046</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
         <v>40</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>9024207.2250826061</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
         <v>40</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>26014337.772836529</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="41" t="s">
         <v>40</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>21218834.523721006</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
         <v>41</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>24485113.215146199</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="41" t="s">
         <v>41</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>42986086.185204685</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="41" t="s">
         <v>41</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>89969889.638869569</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="41" t="s">
         <v>41</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>43092807.72445029</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
         <v>42</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>26223826.190433443</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
         <v>42</v>
       </c>
@@ -6451,7 +6451,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="41" t="s">
         <v>42</v>
       </c>
@@ -6489,7 +6489,7 @@
         <v>38913109.206510134</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="41" t="s">
         <v>42</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>8318128.2670879252</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="42" t="s">
         <v>43</v>
       </c>
@@ -6545,7 +6545,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="43" t="s">
         <v>43</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>593298.1894736843</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="43" t="s">
         <v>43</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>882693.01642857143</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="43" t="s">
         <v>43</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>68866.200000000012</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="44" t="s">
         <v>43</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>9727462.9341666661</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="41" t="s">
         <v>44</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="41" t="s">
         <v>44</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>16995032.578833334</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="41" t="s">
         <v>44</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>22529845.132500004</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="41" t="s">
         <v>45</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>11652763.552941177</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="41" t="s">
         <v>45</v>
       </c>
@@ -6859,7 +6859,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="41" t="s">
         <v>45</v>
       </c>
@@ -6885,7 +6885,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="41" t="s">
         <v>46</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>3129137.4496973683</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="41" t="s">
         <v>46</v>
       </c>
@@ -6941,7 +6941,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="41" t="s">
         <v>46</v>
       </c>
@@ -6967,7 +6967,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="41" t="s">
         <v>47</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>19439134.578947369</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="41" t="s">
         <v>47</v>
       </c>
@@ -7025,7 +7025,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="41" t="s">
         <v>47</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>12278482.1775</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="41" t="s">
         <v>48</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="41" t="s">
         <v>48</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>428081.60342105263</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="41" t="s">
         <v>48</v>
       </c>
@@ -7155,7 +7155,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="41" t="s">
         <v>49</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="41" t="s">
         <v>49</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>15938780.685739476</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="41" t="s">
         <v>49</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>7463.7629999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="41" t="s">
         <v>49</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>6024488.8079210529</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="41" t="s">
         <v>50</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="41" t="s">
         <v>50</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>3357564.5291447369</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="41" t="s">
         <v>50</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>277375.88714868418</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="41" t="s">
         <v>50</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>48463.652665350877</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="41" t="s">
         <v>50</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>962589.57300000009</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>51</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>4199871.1182460524</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="41" t="s">
         <v>52</v>
       </c>
@@ -7549,7 +7549,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="41" t="s">
         <v>52</v>
       </c>
@@ -7581,7 +7581,7 @@
         <v>8001.5255263157915</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="41" t="s">
         <v>52</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>196251.34736842106</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="41" t="s">
         <v>53</v>
       </c>
@@ -7657,7 +7657,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="41" t="s">
         <v>53</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>3969424.3796421057</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="41" t="s">
         <v>53</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>8895367.3138157893</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="41" t="s">
         <v>54</v>
       </c>
@@ -7751,7 +7751,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="41" t="s">
         <v>54</v>
       </c>
@@ -7769,7 +7769,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="41" t="s">
         <v>54</v>
       </c>
@@ -7787,7 +7787,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="41" t="s">
         <v>54</v>
       </c>
@@ -7807,7 +7807,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="41" t="s">
         <v>55</v>
       </c>
@@ -7825,7 +7825,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="41" t="s">
         <v>55</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>44666553.82686425</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="41" t="s">
         <v>55</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>2148068.0935714287</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="41" t="s">
         <v>55</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>10829590.64130117</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="41" t="s">
         <v>55</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>53816727.563368849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="41" t="s">
         <v>56</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>5366204.9252105262</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="41" t="s">
         <v>56</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>1918456.0949999997</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="41" t="s">
         <v>57</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>2456094.4891353385</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="41" t="s">
         <v>57</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>84871745.658650786</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="41" t="s">
         <v>57</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>228007209.74936509</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="41" t="s">
         <v>57</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>32273220.97396826</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>58</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>1012182.5810526316</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="41" t="s">
         <v>59</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="41" t="s">
         <v>59</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>19377207.360228568</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="41" t="s">
         <v>59</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>123225959.44543454</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="41" t="s">
         <v>59</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>9816494.2557882406</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="41" t="s">
         <v>60</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>85488520.6669323</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="41" t="s">
         <v>60</v>
       </c>
@@ -8461,7 +8461,7 @@
         <v>57292565.508875743</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="41" t="s">
         <v>60</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>162941685.62800577</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="41" t="s">
         <v>60</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>66591452.998300254</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="41" t="s">
         <v>61</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>6418700.4964842089</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="41" t="s">
         <v>61</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>657.72019736842117</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="41" t="s">
         <v>61</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>38980.994268421055</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="41" t="s">
         <v>62</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>57668115.752105266</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="41" t="s">
         <v>62</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>48207996.665438592</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="41" t="s">
         <v>62</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>163594841.15653506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="41" t="s">
         <v>62</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>51145121.535921052</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="41" t="s">
         <v>63</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>1140116.518780523</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="41" t="s">
         <v>63</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>3095533.6346984911</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="41" t="s">
         <v>63</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>24073104.668296658</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="41" t="s">
         <v>63</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>8249515.7360912031</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="41" t="s">
         <v>64</v>
       </c>
@@ -8929,7 +8929,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="41" t="s">
         <v>64</v>
       </c>
@@ -8947,7 +8947,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="41" t="s">
         <v>64</v>
       </c>
@@ -8967,7 +8967,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="41" t="s">
         <v>65</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>524620.18888888881</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="41" t="s">
         <v>65</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>11686619.239444446</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="41" t="s">
         <v>65</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>67230835.707277775</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="41" t="s">
         <v>65</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>8927850.3513888884</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="41" t="s">
         <v>66</v>
       </c>
@@ -9127,7 +9127,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="41" t="s">
         <v>66</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>11586096.10842105</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="41" t="s">
         <v>66</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>61286058.379432946</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="41" t="s">
         <v>66</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>198326735.48209769</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="41" t="s">
         <v>66</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>74368544.324421823</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="41" t="s">
         <v>67</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>37434.968421052632</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="41" t="s">
         <v>67</v>
       </c>
@@ -9335,7 +9335,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="41" t="s">
         <v>67</v>
       </c>
@@ -9353,7 +9353,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="41" t="s">
         <v>68</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>14085732.501447368</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="41" t="s">
         <v>68</v>
       </c>
@@ -9423,7 +9423,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="41" t="s">
         <v>68</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>2658726.6143421056</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="41" t="s">
         <v>69</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>5274066.9230263159</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="41" t="s">
         <v>69</v>
       </c>
@@ -9525,7 +9525,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="41" t="s">
         <v>69</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>109338.78881578946</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="41" t="s">
         <v>70</v>
       </c>
@@ -9581,7 +9581,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="41" t="s">
         <v>70</v>
       </c>
@@ -9599,7 +9599,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="41" t="s">
         <v>70</v>
       </c>
@@ -9617,7 +9617,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="41" t="s">
         <v>70</v>
       </c>
@@ -9635,7 +9635,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="41" t="s">
         <v>70</v>
       </c>
@@ -9653,7 +9653,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="41" t="s">
         <v>71</v>
       </c>
@@ -9671,7 +9671,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="41" t="s">
         <v>71</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>1602020.15372807</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="41" t="s">
         <v>71</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="41" t="s">
         <v>71</v>
       </c>
@@ -9773,7 +9773,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="41" t="s">
         <v>71</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>8435990.8228508774</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="41" t="s">
         <v>72</v>
       </c>
@@ -9829,7 +9829,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="41" t="s">
         <v>72</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>41053.861588892236</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="41" t="s">
         <v>72</v>
       </c>
@@ -9897,7 +9897,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="41" t="s">
         <v>72</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>361138.98097679514</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="41" t="s">
         <v>73</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>21801576.347789474</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="41" t="s">
         <v>73</v>
       </c>
@@ -9991,7 +9991,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="41" t="s">
         <v>73</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>4773371.973289473</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="41" t="s">
         <v>74</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="41" t="s">
         <v>74</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>95686.964999999997</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="41" t="s">
         <v>74</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>19427327.223125003</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="41" t="s">
         <v>74</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>28291617.551274512</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="41" t="s">
         <v>74</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>21470697.767319441</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
@@ -10231,7 +10231,7 @@
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
-    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
@@ -10243,7 +10243,7 @@
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
@@ -10255,7 +10255,7 @@
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>43</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>22913488.673833333</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>57</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>312878955.40801585</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>55</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>12977658.734872598</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>71</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>66</v>
       </c>
@@ -10495,7 +10495,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>108</v>
       </c>
@@ -10543,7 +10543,7 @@
         <v>6234188.6265789466</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>109</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>57596497.972499989</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>98</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>99</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>270569619.35592109</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="16" t="s">
         <v>100</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>101</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>132955975.82407425</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>102</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>103</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>35038544.997919135</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>104</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>64955806.190789476</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>105</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>62</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>211802837.82197365</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>60</v>
       </c>
@@ -11071,10 +11071,10 @@
         <v>220234251.13688153</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C224" s="8"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>113</v>
       </c>
@@ -11087,7 +11087,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>114</v>
       </c>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="C226" s="8"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>106</v>
       </c>
@@ -11104,14 +11104,14 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
       <c r="J228" s="15"/>
       <c r="K228" s="15"/>
       <c r="L228" s="15"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B229" s="2" t="s">
         <v>115</v>
       </c>
@@ -11121,7 +11121,7 @@
       <c r="K229" s="27"/>
       <c r="L229" s="27"/>
     </row>
-    <row r="230" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="18" t="s">
         <v>43</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>20622139.806450002</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>75</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>16872659.841640912</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>118</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>3749479.9648090904</v>
       </c>
     </row>
-    <row r="233" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="18" t="s">
         <v>57</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>281591059.86721426</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>75</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>203910767.49005172</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>119</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>77680292.377162561</v>
       </c>
     </row>
-    <row r="236" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="18" t="s">
         <v>55</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>11679892.861385338</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>116</v>
       </c>
@@ -11496,7 +11496,7 @@
         <v>3412103.5325395376</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>117</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>8267789.3288458008</v>
       </c>
     </row>
-    <row r="239" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="18" t="s">
         <v>71</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>75</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>2289842.5978235295</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>118</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>508853.91062745103</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>81</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>290773.66321568622</v>
       </c>
     </row>
-    <row r="243" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="18" t="s">
         <v>66</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>75</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>192418894.27384037</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>118</v>
       </c>
@@ -11874,7 +11874,7 @@
         <v>42759754.283075638</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>81</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>24434145.304614648</v>
       </c>
     </row>
-    <row r="247" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="18" t="s">
         <v>108</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>6857607.4892368419</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>75</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>5082697.3155520121</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>118</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>1129488.2923448917</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>81</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>645421.88133993803</v>
       </c>
     </row>
-    <row r="251" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="18" t="s">
         <v>109</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>63356147.769749992</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>75</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>45878589.764301717</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>119</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>17477558.005448274</v>
       </c>
     </row>
-    <row r="254" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="18" t="s">
         <v>98</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>75</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="256" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="18" t="s">
         <v>99</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>297626581.2915132</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>75</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>165933403.72889677</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>118</v>
       </c>
@@ -12486,7 +12486,7 @@
         <v>36874089.717532612</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>119</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>63212725.230055898</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>82</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>21070908.410018638</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>83</v>
       </c>
@@ -12630,12 +12630,12 @@
         <v>10535454.205009319</v>
       </c>
     </row>
-    <row r="262" spans="1:12" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" s="21" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="23" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="18" t="s">
         <v>101</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>146251573.40648168</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>82</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>53182390.329629704</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>84</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>85</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>86</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>59830189.120833419</v>
       </c>
     </row>
-    <row r="268" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="18" t="s">
         <v>102</v>
       </c>
@@ -12917,7 +12917,7 @@
         <v>404502055.98924994</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>75</v>
       </c>
@@ -12965,7 +12965,7 @@
         <v>172186685.99542397</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="22" t="s">
         <v>76</v>
       </c>
@@ -13013,7 +13013,7 @@
         <v>38263707.998983108</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>77</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>71061171.998111486</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>80</v>
       </c>
@@ -13109,7 +13109,7 @@
         <v>68328049.998184115</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>83</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>10932487.999709459</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>87</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>88</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>27331219.999273647</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="277" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="18" t="s">
         <v>103</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>31534690.498127222</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>77</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>24845513.725797206</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>79</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>90</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="28" t="s">
         <v>154</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="282" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
         <v>104</v>
       </c>
@@ -13578,7 +13578,7 @@
         <v>71451386.809868425</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>75</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>63400526.324249454</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>82</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="285" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="18" t="s">
         <v>105</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>3954.38333881579</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>75</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>2737.650003795547</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>80</v>
       </c>
@@ -13815,7 +13815,7 @@
         <v>1086.3690491252169</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>91</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="289" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="29" t="s">
         <v>62</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>190622554.0397763</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>75</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>121305261.66167584</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>88</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>13932545.477990292</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>77</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>50062488.939739235</v>
       </c>
     </row>
-    <row r="293" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="29" t="s">
         <v>155</v>
       </c>
@@ -14097,7 +14097,7 @@
         <v>242257676.2505697</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>75</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>165893843.51941183</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>156</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>77</v>
       </c>
@@ -14241,7 +14241,7 @@
         <v>68464125.896900132</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H301" s="16"/>
       <c r="I301" s="16"/>
       <c r="J301" s="16"/>
@@ -14340,15 +14340,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55228539-2602-4D9E-BF99-AB1A3FA50A1F}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -14486,7 +14486,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -14622,7 +14622,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -14758,7 +14758,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>142</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -14962,7 +14962,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>144</v>
       </c>
@@ -15098,7 +15098,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>145</v>
       </c>
@@ -15166,7 +15166,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -15234,7 +15234,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -15370,7 +15370,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -15506,7 +15506,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>154</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>147</v>
       </c>
@@ -15710,7 +15710,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>147</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>148</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>149</v>
       </c>
@@ -15984,7 +15984,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>156</v>
       </c>
@@ -16052,7 +16052,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>150</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>150</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>150</v>
       </c>
@@ -16256,7 +16256,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>150</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>150</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>150</v>
       </c>
@@ -16460,7 +16460,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -16528,7 +16528,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -16596,7 +16596,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>152</v>
       </c>
@@ -16732,7 +16732,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>152</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
@@ -16868,7 +16868,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>152</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -17140,7 +17140,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>152</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
@@ -17351,7 +17351,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -17429,7 +17429,7 @@
         <v>25400000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -17507,7 +17507,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M52" t="s">
         <v>145</v>
       </c>
@@ -17786,7 +17786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
         <v>116</v>
       </c>
@@ -17831,7 +17831,7 @@
         <v>217800000</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
         <v>146</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M55" t="s">
         <v>154</v>
       </c>
@@ -17921,7 +17921,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
         <v>147</v>
       </c>
@@ -17966,7 +17966,7 @@
         <v>82300000</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
         <v>148</v>
       </c>
@@ -18011,7 +18011,7 @@
         <v>5700000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M58" t="s">
         <v>149</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M59" t="s">
         <v>156</v>
       </c>
@@ -18101,7 +18101,7 @@
         <v>7900000</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M60" t="s">
         <v>150</v>
       </c>
@@ -18146,7 +18146,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M61" t="s">
         <v>151</v>
       </c>
@@ -18191,7 +18191,7 @@
         <v>128200000</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M62" t="s">
         <v>152</v>
       </c>
@@ -18236,7 +18236,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M63" t="s">
         <v>153</v>
       </c>
@@ -18290,13 +18290,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{770C77AF-CB50-4854-8654-5465FF2CEF2B}">
   <dimension ref="B2:T19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
         <v>84</v>
       </c>
@@ -18352,7 +18352,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
         <v>81</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>"Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>87</v>
       </c>
@@ -18436,7 +18436,7 @@
         <v>"AJ_Vaccines","BB_NCIPD","Beijing_Institute","Bharat_Biotech","Bilthoven","Biological_E","Centro_de","GSK","Haffkine_Bio","LG_Chem","Merck_Sharp","Panacea_Biotec","PT_Bio","Sanofi_Pasteur","Serum_Institute","Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>88</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>85</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
         <v>119</v>
       </c>
@@ -18460,7 +18460,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
         <v>91</v>
       </c>
@@ -18468,7 +18468,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
         <v>77</v>
       </c>
@@ -18476,7 +18476,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="26" t="s">
         <v>89</v>
       </c>
@@ -18484,7 +18484,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="26" t="s">
         <v>82</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
         <v>79</v>
       </c>
@@ -18500,7 +18500,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
         <v>83</v>
       </c>
@@ -18508,7 +18508,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
         <v>118</v>
       </c>
@@ -18516,7 +18516,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
         <v>80</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>75</v>
       </c>
@@ -18532,7 +18532,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
         <v>90</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
         <v>156</v>
       </c>
@@ -18548,7 +18548,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
         <v>154</v>
       </c>
@@ -18565,13 +18565,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="36">
         <v>1</v>
       </c>
@@ -18603,7 +18606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -18638,7 +18641,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -18673,7 +18676,7 @@
         <v>25400000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -18708,7 +18711,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -18743,7 +18746,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>143</v>
       </c>
@@ -18778,7 +18781,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>144</v>
       </c>
@@ -18813,7 +18816,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>145</v>
       </c>
@@ -18848,7 +18851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -18883,7 +18886,7 @@
         <v>217800000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -18918,77 +18921,87 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="37">
-        <v>60600000</v>
-      </c>
-      <c r="C11" s="37">
-        <v>74600000</v>
-      </c>
-      <c r="D11" s="37">
-        <v>83000000</v>
-      </c>
-      <c r="E11" s="37">
-        <v>81300000</v>
-      </c>
-      <c r="F11" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="G11" s="37">
-        <v>79800000</v>
-      </c>
-      <c r="H11" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="I11" s="37">
-        <v>79900000</v>
-      </c>
-      <c r="J11" s="37">
-        <v>81200000</v>
-      </c>
-      <c r="K11" s="37">
-        <v>82300000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="25">
+        <f>B20*17</f>
+        <v>1030200000</v>
+      </c>
+      <c r="C11" s="25">
+        <f t="shared" ref="C11:K11" si="0">C20*17</f>
+        <v>1268200000</v>
+      </c>
+      <c r="D11" s="25">
+        <f t="shared" si="0"/>
+        <v>1411000000</v>
+      </c>
+      <c r="E11" s="25">
+        <f t="shared" si="0"/>
+        <v>1382100000</v>
+      </c>
+      <c r="F11" s="25">
+        <f t="shared" si="0"/>
+        <v>1378700000</v>
+      </c>
+      <c r="G11" s="25">
+        <f t="shared" si="0"/>
+        <v>1356600000</v>
+      </c>
+      <c r="H11" s="25">
+        <f t="shared" si="0"/>
+        <v>1378700000</v>
+      </c>
+      <c r="I11" s="25">
+        <f t="shared" si="0"/>
+        <v>1358300000</v>
+      </c>
+      <c r="J11" s="25">
+        <f t="shared" si="0"/>
+        <v>1380400000</v>
+      </c>
+      <c r="K11" s="25">
+        <f t="shared" si="0"/>
+        <v>1399100000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>148</v>
       </c>
       <c r="B12" s="37">
-        <v>3100000</v>
+        <v>248000000</v>
       </c>
       <c r="C12" s="37">
-        <v>3100000</v>
+        <v>248000000</v>
       </c>
       <c r="D12" s="37">
-        <v>4500000</v>
+        <v>360000000</v>
       </c>
       <c r="E12" s="37">
-        <v>11900000</v>
+        <v>952000000</v>
       </c>
       <c r="F12" s="37">
-        <v>15200000</v>
+        <v>1216000000</v>
       </c>
       <c r="G12" s="37">
-        <v>10600000</v>
+        <v>848000000</v>
       </c>
       <c r="H12" s="37">
-        <v>6900000</v>
+        <v>552000000</v>
       </c>
       <c r="I12" s="37">
-        <v>6900000</v>
+        <v>552000000</v>
       </c>
       <c r="J12" s="37">
-        <v>5500000</v>
+        <v>440000000</v>
       </c>
       <c r="K12" s="37">
-        <v>5700000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>456000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -19023,7 +19036,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -19058,7 +19071,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -19093,7 +19106,7 @@
         <v>128200000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -19128,7 +19141,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -19163,7 +19176,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>156</v>
       </c>
@@ -19198,19 +19211,51 @@
         <v>7900000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="37">
+        <v>60600000</v>
+      </c>
+      <c r="C20" s="37">
+        <v>74600000</v>
+      </c>
+      <c r="D20" s="37">
+        <v>83000000</v>
+      </c>
+      <c r="E20" s="37">
+        <v>81300000</v>
+      </c>
+      <c r="F20" s="37">
+        <v>81100000</v>
+      </c>
+      <c r="G20" s="37">
+        <v>79800000</v>
+      </c>
+      <c r="H20" s="37">
+        <v>81100000</v>
+      </c>
+      <c r="I20" s="37">
+        <v>79900000</v>
+      </c>
+      <c r="J20" s="37">
+        <v>81200000</v>
+      </c>
+      <c r="K20" s="37">
+        <v>82300000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -19222,7 +19267,7 @@
       <c r="J21" s="25"/>
       <c r="K21" s="25"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -19234,7 +19279,7 @@
       <c r="J22" s="25"/>
       <c r="K22" s="25"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -19246,7 +19291,7 @@
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -19258,7 +19303,7 @@
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -19270,7 +19315,7 @@
       <c r="J25" s="25"/>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -19282,7 +19327,7 @@
       <c r="J26" s="25"/>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -19294,7 +19339,7 @@
       <c r="J27" s="25"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -19306,7 +19351,7 @@
       <c r="J28" s="25"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -19318,7 +19363,7 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -19330,7 +19375,7 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -19342,7 +19387,7 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -19354,7 +19399,7 @@
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -19366,7 +19411,7 @@
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -19378,7 +19423,7 @@
       <c r="J34" s="25"/>
       <c r="K34" s="25"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -19390,7 +19435,7 @@
       <c r="J35" s="25"/>
       <c r="K35" s="25"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -19402,7 +19447,7 @@
       <c r="J36" s="25"/>
       <c r="K36" s="25"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -19414,7 +19459,7 @@
       <c r="J37" s="25"/>
       <c r="K37" s="25"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -19426,7 +19471,7 @@
       <c r="J38" s="25"/>
       <c r="K38" s="25"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -19438,7 +19483,7 @@
       <c r="J39" s="25"/>
       <c r="K39" s="25"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -19450,7 +19495,7 @@
       <c r="J40" s="25"/>
       <c r="K40" s="25"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -19462,7 +19507,7 @@
       <c r="J41" s="25"/>
       <c r="K41" s="25"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -19474,7 +19519,7 @@
       <c r="J42" s="25"/>
       <c r="K42" s="25"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -19486,7 +19531,7 @@
       <c r="J43" s="25"/>
       <c r="K43" s="25"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>

--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{318C915B-7EBB-4C2E-AB54-76CE7BB3ECDA}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77F21EE-8157-4E23-95E5-4D730731A823}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -710,7 +710,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -783,6 +783,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF098658"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -937,7 +943,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1009,6 +1015,12 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1798,7 +1810,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M3:W22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -3666,7 +3678,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3684,7 +3696,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -3722,7 +3734,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -3760,7 +3772,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3798,7 +3810,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -3836,7 +3848,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3866,7 +3878,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -3896,7 +3908,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -3926,7 +3938,7 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -3956,7 +3968,7 @@
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="43" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -3994,7 +4006,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="43" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -4032,7 +4044,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="43" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="43" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4144,7 +4156,7 @@
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -4162,7 +4174,7 @@
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -4200,7 +4212,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -4276,7 +4288,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -4314,7 +4326,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -4332,7 +4344,7 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -4370,7 +4382,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -4388,7 +4400,7 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -4418,7 +4430,7 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -4474,7 +4486,7 @@
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -4512,7 +4524,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -4542,7 +4554,7 @@
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -4568,7 +4580,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -4606,7 +4618,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -4632,7 +4644,7 @@
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -4670,7 +4682,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="43" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -4708,7 +4720,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -4738,7 +4750,7 @@
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="43" t="s">
         <v>27</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -4764,7 +4776,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="41" t="s">
+      <c r="A37" s="43" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -4802,7 +4814,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="43" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4828,7 +4840,7 @@
       <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="41" t="s">
+      <c r="A39" s="43" t="s">
         <v>29</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -4866,7 +4878,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="43" t="s">
         <v>29</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -4892,7 +4904,7 @@
       <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="41" t="s">
+      <c r="A41" s="43" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -4930,7 +4942,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="43" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -4968,7 +4980,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="43" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -4986,7 +4998,7 @@
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="43" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -5024,7 +5036,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -5042,7 +5054,7 @@
       <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -5080,7 +5092,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -5118,7 +5130,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -5156,7 +5168,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -5194,7 +5206,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -5212,7 +5224,7 @@
       <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -5230,7 +5242,7 @@
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="41" t="s">
+      <c r="A52" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -5248,7 +5260,7 @@
       <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="41" t="s">
+      <c r="A53" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="43" t="s">
         <v>33</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -5324,7 +5336,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="41" t="s">
+      <c r="A55" s="43" t="s">
         <v>33</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -5362,7 +5374,7 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="43" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -5400,7 +5412,7 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="43" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -5476,7 +5488,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -5552,7 +5564,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="41" t="s">
+      <c r="A61" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -5572,7 +5584,7 @@
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -5610,7 +5622,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="41" t="s">
+      <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -5648,7 +5660,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="41" t="s">
+      <c r="A64" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -5686,7 +5698,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -5704,7 +5716,7 @@
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="41" t="s">
+      <c r="A66" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -5742,7 +5754,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="41" t="s">
+      <c r="A67" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -5780,7 +5792,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="41" t="s">
+      <c r="A68" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -5818,7 +5830,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="41" t="s">
+      <c r="A69" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="41" t="s">
+      <c r="A70" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -5874,7 +5886,7 @@
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="41" t="s">
+      <c r="A71" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -5912,7 +5924,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="41" t="s">
+      <c r="A72" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -5930,7 +5942,7 @@
       <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="41" t="s">
+      <c r="A73" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -5960,7 +5972,7 @@
       <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="41" t="s">
+      <c r="A74" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="41" t="s">
+      <c r="A75" s="43" t="s">
         <v>38</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -6028,7 +6040,7 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="41" t="s">
+      <c r="A76" s="43" t="s">
         <v>38</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -6092,7 +6104,7 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="41" t="s">
+      <c r="A78" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -6130,7 +6142,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="41" t="s">
+      <c r="A79" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -6168,7 +6180,7 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="41" t="s">
+      <c r="A80" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -6206,7 +6218,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="41" t="s">
+      <c r="A81" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="41" t="s">
+      <c r="A82" s="43" t="s">
         <v>41</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -6282,7 +6294,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="43" t="s">
         <v>41</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -6320,7 +6332,7 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="41" t="s">
+      <c r="A84" s="43" t="s">
         <v>41</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -6358,7 +6370,7 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="43" t="s">
         <v>41</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -6396,7 +6408,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="41" t="s">
+      <c r="A86" s="43" t="s">
         <v>42</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -6434,7 +6446,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="41" t="s">
+      <c r="A87" s="43" t="s">
         <v>42</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -6452,7 +6464,7 @@
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="41" t="s">
+      <c r="A88" s="43" t="s">
         <v>42</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -6490,7 +6502,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="41" t="s">
+      <c r="A89" s="43" t="s">
         <v>42</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -6528,7 +6540,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="42" t="s">
+      <c r="A90" s="44" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -6546,7 +6558,7 @@
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="43" t="s">
+      <c r="A91" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -6584,7 +6596,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="43" t="s">
+      <c r="A92" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -6622,7 +6634,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="43" t="s">
+      <c r="A93" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -6660,7 +6672,7 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="44" t="s">
+      <c r="A94" s="46" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -6698,7 +6710,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="41" t="s">
+      <c r="A95" s="43" t="s">
         <v>44</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -6736,7 +6748,7 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="41" t="s">
+      <c r="A96" s="43" t="s">
         <v>44</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -6774,7 +6786,7 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="41" t="s">
+      <c r="A97" s="43" t="s">
         <v>44</v>
       </c>
       <c r="B97" s="4" t="s">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="41" t="s">
+      <c r="A98" s="43" t="s">
         <v>45</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -6842,7 +6854,7 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="41" t="s">
+      <c r="A99" s="43" t="s">
         <v>45</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -6860,7 +6872,7 @@
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="41" t="s">
+      <c r="A100" s="43" t="s">
         <v>45</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -6886,7 +6898,7 @@
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="41" t="s">
+      <c r="A101" s="43" t="s">
         <v>46</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -6924,7 +6936,7 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="41" t="s">
+      <c r="A102" s="43" t="s">
         <v>46</v>
       </c>
       <c r="B102" s="4" t="s">
@@ -6942,7 +6954,7 @@
       <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="41" t="s">
+      <c r="A103" s="43" t="s">
         <v>46</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -6968,7 +6980,7 @@
       <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="41" t="s">
+      <c r="A104" s="43" t="s">
         <v>47</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="41" t="s">
+      <c r="A105" s="43" t="s">
         <v>47</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -7026,7 +7038,7 @@
       <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="41" t="s">
+      <c r="A106" s="43" t="s">
         <v>47</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="41" t="s">
+      <c r="A107" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -7100,7 +7112,7 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="41" t="s">
+      <c r="A108" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="41" t="s">
+      <c r="A109" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -7156,7 +7168,7 @@
       <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="41" t="s">
+      <c r="A110" s="43" t="s">
         <v>49</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -7194,7 +7206,7 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="41" t="s">
+      <c r="A111" s="43" t="s">
         <v>49</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -7232,7 +7244,7 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="41" t="s">
+      <c r="A112" s="43" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="4" t="s">
@@ -7268,7 +7280,7 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="41" t="s">
+      <c r="A113" s="43" t="s">
         <v>49</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -7306,7 +7318,7 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="41" t="s">
+      <c r="A114" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B114" s="4" t="s">
@@ -7344,7 +7356,7 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="41" t="s">
+      <c r="A115" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -7382,7 +7394,7 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="41" t="s">
+      <c r="A116" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B116" s="4" t="s">
@@ -7420,7 +7432,7 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="41" t="s">
+      <c r="A117" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -7458,7 +7470,7 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="41" t="s">
+      <c r="A118" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -7532,7 +7544,7 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="41" t="s">
+      <c r="A120" s="43" t="s">
         <v>52</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -7550,7 +7562,7 @@
       <c r="L120" s="6"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="41" t="s">
+      <c r="A121" s="43" t="s">
         <v>52</v>
       </c>
       <c r="B121" s="4" t="s">
@@ -7582,7 +7594,7 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="41" t="s">
+      <c r="A122" s="43" t="s">
         <v>52</v>
       </c>
       <c r="B122" s="4" t="s">
@@ -7620,7 +7632,7 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="41" t="s">
+      <c r="A123" s="43" t="s">
         <v>53</v>
       </c>
       <c r="B123" s="4" t="s">
@@ -7658,7 +7670,7 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="41" t="s">
+      <c r="A124" s="43" t="s">
         <v>53</v>
       </c>
       <c r="B124" s="4" t="s">
@@ -7696,7 +7708,7 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="41" t="s">
+      <c r="A125" s="43" t="s">
         <v>53</v>
       </c>
       <c r="B125" s="4" t="s">
@@ -7734,7 +7746,7 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="41" t="s">
+      <c r="A126" s="43" t="s">
         <v>54</v>
       </c>
       <c r="B126" s="4" t="s">
@@ -7752,7 +7764,7 @@
       <c r="L126" s="6"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="41" t="s">
+      <c r="A127" s="43" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -7770,7 +7782,7 @@
       <c r="L127" s="6"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="41" t="s">
+      <c r="A128" s="43" t="s">
         <v>54</v>
       </c>
       <c r="B128" s="4" t="s">
@@ -7788,7 +7800,7 @@
       <c r="L128" s="6"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="41" t="s">
+      <c r="A129" s="43" t="s">
         <v>54</v>
       </c>
       <c r="B129" s="4" t="s">
@@ -7808,7 +7820,7 @@
       <c r="L129" s="6"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="41" t="s">
+      <c r="A130" s="43" t="s">
         <v>55</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -7826,7 +7838,7 @@
       <c r="L130" s="6"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="41" t="s">
+      <c r="A131" s="43" t="s">
         <v>55</v>
       </c>
       <c r="B131" s="4" t="s">
@@ -7864,7 +7876,7 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="41" t="s">
+      <c r="A132" s="43" t="s">
         <v>55</v>
       </c>
       <c r="B132" s="4" t="s">
@@ -7902,7 +7914,7 @@
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="41" t="s">
+      <c r="A133" s="43" t="s">
         <v>55</v>
       </c>
       <c r="B133" s="4" t="s">
@@ -7940,7 +7952,7 @@
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="41" t="s">
+      <c r="A134" s="43" t="s">
         <v>55</v>
       </c>
       <c r="B134" s="4" t="s">
@@ -7978,7 +7990,7 @@
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="41" t="s">
+      <c r="A135" s="43" t="s">
         <v>56</v>
       </c>
       <c r="B135" s="4" t="s">
@@ -8016,7 +8028,7 @@
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="41" t="s">
+      <c r="A136" s="43" t="s">
         <v>56</v>
       </c>
       <c r="B136" s="4" t="s">
@@ -8054,7 +8066,7 @@
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="41" t="s">
+      <c r="A137" s="43" t="s">
         <v>57</v>
       </c>
       <c r="B137" s="4" t="s">
@@ -8092,7 +8104,7 @@
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="41" t="s">
+      <c r="A138" s="43" t="s">
         <v>57</v>
       </c>
       <c r="B138" s="4" t="s">
@@ -8130,7 +8142,7 @@
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="41" t="s">
+      <c r="A139" s="43" t="s">
         <v>57</v>
       </c>
       <c r="B139" s="4" t="s">
@@ -8168,7 +8180,7 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="41" t="s">
+      <c r="A140" s="43" t="s">
         <v>57</v>
       </c>
       <c r="B140" s="4" t="s">
@@ -8244,7 +8256,7 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="41" t="s">
+      <c r="A142" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B142" s="4" t="s">
@@ -8282,7 +8294,7 @@
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="41" t="s">
+      <c r="A143" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B143" s="4" t="s">
@@ -8320,7 +8332,7 @@
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="41" t="s">
+      <c r="A144" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B144" s="4" t="s">
@@ -8358,7 +8370,7 @@
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="41" t="s">
+      <c r="A145" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B145" s="4" t="s">
@@ -8386,7 +8398,7 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="41" t="s">
+      <c r="A146" s="43" t="s">
         <v>60</v>
       </c>
       <c r="B146" s="4" t="s">
@@ -8424,7 +8436,7 @@
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="41" t="s">
+      <c r="A147" s="43" t="s">
         <v>60</v>
       </c>
       <c r="B147" s="4" t="s">
@@ -8462,7 +8474,7 @@
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="41" t="s">
+      <c r="A148" s="43" t="s">
         <v>60</v>
       </c>
       <c r="B148" s="4" t="s">
@@ -8500,7 +8512,7 @@
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="41" t="s">
+      <c r="A149" s="43" t="s">
         <v>60</v>
       </c>
       <c r="B149" s="4" t="s">
@@ -8538,7 +8550,7 @@
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="41" t="s">
+      <c r="A150" s="43" t="s">
         <v>61</v>
       </c>
       <c r="B150" s="4" t="s">
@@ -8576,7 +8588,7 @@
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="41" t="s">
+      <c r="A151" s="43" t="s">
         <v>61</v>
       </c>
       <c r="B151" s="4" t="s">
@@ -8614,7 +8626,7 @@
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="41" t="s">
+      <c r="A152" s="43" t="s">
         <v>61</v>
       </c>
       <c r="B152" s="4" t="s">
@@ -8652,7 +8664,7 @@
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="41" t="s">
+      <c r="A153" s="43" t="s">
         <v>62</v>
       </c>
       <c r="B153" s="4" t="s">
@@ -8690,7 +8702,7 @@
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="41" t="s">
+      <c r="A154" s="43" t="s">
         <v>62</v>
       </c>
       <c r="B154" s="4" t="s">
@@ -8728,7 +8740,7 @@
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="41" t="s">
+      <c r="A155" s="43" t="s">
         <v>62</v>
       </c>
       <c r="B155" s="4" t="s">
@@ -8766,7 +8778,7 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="41" t="s">
+      <c r="A156" s="43" t="s">
         <v>62</v>
       </c>
       <c r="B156" s="4" t="s">
@@ -8804,7 +8816,7 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="41" t="s">
+      <c r="A157" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B157" s="4" t="s">
@@ -8830,7 +8842,7 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="41" t="s">
+      <c r="A158" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B158" s="4" t="s">
@@ -8856,7 +8868,7 @@
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="41" t="s">
+      <c r="A159" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B159" s="4" t="s">
@@ -8884,7 +8896,7 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="41" t="s">
+      <c r="A160" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B160" s="4" t="s">
@@ -8912,7 +8924,7 @@
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="41" t="s">
+      <c r="A161" s="43" t="s">
         <v>64</v>
       </c>
       <c r="B161" s="4" t="s">
@@ -8930,7 +8942,7 @@
       <c r="L161" s="6"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="41" t="s">
+      <c r="A162" s="43" t="s">
         <v>64</v>
       </c>
       <c r="B162" s="4" t="s">
@@ -8948,7 +8960,7 @@
       <c r="L162" s="6"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="41" t="s">
+      <c r="A163" s="43" t="s">
         <v>64</v>
       </c>
       <c r="B163" s="4" t="s">
@@ -8968,7 +8980,7 @@
       <c r="L163" s="6"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="41" t="s">
+      <c r="A164" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B164" s="4" t="s">
@@ -8996,7 +9008,7 @@
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="41" t="s">
+      <c r="A165" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B165" s="4" t="s">
@@ -9034,7 +9046,7 @@
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="41" t="s">
+      <c r="A166" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B166" s="4" t="s">
@@ -9072,7 +9084,7 @@
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="41" t="s">
+      <c r="A167" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B167" s="4" t="s">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="41" t="s">
+      <c r="A168" s="43" t="s">
         <v>66</v>
       </c>
       <c r="B168" s="4" t="s">
@@ -9128,7 +9140,7 @@
       <c r="L168" s="6"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="41" t="s">
+      <c r="A169" s="43" t="s">
         <v>66</v>
       </c>
       <c r="B169" s="4" t="s">
@@ -9166,7 +9178,7 @@
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="41" t="s">
+      <c r="A170" s="43" t="s">
         <v>66</v>
       </c>
       <c r="B170" s="4" t="s">
@@ -9204,7 +9216,7 @@
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="41" t="s">
+      <c r="A171" s="43" t="s">
         <v>66</v>
       </c>
       <c r="B171" s="4" t="s">
@@ -9242,7 +9254,7 @@
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="41" t="s">
+      <c r="A172" s="43" t="s">
         <v>66</v>
       </c>
       <c r="B172" s="4" t="s">
@@ -9280,7 +9292,7 @@
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="41" t="s">
+      <c r="A173" s="43" t="s">
         <v>67</v>
       </c>
       <c r="B173" s="4" t="s">
@@ -9318,7 +9330,7 @@
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="41" t="s">
+      <c r="A174" s="43" t="s">
         <v>67</v>
       </c>
       <c r="B174" s="4" t="s">
@@ -9336,7 +9348,7 @@
       <c r="L174" s="6"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="41" t="s">
+      <c r="A175" s="43" t="s">
         <v>67</v>
       </c>
       <c r="B175" s="4" t="s">
@@ -9354,7 +9366,7 @@
       <c r="L175" s="6"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="41" t="s">
+      <c r="A176" s="43" t="s">
         <v>68</v>
       </c>
       <c r="B176" s="4" t="s">
@@ -9392,7 +9404,7 @@
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="41" t="s">
+      <c r="A177" s="43" t="s">
         <v>68</v>
       </c>
       <c r="B177" s="4" t="s">
@@ -9424,7 +9436,7 @@
       <c r="L177" s="6"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="41" t="s">
+      <c r="A178" s="43" t="s">
         <v>68</v>
       </c>
       <c r="B178" s="4" t="s">
@@ -9462,7 +9474,7 @@
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="41" t="s">
+      <c r="A179" s="43" t="s">
         <v>69</v>
       </c>
       <c r="B179" s="4" t="s">
@@ -9500,7 +9512,7 @@
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="41" t="s">
+      <c r="A180" s="43" t="s">
         <v>69</v>
       </c>
       <c r="B180" s="4" t="s">
@@ -9526,7 +9538,7 @@
       <c r="L180" s="6"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="41" t="s">
+      <c r="A181" s="43" t="s">
         <v>69</v>
       </c>
       <c r="B181" s="4" t="s">
@@ -9564,7 +9576,7 @@
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="41" t="s">
+      <c r="A182" s="43" t="s">
         <v>70</v>
       </c>
       <c r="B182" s="4" t="s">
@@ -9582,7 +9594,7 @@
       <c r="L182" s="6"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="41" t="s">
+      <c r="A183" s="43" t="s">
         <v>70</v>
       </c>
       <c r="B183" s="4" t="s">
@@ -9600,7 +9612,7 @@
       <c r="L183" s="6"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="41" t="s">
+      <c r="A184" s="43" t="s">
         <v>70</v>
       </c>
       <c r="B184" s="4" t="s">
@@ -9618,7 +9630,7 @@
       <c r="L184" s="6"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="41" t="s">
+      <c r="A185" s="43" t="s">
         <v>70</v>
       </c>
       <c r="B185" s="4" t="s">
@@ -9636,7 +9648,7 @@
       <c r="L185" s="6"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" s="41" t="s">
+      <c r="A186" s="43" t="s">
         <v>70</v>
       </c>
       <c r="B186" s="4" t="s">
@@ -9654,7 +9666,7 @@
       <c r="L186" s="6"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="41" t="s">
+      <c r="A187" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B187" s="4" t="s">
@@ -9672,7 +9684,7 @@
       <c r="L187" s="6"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" s="41" t="s">
+      <c r="A188" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B188" s="4" t="s">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" s="41" t="s">
+      <c r="A189" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B189" s="4" t="s">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="41" t="s">
+      <c r="A190" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B190" s="4" t="s">
@@ -9774,7 +9786,7 @@
       <c r="L190" s="6"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="41" t="s">
+      <c r="A191" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B191" s="4" t="s">
@@ -9812,7 +9824,7 @@
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="41" t="s">
+      <c r="A192" s="43" t="s">
         <v>72</v>
       </c>
       <c r="B192" s="4" t="s">
@@ -9830,7 +9842,7 @@
       <c r="L192" s="6"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="41" t="s">
+      <c r="A193" s="43" t="s">
         <v>72</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -9868,7 +9880,7 @@
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" s="41" t="s">
+      <c r="A194" s="43" t="s">
         <v>72</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -9898,7 +9910,7 @@
       <c r="L194" s="6"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="41" t="s">
+      <c r="A195" s="43" t="s">
         <v>72</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -9936,7 +9948,7 @@
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="41" t="s">
+      <c r="A196" s="43" t="s">
         <v>73</v>
       </c>
       <c r="B196" s="4" t="s">
@@ -9974,7 +9986,7 @@
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="41" t="s">
+      <c r="A197" s="43" t="s">
         <v>73</v>
       </c>
       <c r="B197" s="4" t="s">
@@ -9992,7 +10004,7 @@
       <c r="L197" s="6"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="41" t="s">
+      <c r="A198" s="43" t="s">
         <v>73</v>
       </c>
       <c r="B198" s="4" t="s">
@@ -10030,7 +10042,7 @@
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="41" t="s">
+      <c r="A199" s="43" t="s">
         <v>74</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -10068,7 +10080,7 @@
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="41" t="s">
+      <c r="A200" s="43" t="s">
         <v>74</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -10106,7 +10118,7 @@
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="41" t="s">
+      <c r="A201" s="43" t="s">
         <v>74</v>
       </c>
       <c r="B201" s="4" t="s">
@@ -10144,7 +10156,7 @@
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="41" t="s">
+      <c r="A202" s="43" t="s">
         <v>74</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -10182,7 +10194,7 @@
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="41" t="s">
+      <c r="A203" s="43" t="s">
         <v>74</v>
       </c>
       <c r="B203" s="4" t="s">
@@ -14278,12 +14290,40 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="A123:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="A150:A152"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="A157:A160"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A70:A74"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
@@ -14296,40 +14336,12 @@
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="A62:A64"/>
     <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18568,7 +18580,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -18646,34 +18658,34 @@
         <v>140</v>
       </c>
       <c r="B3" s="37">
-        <v>24300000</v>
+        <v>243000000</v>
       </c>
       <c r="C3" s="37">
-        <v>26300000</v>
+        <v>263000000</v>
       </c>
       <c r="D3" s="37">
-        <v>26500000</v>
+        <v>265000000</v>
       </c>
       <c r="E3" s="37">
-        <v>25000000</v>
+        <v>250000000</v>
       </c>
       <c r="F3" s="37">
-        <v>24900000</v>
+        <v>249000000</v>
       </c>
       <c r="G3" s="37">
-        <v>24700000</v>
+        <v>247000000</v>
       </c>
       <c r="H3" s="37">
-        <v>25000000</v>
+        <v>250000000</v>
       </c>
       <c r="I3" s="37">
-        <v>24800000</v>
+        <v>248000000</v>
       </c>
       <c r="J3" s="37">
-        <v>25100000</v>
+        <v>251000000</v>
       </c>
       <c r="K3" s="37">
-        <v>25400000</v>
+        <v>254000000</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -18856,34 +18868,34 @@
         <v>116</v>
       </c>
       <c r="B9" s="37">
-        <v>173300000</v>
+        <v>1733000000</v>
       </c>
       <c r="C9" s="37">
-        <v>192100000</v>
+        <v>1921000000</v>
       </c>
       <c r="D9" s="37">
-        <v>207900000</v>
+        <v>2079000000</v>
       </c>
       <c r="E9" s="37">
-        <v>239100000</v>
+        <v>2391000000</v>
       </c>
       <c r="F9" s="37">
-        <v>260300000</v>
+        <v>2603000000</v>
       </c>
       <c r="G9" s="37">
-        <v>237100000</v>
+        <v>2371000000</v>
       </c>
       <c r="H9" s="37">
-        <v>225100000</v>
+        <v>2251000000</v>
       </c>
       <c r="I9" s="37">
-        <v>219800000</v>
+        <v>2198000000</v>
       </c>
       <c r="J9" s="37">
-        <v>215500000</v>
+        <v>2155000000</v>
       </c>
       <c r="K9" s="37">
-        <v>217800000</v>
+        <v>2178000000</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -18926,43 +18938,33 @@
         <v>147</v>
       </c>
       <c r="B11" s="25">
-        <f>B20*17</f>
         <v>1030200000</v>
       </c>
       <c r="C11" s="25">
-        <f t="shared" ref="C11:K11" si="0">C20*17</f>
         <v>1268200000</v>
       </c>
       <c r="D11" s="25">
-        <f t="shared" si="0"/>
         <v>1411000000</v>
       </c>
       <c r="E11" s="25">
-        <f t="shared" si="0"/>
         <v>1382100000</v>
       </c>
       <c r="F11" s="25">
-        <f t="shared" si="0"/>
         <v>1378700000</v>
       </c>
       <c r="G11" s="25">
-        <f t="shared" si="0"/>
         <v>1356600000</v>
       </c>
       <c r="H11" s="25">
-        <f t="shared" si="0"/>
         <v>1378700000</v>
       </c>
       <c r="I11" s="25">
-        <f t="shared" si="0"/>
         <v>1358300000</v>
       </c>
       <c r="J11" s="25">
-        <f t="shared" si="0"/>
         <v>1380400000</v>
       </c>
       <c r="K11" s="25">
-        <f t="shared" si="0"/>
         <v>1399100000</v>
       </c>
     </row>
@@ -19076,34 +19078,34 @@
         <v>151</v>
       </c>
       <c r="B15" s="37">
-        <v>104600000</v>
+        <v>1046000000</v>
       </c>
       <c r="C15" s="37">
-        <v>122100000</v>
+        <v>1221000000</v>
       </c>
       <c r="D15" s="37">
-        <v>131700000</v>
+        <v>1317000000</v>
       </c>
       <c r="E15" s="37">
-        <v>128600000</v>
+        <v>1286000000</v>
       </c>
       <c r="F15" s="37">
-        <v>128700000</v>
+        <v>1287000000</v>
       </c>
       <c r="G15" s="37">
-        <v>125200000</v>
+        <v>1252000000</v>
       </c>
       <c r="H15" s="37">
-        <v>127600000</v>
+        <v>1276000000</v>
       </c>
       <c r="I15" s="37">
-        <v>126000000</v>
+        <v>1260000000</v>
       </c>
       <c r="J15" s="37">
-        <v>127400000</v>
+        <v>1274000000</v>
       </c>
       <c r="K15" s="37">
-        <v>128200000</v>
+        <v>1282000000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -19146,34 +19148,34 @@
         <v>153</v>
       </c>
       <c r="B17" s="25">
-        <v>500000</v>
+        <v>50000000</v>
       </c>
       <c r="C17" s="25">
-        <v>500000</v>
+        <v>50000000</v>
       </c>
       <c r="D17" s="25">
-        <v>700000</v>
+        <v>70000000</v>
       </c>
       <c r="E17" s="25">
-        <v>2000000</v>
+        <v>200000000</v>
       </c>
       <c r="F17" s="25">
-        <v>2500000</v>
+        <v>250000000</v>
       </c>
       <c r="G17" s="25">
-        <v>1800000</v>
+        <v>180000000</v>
       </c>
       <c r="H17" s="25">
-        <v>1200000</v>
+        <v>120000000</v>
       </c>
       <c r="I17" s="25">
-        <v>1200000</v>
+        <v>120000000</v>
       </c>
       <c r="J17" s="25">
-        <v>900000</v>
+        <v>90000000</v>
       </c>
       <c r="K17" s="25">
-        <v>1000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -19181,34 +19183,34 @@
         <v>156</v>
       </c>
       <c r="B18" s="37">
-        <v>5800000</v>
+        <v>58000000</v>
       </c>
       <c r="C18" s="37">
-        <v>6700000</v>
+        <v>67000000</v>
       </c>
       <c r="D18" s="37">
-        <v>7500000</v>
+        <v>75000000</v>
       </c>
       <c r="E18" s="37">
-        <v>7400000</v>
+        <v>74000000</v>
       </c>
       <c r="F18" s="37">
-        <v>7900000</v>
+        <v>79000000</v>
       </c>
       <c r="G18" s="37">
-        <v>7900000</v>
+        <v>79000000</v>
       </c>
       <c r="H18" s="37">
-        <v>8000000</v>
+        <v>80000000</v>
       </c>
       <c r="I18" s="37">
-        <v>7800000</v>
+        <v>78000000</v>
       </c>
       <c r="J18" s="37">
-        <v>7800000</v>
+        <v>78000000</v>
       </c>
       <c r="K18" s="37">
-        <v>7900000</v>
+        <v>79000000</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -19224,63 +19226,43 @@
       <c r="K19" s="25"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="37">
-        <v>60600000</v>
-      </c>
-      <c r="C20" s="37">
-        <v>74600000</v>
-      </c>
-      <c r="D20" s="37">
-        <v>83000000</v>
-      </c>
-      <c r="E20" s="37">
-        <v>81300000</v>
-      </c>
-      <c r="F20" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="G20" s="37">
-        <v>79800000</v>
-      </c>
-      <c r="H20" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="I20" s="37">
-        <v>79900000</v>
-      </c>
-      <c r="J20" s="37">
-        <v>81200000</v>
-      </c>
-      <c r="K20" s="37">
-        <v>82300000</v>
-      </c>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
+      <c r="B23" s="37"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="40"/>

--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77F21EE-8157-4E23-95E5-4D730731A823}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{391AB4AD-8E06-448B-8305-29E04006C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4C4965B-25D1-4585-AEAE-6EF4D9F6A7EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Medium_Capacity" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Medium_Capacity!$A$1:$K$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Prod_capacity_agg!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">total_capacity_calcs!$A$229:$L$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'vaccine-producer list'!$A$1:$R$54</definedName>
@@ -29,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1810,7 +1811,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B95A2301-B56D-4CF8-964C-AEC6E5E61117}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M3:W22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -14290,16 +14291,36 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A70:A74"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A161:A163"/>
     <mergeCell ref="A120:A122"/>
     <mergeCell ref="A123:A125"/>
@@ -14312,36 +14333,16 @@
     <mergeCell ref="A150:A152"/>
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A70:A74"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18580,10 +18581,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -19040,177 +19038,177 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B14" s="37">
-        <v>116600000</v>
+        <v>58000000</v>
       </c>
       <c r="C14" s="37">
-        <v>129900000</v>
+        <v>67000000</v>
       </c>
       <c r="D14" s="37">
-        <v>128200000</v>
+        <v>75000000</v>
       </c>
       <c r="E14" s="37">
-        <v>123000000</v>
+        <v>74000000</v>
       </c>
       <c r="F14" s="37">
-        <v>123100000</v>
+        <v>79000000</v>
       </c>
       <c r="G14" s="37">
-        <v>120400000</v>
+        <v>79000000</v>
       </c>
       <c r="H14" s="37">
-        <v>121900000</v>
+        <v>80000000</v>
       </c>
       <c r="I14" s="37">
-        <v>121000000</v>
+        <v>78000000</v>
       </c>
       <c r="J14" s="37">
-        <v>122400000</v>
+        <v>78000000</v>
       </c>
       <c r="K14" s="37">
-        <v>123300000</v>
+        <v>79000000</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B15" s="37">
-        <v>1046000000</v>
+        <v>116600000</v>
       </c>
       <c r="C15" s="37">
-        <v>1221000000</v>
+        <v>129900000</v>
       </c>
       <c r="D15" s="37">
-        <v>1317000000</v>
+        <v>128200000</v>
       </c>
       <c r="E15" s="37">
-        <v>1286000000</v>
+        <v>123000000</v>
       </c>
       <c r="F15" s="37">
-        <v>1287000000</v>
+        <v>123100000</v>
       </c>
       <c r="G15" s="37">
-        <v>1252000000</v>
+        <v>120400000</v>
       </c>
       <c r="H15" s="37">
-        <v>1276000000</v>
+        <v>121900000</v>
       </c>
       <c r="I15" s="37">
-        <v>1260000000</v>
+        <v>121000000</v>
       </c>
       <c r="J15" s="37">
-        <v>1274000000</v>
+        <v>122400000</v>
       </c>
       <c r="K15" s="37">
-        <v>1282000000</v>
+        <v>123300000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16">
-        <v>1074100000</v>
-      </c>
-      <c r="C16">
-        <v>1109700000</v>
-      </c>
-      <c r="D16">
-        <v>1160000000</v>
-      </c>
-      <c r="E16">
-        <v>1115800000</v>
-      </c>
-      <c r="F16">
-        <v>1141600000</v>
-      </c>
-      <c r="G16">
-        <v>1191500000</v>
-      </c>
-      <c r="H16">
-        <v>1120400000</v>
-      </c>
-      <c r="I16">
-        <v>1192500000</v>
-      </c>
-      <c r="J16">
-        <v>1139200000</v>
-      </c>
-      <c r="K16">
-        <v>1169600000</v>
+        <v>151</v>
+      </c>
+      <c r="B16" s="37">
+        <v>1046000000</v>
+      </c>
+      <c r="C16" s="37">
+        <v>1221000000</v>
+      </c>
+      <c r="D16" s="37">
+        <v>1317000000</v>
+      </c>
+      <c r="E16" s="37">
+        <v>1286000000</v>
+      </c>
+      <c r="F16" s="37">
+        <v>1287000000</v>
+      </c>
+      <c r="G16" s="37">
+        <v>1252000000</v>
+      </c>
+      <c r="H16" s="37">
+        <v>1276000000</v>
+      </c>
+      <c r="I16" s="37">
+        <v>1260000000</v>
+      </c>
+      <c r="J16" s="37">
+        <v>1274000000</v>
+      </c>
+      <c r="K16" s="37">
+        <v>1282000000</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B17" s="25">
-        <v>50000000</v>
-      </c>
-      <c r="C17" s="25">
-        <v>50000000</v>
-      </c>
-      <c r="D17" s="25">
-        <v>70000000</v>
-      </c>
-      <c r="E17" s="25">
-        <v>200000000</v>
-      </c>
-      <c r="F17" s="25">
-        <v>250000000</v>
-      </c>
-      <c r="G17" s="25">
-        <v>180000000</v>
-      </c>
-      <c r="H17" s="25">
-        <v>120000000</v>
-      </c>
-      <c r="I17" s="25">
-        <v>120000000</v>
-      </c>
-      <c r="J17" s="25">
-        <v>90000000</v>
-      </c>
-      <c r="K17" s="25">
-        <v>100000000</v>
+        <v>152</v>
+      </c>
+      <c r="B17">
+        <v>1074100000</v>
+      </c>
+      <c r="C17">
+        <v>1109700000</v>
+      </c>
+      <c r="D17">
+        <v>1160000000</v>
+      </c>
+      <c r="E17">
+        <v>1115800000</v>
+      </c>
+      <c r="F17">
+        <v>1141600000</v>
+      </c>
+      <c r="G17">
+        <v>1191500000</v>
+      </c>
+      <c r="H17">
+        <v>1120400000</v>
+      </c>
+      <c r="I17">
+        <v>1192500000</v>
+      </c>
+      <c r="J17">
+        <v>1139200000</v>
+      </c>
+      <c r="K17">
+        <v>1169600000</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="37">
-        <v>58000000</v>
-      </c>
-      <c r="C18" s="37">
-        <v>67000000</v>
-      </c>
-      <c r="D18" s="37">
-        <v>75000000</v>
-      </c>
-      <c r="E18" s="37">
-        <v>74000000</v>
-      </c>
-      <c r="F18" s="37">
-        <v>79000000</v>
-      </c>
-      <c r="G18" s="37">
-        <v>79000000</v>
-      </c>
-      <c r="H18" s="37">
-        <v>80000000</v>
-      </c>
-      <c r="I18" s="37">
-        <v>78000000</v>
-      </c>
-      <c r="J18" s="37">
-        <v>78000000</v>
-      </c>
-      <c r="K18" s="37">
-        <v>79000000</v>
+        <v>153</v>
+      </c>
+      <c r="B18" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="C18" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="D18" s="25">
+        <v>70000000</v>
+      </c>
+      <c r="E18" s="25">
+        <v>200000000</v>
+      </c>
+      <c r="F18" s="25">
+        <v>250000000</v>
+      </c>
+      <c r="G18" s="25">
+        <v>180000000</v>
+      </c>
+      <c r="H18" s="25">
+        <v>120000000</v>
+      </c>
+      <c r="I18" s="25">
+        <v>120000000</v>
+      </c>
+      <c r="J18" s="25">
+        <v>90000000</v>
+      </c>
+      <c r="K18" s="25">
+        <v>100000000</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -19526,6 +19524,11 @@
       <c r="K44" s="25"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K18" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
+      <sortCondition ref="A1:A18"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49F25625-B636-41FB-B8B0-30066A052327}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E313997-B984-44EE-A796-E33C8848E5C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
@@ -957,7 +957,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1045,6 +1045,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -19467,7 +19470,9 @@
       <c r="K20" s="43"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="43"/>
+      <c r="B21" s="43">
+        <v>43365104</v>
+      </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="25"/>
@@ -19479,7 +19484,9 @@
       <c r="K21" s="25"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="42"/>
+      <c r="B22" s="48">
+        <v>61220888</v>
+      </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="25"/>
@@ -19491,7 +19498,10 @@
       <c r="K22" s="25"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
+      <c r="B23" s="25">
+        <f>B22+B21</f>
+        <v>104585992</v>
+      </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="40"/>
@@ -19503,7 +19513,10 @@
       <c r="K23" s="25"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="25"/>
+      <c r="B24" s="25">
+        <f>B16-B23</f>
+        <v>14008</v>
+      </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>

--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/35 years - bundles as antigen (ONGOING)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A464C6C2-7F1F-462F-B25F-B21FBF903C6F}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8122D5-EDF5-4662-BD7C-12F76566BD82}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="GAVI_countries" localSheetId="0">#REF!</definedName>
     <definedName name="GAVI_countries">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
@@ -1957,9 +1957,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1997,7 +1997,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2103,7 +2103,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2245,7 +2245,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10255,44 +10255,44 @@
         <v>110</v>
       </c>
       <c r="C207" s="8">
-        <f t="shared" ref="C207:L207" si="0">SUM(C96+C136+C142)</f>
-        <v>14777182.228013158</v>
+        <f>SUM(C92+C93)</f>
+        <v>62765698.894231752</v>
       </c>
       <c r="D207" s="8">
+        <f>SUM(D92+D93)</f>
+        <v>104605466.70853016</v>
+      </c>
+      <c r="E207" s="8">
+        <f t="shared" ref="E207:L207" si="0">SUM(E92+E93)</f>
+        <v>90210217.166338012</v>
+      </c>
+      <c r="F207" s="8">
         <f t="shared" si="0"/>
-        <v>37949221.241086259</v>
-      </c>
-      <c r="E207" s="8">
-        <f t="shared" si="0"/>
-        <v>17547795.842103511</v>
-      </c>
-      <c r="F207" s="8">
-        <f>SUM(F96+F136+F142)</f>
-        <v>21303104.688398462</v>
+        <v>69199357.094551593</v>
       </c>
       <c r="G207" s="8">
         <f t="shared" si="0"/>
-        <v>22347712.522483818</v>
+        <v>86221766.026547611</v>
       </c>
       <c r="H207" s="8">
         <f t="shared" si="0"/>
-        <v>20946969.555763159</v>
+        <v>20943493.617039636</v>
       </c>
       <c r="I207" s="8">
         <f t="shared" si="0"/>
-        <v>19884769.205236845</v>
+        <v>12437570.342499999</v>
       </c>
       <c r="J207" s="8">
         <f t="shared" si="0"/>
-        <v>20824130.238903508</v>
+        <v>899709.40166666661</v>
       </c>
       <c r="K207" s="8">
         <f t="shared" si="0"/>
-        <v>21884645.404903509</v>
+        <v>923478.11952380964</v>
       </c>
       <c r="L207" s="8">
         <f t="shared" si="0"/>
-        <v>22913488.673833333</v>
+        <v>951559.21642857138</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -10303,11 +10303,11 @@
         <v>110</v>
       </c>
       <c r="C208" s="8">
-        <f t="shared" ref="C208:L208" si="1">C138+C139</f>
+        <f>C138+C139</f>
         <v>331279149.4189564</v>
       </c>
       <c r="D208" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C208:L208" si="1">D138+D139</f>
         <v>227385022.03396031</v>
       </c>
       <c r="E208" s="8">
@@ -10351,11 +10351,11 @@
         <v>110</v>
       </c>
       <c r="C209" s="8">
-        <f t="shared" ref="C209:L209" si="2">C132+C133</f>
+        <f>C132+C133</f>
         <v>26052155.976207186</v>
       </c>
       <c r="D209" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C209:L209" si="2">D132+D133</f>
         <v>26626398.679317039</v>
       </c>
       <c r="E209" s="8">
@@ -11119,43 +11119,43 @@
       </c>
       <c r="C230" s="19">
         <f t="shared" ref="C230:L230" si="17">C207*$B226</f>
-        <v>13299464.005211843</v>
+        <v>56489129.004808575</v>
       </c>
       <c r="D230" s="19">
         <f t="shared" si="17"/>
-        <v>34154299.116977632</v>
+        <v>94144920.037677139</v>
       </c>
       <c r="E230" s="19">
         <f t="shared" si="17"/>
-        <v>15793016.25789316</v>
+        <v>81189195.449704215</v>
       </c>
       <c r="F230" s="19">
         <f t="shared" si="17"/>
-        <v>19172794.219558615</v>
+        <v>62279421.385096438</v>
       </c>
       <c r="G230" s="19">
         <f t="shared" si="17"/>
-        <v>20112941.270235438</v>
+        <v>77599589.423892856</v>
       </c>
       <c r="H230" s="19">
         <f t="shared" si="17"/>
-        <v>18852272.600186843</v>
+        <v>18849144.255335674</v>
       </c>
       <c r="I230" s="19">
         <f t="shared" si="17"/>
-        <v>17896292.28471316</v>
+        <v>11193813.308249999</v>
       </c>
       <c r="J230" s="19">
         <f t="shared" si="17"/>
-        <v>18741717.215013158</v>
+        <v>809738.46149999998</v>
       </c>
       <c r="K230" s="19">
         <f t="shared" si="17"/>
-        <v>19696180.864413157</v>
+        <v>831130.30757142871</v>
       </c>
       <c r="L230" s="19">
         <f t="shared" si="17"/>
-        <v>20622139.806450002</v>
+        <v>856403.29478571424</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -11167,43 +11167,43 @@
       </c>
       <c r="C231" s="2">
         <f t="shared" ref="C231:L231" si="18">$B$231*C230</f>
-        <v>10881379.640627872</v>
+        <v>46218378.276661567</v>
       </c>
       <c r="D231" s="2">
         <f t="shared" si="18"/>
-        <v>27944426.550254427</v>
+        <v>77027661.849008575</v>
       </c>
       <c r="E231" s="2">
         <f t="shared" si="18"/>
-        <v>12921558.75645804</v>
+        <v>66427523.549757995</v>
       </c>
       <c r="F231" s="2">
         <f t="shared" si="18"/>
-        <v>15686831.634184323</v>
+        <v>50955890.224169813</v>
       </c>
       <c r="G231" s="2">
         <f t="shared" si="18"/>
-        <v>16456042.857465358</v>
+        <v>63490573.165003248</v>
       </c>
       <c r="H231" s="2">
         <f t="shared" si="18"/>
-        <v>15424586.672880145</v>
+        <v>15422027.118001916</v>
       </c>
       <c r="I231" s="2">
         <f t="shared" si="18"/>
-        <v>14642420.96021986</v>
+        <v>9158574.5249318182</v>
       </c>
       <c r="J231" s="2">
         <f t="shared" si="18"/>
-        <v>15334132.266828949</v>
+        <v>662513.28668181819</v>
       </c>
       <c r="K231" s="2">
         <f t="shared" si="18"/>
-        <v>16115057.070883494</v>
+        <v>680015.70619480533</v>
       </c>
       <c r="L231" s="2">
         <f t="shared" si="18"/>
-        <v>16872659.841640912</v>
+        <v>700693.60482467536</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -11215,43 +11215,43 @@
       </c>
       <c r="C232" s="2">
         <f t="shared" ref="C232:L232" si="19">$B$232*C230</f>
-        <v>2418084.364583971</v>
+        <v>10270750.728147011</v>
       </c>
       <c r="D232" s="2">
         <f t="shared" si="19"/>
-        <v>6209872.5667232042</v>
+        <v>17117258.188668568</v>
       </c>
       <c r="E232" s="2">
         <f t="shared" si="19"/>
-        <v>2871457.5014351192</v>
+        <v>14761671.899946216</v>
       </c>
       <c r="F232" s="2">
         <f t="shared" si="19"/>
-        <v>3485962.5853742929</v>
+        <v>11323531.160926621</v>
       </c>
       <c r="G232" s="2">
         <f t="shared" si="19"/>
-        <v>3656898.4127700785</v>
+        <v>14109016.258889606</v>
       </c>
       <c r="H232" s="2">
         <f t="shared" si="19"/>
-        <v>3427685.9273066977</v>
+        <v>3427117.1373337577</v>
       </c>
       <c r="I232" s="2">
         <f t="shared" si="19"/>
-        <v>3253871.3244933011</v>
+        <v>2035238.7833181811</v>
       </c>
       <c r="J232" s="2">
         <f t="shared" si="19"/>
-        <v>3407584.9481842094</v>
+        <v>147225.17481818178</v>
       </c>
       <c r="K232" s="2">
         <f t="shared" si="19"/>
-        <v>3581123.7935296642</v>
+        <v>151114.60137662335</v>
       </c>
       <c r="L232" s="2">
         <f t="shared" si="19"/>
-        <v>3749479.9648090904</v>
+        <v>155709.68996103891</v>
       </c>
     </row>
     <row r="233" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -14270,12 +14270,40 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="A123:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="A150:A152"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="A157:A160"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A70:A74"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
@@ -14288,40 +14316,12 @@
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="A62:A64"/>
     <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\L-shaped method\Using_deterministic_model_from_IISE_paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8122D5-EDF5-4662-BD7C-12F76566BD82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC75AC5-5DFF-42F9-8F6A-B58AA24898A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -18,10 +18,9 @@
     <sheet name="Prod_capacity_agg" sheetId="9" r:id="rId3"/>
     <sheet name="Producers_short_name" sheetId="5" r:id="rId4"/>
     <sheet name="Medium_Capacity" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Medium_Capacity!$A$2:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Medium_Capacity!$A$1:$K$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Prod_capacity_agg!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">total_capacity_calcs!$A$229:$L$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'vaccine-producer list'!$A$1:$R$54</definedName>
@@ -29,9 +28,9 @@
     <definedName name="GAVI_countries" localSheetId="0">#REF!</definedName>
     <definedName name="GAVI_countries">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -170,8 +169,26 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={C1098999-8042-465E-9ACB-457F7828CEE0}</author>
+  </authors>
+  <commentList>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{C1098999-8042-465E-9ACB-457F7828CEE0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nigerian company, added for sensitivity. Numbers are synthetic, and represent possible scenario near the end of the decade</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="171">
   <si>
     <t>Vaccine</t>
   </si>
@@ -653,6 +670,9 @@
     <t>"Pfizer"</t>
   </si>
   <si>
+    <t>"Innovative_Biotech"</t>
+  </si>
+  <si>
     <t>Sum of 1</t>
   </si>
   <si>
@@ -681,15 +701,6 @@
   </si>
   <si>
     <t>Sum of 10</t>
-  </si>
-  <si>
-    <t>Producer X</t>
-  </si>
-  <si>
-    <t>"Producer_X"</t>
-  </si>
-  <si>
-    <t>CO X</t>
   </si>
 </sst>
 </file>
@@ -1005,8 +1016,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2295,17 +2308,25 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A20" dT="2023-11-02T14:14:51.18" personId="{E6293415-C8D6-4C48-A35A-5D150AA40776}" id="{C1098999-8042-465E-9ACB-457F7828CEE0}">
+    <text>Nigerian company, added for sensitivity. Numbers are synthetic, and represent possible scenario near the end of the decade</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3694F37-B2B5-4F9D-9ACD-67519624FADB}">
   <dimension ref="A1:T54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="91.140625" customWidth="1"/>
-    <col min="2" max="18" width="15.7109375" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="91.109375" customWidth="1"/>
+    <col min="2" max="18" width="15.6640625" customWidth="1"/>
+    <col min="20" max="20" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2364,10 +2385,10 @@
         <v>156</v>
       </c>
       <c r="T1" s="33" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
@@ -2395,7 +2416,7 @@
       <c r="S2" s="34"/>
       <c r="T2" s="34"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>92</v>
       </c>
@@ -2423,7 +2444,7 @@
       <c r="S3" s="34"/>
       <c r="T3" s="34"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>93</v>
       </c>
@@ -2451,7 +2472,7 @@
       <c r="S4" s="34"/>
       <c r="T4" s="34"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>94</v>
       </c>
@@ -2481,7 +2502,7 @@
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>95</v>
       </c>
@@ -2511,7 +2532,7 @@
       <c r="S6" s="34"/>
       <c r="T6" s="34"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>96</v>
       </c>
@@ -2541,7 +2562,7 @@
       <c r="S7" s="34"/>
       <c r="T7" s="34"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>157</v>
       </c>
@@ -2575,7 +2596,7 @@
       <c r="S8" s="34"/>
       <c r="T8" s="34"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>97</v>
       </c>
@@ -2603,7 +2624,7 @@
       <c r="S9" s="34"/>
       <c r="T9" s="34"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>98</v>
       </c>
@@ -2629,7 +2650,7 @@
       <c r="S10" s="34"/>
       <c r="T10" s="34"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>99</v>
       </c>
@@ -2663,7 +2684,7 @@
       <c r="S11" s="34"/>
       <c r="T11" s="34"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>100</v>
       </c>
@@ -2689,7 +2710,7 @@
       <c r="S12" s="34"/>
       <c r="T12" s="34"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>101</v>
       </c>
@@ -2721,7 +2742,7 @@
       <c r="S13" s="34"/>
       <c r="T13" s="34"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>102</v>
       </c>
@@ -2761,7 +2782,7 @@
       <c r="S14" s="34"/>
       <c r="T14" s="34"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>103</v>
       </c>
@@ -2793,7 +2814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>104</v>
       </c>
@@ -2821,7 +2842,7 @@
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>105</v>
       </c>
@@ -2851,7 +2872,7 @@
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>158</v>
       </c>
@@ -2881,7 +2902,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>155</v>
       </c>
@@ -2911,7 +2932,7 @@
       </c>
       <c r="T19" s="10"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2931,7 +2952,7 @@
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2950,7 +2971,7 @@
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2969,7 +2990,7 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -2988,7 +3009,7 @@
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3007,7 +3028,7 @@
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -3026,7 +3047,7 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -3045,7 +3066,7 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -3064,7 +3085,7 @@
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -3083,7 +3104,7 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3102,7 +3123,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -3121,7 +3142,7 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3140,7 +3161,7 @@
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3159,7 +3180,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3178,7 +3199,7 @@
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3197,7 +3218,7 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3216,7 +3237,7 @@
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3235,7 +3256,7 @@
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3254,7 +3275,7 @@
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3273,7 +3294,7 @@
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3292,7 +3313,7 @@
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3311,7 +3332,7 @@
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3330,7 +3351,7 @@
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3349,7 +3370,7 @@
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3368,7 +3389,7 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3387,7 +3408,7 @@
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3406,7 +3427,7 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3425,7 +3446,7 @@
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3444,7 +3465,7 @@
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3463,7 +3484,7 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3482,7 +3503,7 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3501,7 +3522,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -3520,7 +3541,7 @@
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -3539,7 +3560,7 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3558,7 +3579,7 @@
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3609,17 +3630,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7054496A-AF4B-4EC1-B368-49C550220A1C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L301"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="94.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="12" width="18" style="2" customWidth="1"/>
     <col min="13" max="13" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3657,7 +3678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
@@ -3675,7 +3696,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="43" t="s">
         <v>12</v>
       </c>
@@ -3713,7 +3734,7 @@
         <v>26819200.996155463</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
         <v>12</v>
       </c>
@@ -3751,7 +3772,7 @@
         <v>56018232.597976193</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
         <v>12</v>
       </c>
@@ -3789,7 +3810,7 @@
         <v>170565705.92964286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="43" t="s">
         <v>12</v>
       </c>
@@ -3827,7 +3848,7 @@
         <v>79877180.657261893</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
         <v>18</v>
       </c>
@@ -3857,7 +3878,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
         <v>18</v>
       </c>
@@ -3887,7 +3908,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
         <v>18</v>
       </c>
@@ -3917,7 +3938,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
         <v>18</v>
       </c>
@@ -3947,7 +3968,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="43" t="s">
         <v>19</v>
       </c>
@@ -3985,7 +4006,7 @@
         <v>1403270410.0475006</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="43" t="s">
         <v>19</v>
       </c>
@@ -4023,7 +4044,7 @@
         <v>43232783.299999997</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
         <v>19</v>
       </c>
@@ -4061,7 +4082,7 @@
         <v>789204932.27500033</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="43" t="s">
         <v>19</v>
       </c>
@@ -4099,7 +4120,7 @@
         <v>500814543.58749998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -4117,7 +4138,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -4135,7 +4156,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="43" t="s">
         <v>22</v>
       </c>
@@ -4153,7 +4174,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
         <v>22</v>
       </c>
@@ -4191,7 +4212,7 @@
         <v>12788293.736842105</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="43" t="s">
         <v>22</v>
       </c>
@@ -4229,7 +4250,7 @@
         <v>863986.71500000008</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
         <v>22</v>
       </c>
@@ -4267,7 +4288,7 @@
         <v>5370201.9115789467</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
         <v>22</v>
       </c>
@@ -4305,7 +4326,7 @@
         <v>4313357.7878842624</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
         <v>23</v>
       </c>
@@ -4323,7 +4344,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
         <v>23</v>
       </c>
@@ -4361,7 +4382,7 @@
         <v>44326790.909789473</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
         <v>23</v>
       </c>
@@ -4379,7 +4400,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="43" t="s">
         <v>23</v>
       </c>
@@ -4409,7 +4430,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -4447,7 +4468,7 @@
         <v>430931.20894736843</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -4465,7 +4486,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
         <v>25</v>
       </c>
@@ -4503,7 +4524,7 @@
         <v>24359.106315789475</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
         <v>25</v>
       </c>
@@ -4533,7 +4554,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="43" t="s">
         <v>25</v>
       </c>
@@ -4559,7 +4580,7 @@
         <v>29653.105263157893</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="43" t="s">
         <v>26</v>
       </c>
@@ -4597,7 +4618,7 @@
         <v>22700002.013999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
         <v>26</v>
       </c>
@@ -4623,7 +4644,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
         <v>26</v>
       </c>
@@ -4661,7 +4682,7 @@
         <v>9708542.1121710539</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
         <v>27</v>
       </c>
@@ -4699,7 +4720,7 @@
         <v>2385352.0408421056</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
@@ -4729,7 +4750,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="43" t="s">
         <v>27</v>
       </c>
@@ -4755,7 +4776,7 @@
         <v>6987.9032894736847</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>28</v>
       </c>
@@ -4793,7 +4814,7 @@
         <v>3753257.1406578948</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
         <v>28</v>
       </c>
@@ -4819,7 +4840,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="43" t="s">
         <v>29</v>
       </c>
@@ -4857,7 +4878,7 @@
         <v>17711618.430631582</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="43" t="s">
         <v>29</v>
       </c>
@@ -4883,7 +4904,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="43" t="s">
         <v>29</v>
       </c>
@@ -4921,7 +4942,7 @@
         <v>8274488.3427631576</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="43" t="s">
         <v>30</v>
       </c>
@@ -4959,7 +4980,7 @@
         <v>12708293.497763159</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="43" t="s">
         <v>30</v>
       </c>
@@ -4977,7 +4998,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="43" t="s">
         <v>30</v>
       </c>
@@ -5015,7 +5036,7 @@
         <v>129709.70407894738</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="43" t="s">
         <v>31</v>
       </c>
@@ -5033,7 +5054,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="43" t="s">
         <v>31</v>
       </c>
@@ -5071,7 +5092,7 @@
         <v>4366498.504999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="43" t="s">
         <v>31</v>
       </c>
@@ -5109,7 +5130,7 @@
         <v>924903.77499999991</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="43" t="s">
         <v>31</v>
       </c>
@@ -5147,7 +5168,7 @@
         <v>56671594.19749999</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="43" t="s">
         <v>31</v>
       </c>
@@ -5185,7 +5206,7 @@
         <v>28451376.886823118</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="43" t="s">
         <v>32</v>
       </c>
@@ -5203,7 +5224,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="43" t="s">
         <v>32</v>
       </c>
@@ -5221,7 +5242,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="43" t="s">
         <v>32</v>
       </c>
@@ -5239,7 +5260,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="43" t="s">
         <v>32</v>
       </c>
@@ -5277,7 +5298,7 @@
         <v>1371371.7111111111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="43" t="s">
         <v>33</v>
       </c>
@@ -5315,7 +5336,7 @@
         <v>4588112.7602708973</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
         <v>33</v>
       </c>
@@ -5353,7 +5374,7 @@
         <v>68258991.188157901</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
         <v>33</v>
       </c>
@@ -5391,7 +5412,7 @@
         <v>202310628.16776317</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="43" t="s">
         <v>33</v>
       </c>
@@ -5429,7 +5450,7 @@
         <v>61534344.793815792</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="43" t="s">
         <v>34</v>
       </c>
@@ -5467,7 +5488,7 @@
         <v>99151.439999999988</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="43" t="s">
         <v>34</v>
       </c>
@@ -5505,7 +5526,7 @@
         <v>3781590.8850000007</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="43" t="s">
         <v>34</v>
       </c>
@@ -5543,7 +5564,7 @@
         <v>2364272.5157894739</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="43" t="s">
         <v>34</v>
       </c>
@@ -5563,7 +5584,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="43" t="s">
         <v>35</v>
       </c>
@@ -5601,7 +5622,7 @@
         <v>42709218.048947372</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -5639,7 +5660,7 @@
         <v>585519.70234210533</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="43" t="s">
         <v>35</v>
       </c>
@@ -5677,7 +5698,7 @@
         <v>6391844.9436842091</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="43" t="s">
         <v>36</v>
       </c>
@@ -5695,7 +5716,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="43" t="s">
         <v>36</v>
       </c>
@@ -5733,7 +5754,7 @@
         <v>71135570.336828187</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="43" t="s">
         <v>36</v>
       </c>
@@ -5771,7 +5792,7 @@
         <v>8918362.7869736832</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="43" t="s">
         <v>36</v>
       </c>
@@ -5809,7 +5830,7 @@
         <v>56037443.403815791</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
         <v>36</v>
       </c>
@@ -5847,7 +5868,7 @@
         <v>26078721.471578948</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
         <v>37</v>
       </c>
@@ -5865,7 +5886,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="43" t="s">
         <v>37</v>
       </c>
@@ -5903,7 +5924,7 @@
         <v>13285092.037631579</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="43" t="s">
         <v>37</v>
       </c>
@@ -5921,7 +5942,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="43" t="s">
         <v>37</v>
       </c>
@@ -5951,7 +5972,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="43" t="s">
         <v>37</v>
       </c>
@@ -5989,7 +6010,7 @@
         <v>7212690.1784210531</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="43" t="s">
         <v>38</v>
       </c>
@@ -6019,7 +6040,7 @@
         <v>3143161.6294736844</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="43" t="s">
         <v>38</v>
       </c>
@@ -6045,7 +6066,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -6083,7 +6104,7 @@
         <v>694846.97368421056</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="43" t="s">
         <v>40</v>
       </c>
@@ -6121,7 +6142,7 @@
         <v>31169164.653893046</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="43" t="s">
         <v>40</v>
       </c>
@@ -6159,7 +6180,7 @@
         <v>9024207.2250826061</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="43" t="s">
         <v>40</v>
       </c>
@@ -6197,7 +6218,7 @@
         <v>26014337.772836529</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
         <v>40</v>
       </c>
@@ -6235,7 +6256,7 @@
         <v>21218834.523721006</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
         <v>41</v>
       </c>
@@ -6273,7 +6294,7 @@
         <v>24485113.215146199</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="43" t="s">
         <v>41</v>
       </c>
@@ -6311,7 +6332,7 @@
         <v>42986086.185204685</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="43" t="s">
         <v>41</v>
       </c>
@@ -6349,7 +6370,7 @@
         <v>89969889.638869569</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="43" t="s">
         <v>41</v>
       </c>
@@ -6387,7 +6408,7 @@
         <v>43092807.72445029</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="43" t="s">
         <v>42</v>
       </c>
@@ -6425,7 +6446,7 @@
         <v>26223826.190433443</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="43" t="s">
         <v>42</v>
       </c>
@@ -6443,7 +6464,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="43" t="s">
         <v>42</v>
       </c>
@@ -6481,7 +6502,7 @@
         <v>38913109.206510134</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="43" t="s">
         <v>42</v>
       </c>
@@ -6519,7 +6540,7 @@
         <v>8318128.2670879252</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="44" t="s">
         <v>43</v>
       </c>
@@ -6537,7 +6558,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
         <v>43</v>
       </c>
@@ -6575,7 +6596,7 @@
         <v>593298.1894736843</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="45" t="s">
         <v>43</v>
       </c>
@@ -6613,7 +6634,7 @@
         <v>882693.01642857143</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="45" t="s">
         <v>43</v>
       </c>
@@ -6651,7 +6672,7 @@
         <v>68866.200000000012</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="46" t="s">
         <v>43</v>
       </c>
@@ -6689,7 +6710,7 @@
         <v>9727462.9341666661</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="43" t="s">
         <v>44</v>
       </c>
@@ -6727,7 +6748,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="43" t="s">
         <v>44</v>
       </c>
@@ -6765,7 +6786,7 @@
         <v>16995032.578833334</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="43" t="s">
         <v>44</v>
       </c>
@@ -6803,7 +6824,7 @@
         <v>22529845.132500004</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="43" t="s">
         <v>45</v>
       </c>
@@ -6833,7 +6854,7 @@
         <v>11652763.552941177</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="43" t="s">
         <v>45</v>
       </c>
@@ -6851,7 +6872,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="43" t="s">
         <v>45</v>
       </c>
@@ -6877,7 +6898,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="43" t="s">
         <v>46</v>
       </c>
@@ -6915,7 +6936,7 @@
         <v>3129137.4496973683</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="43" t="s">
         <v>46</v>
       </c>
@@ -6933,7 +6954,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="43" t="s">
         <v>46</v>
       </c>
@@ -6959,7 +6980,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="43" t="s">
         <v>47</v>
       </c>
@@ -6989,7 +7010,7 @@
         <v>19439134.578947369</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="43" t="s">
         <v>47</v>
       </c>
@@ -7017,7 +7038,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="43" t="s">
         <v>47</v>
       </c>
@@ -7053,7 +7074,7 @@
         <v>12278482.1775</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="43" t="s">
         <v>48</v>
       </c>
@@ -7091,7 +7112,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="43" t="s">
         <v>48</v>
       </c>
@@ -7129,7 +7150,7 @@
         <v>428081.60342105263</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="43" t="s">
         <v>48</v>
       </c>
@@ -7147,7 +7168,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="43" t="s">
         <v>49</v>
       </c>
@@ -7185,7 +7206,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="43" t="s">
         <v>49</v>
       </c>
@@ -7223,7 +7244,7 @@
         <v>15938780.685739476</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="43" t="s">
         <v>49</v>
       </c>
@@ -7259,7 +7280,7 @@
         <v>7463.7629999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="43" t="s">
         <v>49</v>
       </c>
@@ -7297,7 +7318,7 @@
         <v>6024488.8079210529</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="43" t="s">
         <v>50</v>
       </c>
@@ -7335,7 +7356,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="43" t="s">
         <v>50</v>
       </c>
@@ -7373,7 +7394,7 @@
         <v>3357564.5291447369</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="43" t="s">
         <v>50</v>
       </c>
@@ -7411,7 +7432,7 @@
         <v>277375.88714868418</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="43" t="s">
         <v>50</v>
       </c>
@@ -7449,7 +7470,7 @@
         <v>48463.652665350877</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="43" t="s">
         <v>50</v>
       </c>
@@ -7485,7 +7506,7 @@
         <v>962589.57300000009</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>51</v>
       </c>
@@ -7523,7 +7544,7 @@
         <v>4199871.1182460524</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="43" t="s">
         <v>52</v>
       </c>
@@ -7541,7 +7562,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="43" t="s">
         <v>52</v>
       </c>
@@ -7573,7 +7594,7 @@
         <v>8001.5255263157915</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="43" t="s">
         <v>52</v>
       </c>
@@ -7611,7 +7632,7 @@
         <v>196251.34736842106</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="43" t="s">
         <v>53</v>
       </c>
@@ -7649,7 +7670,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="43" t="s">
         <v>53</v>
       </c>
@@ -7687,7 +7708,7 @@
         <v>3969424.3796421057</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="43" t="s">
         <v>53</v>
       </c>
@@ -7725,7 +7746,7 @@
         <v>8895367.3138157893</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="43" t="s">
         <v>54</v>
       </c>
@@ -7743,7 +7764,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="43" t="s">
         <v>54</v>
       </c>
@@ -7761,7 +7782,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="43" t="s">
         <v>54</v>
       </c>
@@ -7779,7 +7800,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="43" t="s">
         <v>54</v>
       </c>
@@ -7799,7 +7820,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="43" t="s">
         <v>55</v>
       </c>
@@ -7817,7 +7838,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="43" t="s">
         <v>55</v>
       </c>
@@ -7855,7 +7876,7 @@
         <v>44666553.82686425</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="43" t="s">
         <v>55</v>
       </c>
@@ -7893,7 +7914,7 @@
         <v>2148068.0935714287</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="43" t="s">
         <v>55</v>
       </c>
@@ -7931,7 +7952,7 @@
         <v>10829590.64130117</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="43" t="s">
         <v>55</v>
       </c>
@@ -7969,7 +7990,7 @@
         <v>53816727.563368849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="43" t="s">
         <v>56</v>
       </c>
@@ -8007,7 +8028,7 @@
         <v>5366204.9252105262</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="43" t="s">
         <v>56</v>
       </c>
@@ -8045,7 +8066,7 @@
         <v>1918456.0949999997</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="43" t="s">
         <v>57</v>
       </c>
@@ -8083,7 +8104,7 @@
         <v>2456094.4891353385</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="43" t="s">
         <v>57</v>
       </c>
@@ -8121,7 +8142,7 @@
         <v>84871745.658650786</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="43" t="s">
         <v>57</v>
       </c>
@@ -8159,7 +8180,7 @@
         <v>228007209.74936509</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="43" t="s">
         <v>57</v>
       </c>
@@ -8197,7 +8218,7 @@
         <v>32273220.97396826</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>58</v>
       </c>
@@ -8235,7 +8256,7 @@
         <v>1012182.5810526316</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="43" t="s">
         <v>59</v>
       </c>
@@ -8273,7 +8294,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="43" t="s">
         <v>59</v>
       </c>
@@ -8311,7 +8332,7 @@
         <v>19377207.360228568</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="43" t="s">
         <v>59</v>
       </c>
@@ -8349,7 +8370,7 @@
         <v>123225959.44543454</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="43" t="s">
         <v>59</v>
       </c>
@@ -8377,7 +8398,7 @@
         <v>9816494.2557882406</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="43" t="s">
         <v>60</v>
       </c>
@@ -8415,7 +8436,7 @@
         <v>85488520.6669323</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="43" t="s">
         <v>60</v>
       </c>
@@ -8453,7 +8474,7 @@
         <v>57292565.508875743</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="43" t="s">
         <v>60</v>
       </c>
@@ -8491,7 +8512,7 @@
         <v>162941685.62800577</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="43" t="s">
         <v>60</v>
       </c>
@@ -8529,7 +8550,7 @@
         <v>66591452.998300254</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="43" t="s">
         <v>61</v>
       </c>
@@ -8567,7 +8588,7 @@
         <v>6418700.4964842089</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="43" t="s">
         <v>61</v>
       </c>
@@ -8605,7 +8626,7 @@
         <v>657.72019736842117</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="43" t="s">
         <v>61</v>
       </c>
@@ -8643,7 +8664,7 @@
         <v>38980.994268421055</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="43" t="s">
         <v>62</v>
       </c>
@@ -8681,7 +8702,7 @@
         <v>57668115.752105266</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="43" t="s">
         <v>62</v>
       </c>
@@ -8719,7 +8740,7 @@
         <v>48207996.665438592</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="43" t="s">
         <v>62</v>
       </c>
@@ -8757,7 +8778,7 @@
         <v>163594841.15653506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="43" t="s">
         <v>62</v>
       </c>
@@ -8795,7 +8816,7 @@
         <v>51145121.535921052</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="43" t="s">
         <v>63</v>
       </c>
@@ -8821,7 +8842,7 @@
         <v>1140116.518780523</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="43" t="s">
         <v>63</v>
       </c>
@@ -8847,7 +8868,7 @@
         <v>3095533.6346984911</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="43" t="s">
         <v>63</v>
       </c>
@@ -8875,7 +8896,7 @@
         <v>24073104.668296658</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="43" t="s">
         <v>63</v>
       </c>
@@ -8903,7 +8924,7 @@
         <v>8249515.7360912031</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="43" t="s">
         <v>64</v>
       </c>
@@ -8921,7 +8942,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="43" t="s">
         <v>64</v>
       </c>
@@ -8939,7 +8960,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="43" t="s">
         <v>64</v>
       </c>
@@ -8959,7 +8980,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="43" t="s">
         <v>65</v>
       </c>
@@ -8987,7 +9008,7 @@
         <v>524620.18888888881</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="43" t="s">
         <v>65</v>
       </c>
@@ -9025,7 +9046,7 @@
         <v>11686619.239444446</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="43" t="s">
         <v>65</v>
       </c>
@@ -9063,7 +9084,7 @@
         <v>67230835.707277775</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="43" t="s">
         <v>65</v>
       </c>
@@ -9101,7 +9122,7 @@
         <v>8927850.3513888884</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="43" t="s">
         <v>66</v>
       </c>
@@ -9119,7 +9140,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="43" t="s">
         <v>66</v>
       </c>
@@ -9157,7 +9178,7 @@
         <v>11586096.10842105</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="43" t="s">
         <v>66</v>
       </c>
@@ -9195,7 +9216,7 @@
         <v>61286058.379432946</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="43" t="s">
         <v>66</v>
       </c>
@@ -9233,7 +9254,7 @@
         <v>198326735.48209769</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="43" t="s">
         <v>66</v>
       </c>
@@ -9271,7 +9292,7 @@
         <v>74368544.324421823</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="43" t="s">
         <v>67</v>
       </c>
@@ -9309,7 +9330,7 @@
         <v>37434.968421052632</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="43" t="s">
         <v>67</v>
       </c>
@@ -9327,7 +9348,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="43" t="s">
         <v>67</v>
       </c>
@@ -9345,7 +9366,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="43" t="s">
         <v>68</v>
       </c>
@@ -9383,7 +9404,7 @@
         <v>14085732.501447368</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="43" t="s">
         <v>68</v>
       </c>
@@ -9415,7 +9436,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="43" t="s">
         <v>68</v>
       </c>
@@ -9453,7 +9474,7 @@
         <v>2658726.6143421056</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="43" t="s">
         <v>69</v>
       </c>
@@ -9491,7 +9512,7 @@
         <v>5274066.9230263159</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="43" t="s">
         <v>69</v>
       </c>
@@ -9517,7 +9538,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="43" t="s">
         <v>69</v>
       </c>
@@ -9555,7 +9576,7 @@
         <v>109338.78881578946</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="43" t="s">
         <v>70</v>
       </c>
@@ -9573,7 +9594,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="43" t="s">
         <v>70</v>
       </c>
@@ -9591,7 +9612,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="43" t="s">
         <v>70</v>
       </c>
@@ -9609,7 +9630,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="43" t="s">
         <v>70</v>
       </c>
@@ -9627,7 +9648,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="43" t="s">
         <v>70</v>
       </c>
@@ -9645,7 +9666,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="43" t="s">
         <v>71</v>
       </c>
@@ -9663,7 +9684,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="43" t="s">
         <v>71</v>
       </c>
@@ -9701,7 +9722,7 @@
         <v>1602020.15372807</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="43" t="s">
         <v>71</v>
       </c>
@@ -9739,7 +9760,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="43" t="s">
         <v>71</v>
       </c>
@@ -9765,7 +9786,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="43" t="s">
         <v>71</v>
       </c>
@@ -9803,7 +9824,7 @@
         <v>8435990.8228508774</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="43" t="s">
         <v>72</v>
       </c>
@@ -9821,7 +9842,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="43" t="s">
         <v>72</v>
       </c>
@@ -9859,7 +9880,7 @@
         <v>41053.861588892236</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="43" t="s">
         <v>72</v>
       </c>
@@ -9889,7 +9910,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="43" t="s">
         <v>72</v>
       </c>
@@ -9927,7 +9948,7 @@
         <v>361138.98097679514</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="43" t="s">
         <v>73</v>
       </c>
@@ -9965,7 +9986,7 @@
         <v>21801576.347789474</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="43" t="s">
         <v>73</v>
       </c>
@@ -9983,7 +10004,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="43" t="s">
         <v>73</v>
       </c>
@@ -10021,7 +10042,7 @@
         <v>4773371.973289473</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="43" t="s">
         <v>74</v>
       </c>
@@ -10059,7 +10080,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="43" t="s">
         <v>74</v>
       </c>
@@ -10097,7 +10118,7 @@
         <v>95686.964999999997</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="43" t="s">
         <v>74</v>
       </c>
@@ -10135,7 +10156,7 @@
         <v>19427327.223125003</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="43" t="s">
         <v>74</v>
       </c>
@@ -10173,7 +10194,7 @@
         <v>28291617.551274512</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="43" t="s">
         <v>74</v>
       </c>
@@ -10211,7 +10232,7 @@
         <v>21470697.767319441</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
@@ -10223,7 +10244,7 @@
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
-    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
@@ -10235,7 +10256,7 @@
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
@@ -10247,7 +10268,7 @@
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>43</v>
       </c>
@@ -10255,47 +10276,47 @@
         <v>110</v>
       </c>
       <c r="C207" s="8">
-        <f>SUM(C92+C93)</f>
-        <v>62765698.894231752</v>
+        <f t="shared" ref="C207:L207" si="0">SUM(C96+C136+C142)</f>
+        <v>14777182.228013158</v>
       </c>
       <c r="D207" s="8">
-        <f>SUM(D92+D93)</f>
-        <v>104605466.70853016</v>
+        <f t="shared" si="0"/>
+        <v>37949221.241086259</v>
       </c>
       <c r="E207" s="8">
-        <f t="shared" ref="E207:L207" si="0">SUM(E92+E93)</f>
-        <v>90210217.166338012</v>
+        <f t="shared" si="0"/>
+        <v>17547795.842103511</v>
       </c>
       <c r="F207" s="8">
-        <f t="shared" si="0"/>
-        <v>69199357.094551593</v>
+        <f>SUM(F96+F136+F142)</f>
+        <v>21303104.688398462</v>
       </c>
       <c r="G207" s="8">
         <f t="shared" si="0"/>
-        <v>86221766.026547611</v>
+        <v>22347712.522483818</v>
       </c>
       <c r="H207" s="8">
         <f t="shared" si="0"/>
-        <v>20943493.617039636</v>
+        <v>20946969.555763159</v>
       </c>
       <c r="I207" s="8">
         <f t="shared" si="0"/>
-        <v>12437570.342499999</v>
+        <v>19884769.205236845</v>
       </c>
       <c r="J207" s="8">
         <f t="shared" si="0"/>
-        <v>899709.40166666661</v>
+        <v>20824130.238903508</v>
       </c>
       <c r="K207" s="8">
         <f t="shared" si="0"/>
-        <v>923478.11952380964</v>
+        <v>21884645.404903509</v>
       </c>
       <c r="L207" s="8">
         <f t="shared" si="0"/>
-        <v>951559.21642857138</v>
-      </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22913488.673833333</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>57</v>
       </c>
@@ -10303,11 +10324,11 @@
         <v>110</v>
       </c>
       <c r="C208" s="8">
-        <f>C138+C139</f>
+        <f t="shared" ref="C208:L208" si="1">C138+C139</f>
         <v>331279149.4189564</v>
       </c>
       <c r="D208" s="8">
-        <f t="shared" ref="C208:L208" si="1">D138+D139</f>
+        <f t="shared" si="1"/>
         <v>227385022.03396031</v>
       </c>
       <c r="E208" s="8">
@@ -10343,7 +10364,7 @@
         <v>312878955.40801585</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>55</v>
       </c>
@@ -10351,11 +10372,11 @@
         <v>110</v>
       </c>
       <c r="C209" s="8">
-        <f>C132+C133</f>
+        <f t="shared" ref="C209:L209" si="2">C132+C133</f>
         <v>26052155.976207186</v>
       </c>
       <c r="D209" s="8">
-        <f t="shared" ref="C209:L209" si="2">D132+D133</f>
+        <f t="shared" si="2"/>
         <v>26626398.679317039</v>
       </c>
       <c r="E209" s="8">
@@ -10391,7 +10412,7 @@
         <v>12977658.734872598</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>71</v>
       </c>
@@ -10439,7 +10460,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>66</v>
       </c>
@@ -10487,7 +10508,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>108</v>
       </c>
@@ -10535,7 +10556,7 @@
         <v>6234188.6265789466</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>109</v>
       </c>
@@ -10583,7 +10604,7 @@
         <v>57596497.972499989</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>98</v>
       </c>
@@ -10631,7 +10652,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>99</v>
       </c>
@@ -10679,7 +10700,7 @@
         <v>270569619.35592109</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="16" t="s">
         <v>100</v>
       </c>
@@ -10727,7 +10748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>101</v>
       </c>
@@ -10775,7 +10796,7 @@
         <v>132955975.82407425</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>102</v>
       </c>
@@ -10823,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>103</v>
       </c>
@@ -10871,7 +10892,7 @@
         <v>35038544.997919135</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>104</v>
       </c>
@@ -10919,7 +10940,7 @@
         <v>64955806.190789476</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>105</v>
       </c>
@@ -10967,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>62</v>
       </c>
@@ -11015,7 +11036,7 @@
         <v>211802837.82197365</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>60</v>
       </c>
@@ -11063,10 +11084,10 @@
         <v>220234251.13688153</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C224" s="8"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>113</v>
       </c>
@@ -11079,7 +11100,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>114</v>
       </c>
@@ -11088,7 +11109,7 @@
       </c>
       <c r="C226" s="8"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>106</v>
       </c>
@@ -11096,14 +11117,14 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
       <c r="J228" s="15"/>
       <c r="K228" s="15"/>
       <c r="L228" s="15"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B229" s="2" t="s">
         <v>115</v>
       </c>
@@ -11113,52 +11134,52 @@
       <c r="K229" s="27"/>
       <c r="L229" s="27"/>
     </row>
-    <row r="230" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="18" t="s">
         <v>43</v>
       </c>
       <c r="C230" s="19">
         <f t="shared" ref="C230:L230" si="17">C207*$B226</f>
-        <v>56489129.004808575</v>
+        <v>13299464.005211843</v>
       </c>
       <c r="D230" s="19">
         <f t="shared" si="17"/>
-        <v>94144920.037677139</v>
+        <v>34154299.116977632</v>
       </c>
       <c r="E230" s="19">
         <f t="shared" si="17"/>
-        <v>81189195.449704215</v>
+        <v>15793016.25789316</v>
       </c>
       <c r="F230" s="19">
         <f t="shared" si="17"/>
-        <v>62279421.385096438</v>
+        <v>19172794.219558615</v>
       </c>
       <c r="G230" s="19">
         <f t="shared" si="17"/>
-        <v>77599589.423892856</v>
+        <v>20112941.270235438</v>
       </c>
       <c r="H230" s="19">
         <f t="shared" si="17"/>
-        <v>18849144.255335674</v>
+        <v>18852272.600186843</v>
       </c>
       <c r="I230" s="19">
         <f t="shared" si="17"/>
-        <v>11193813.308249999</v>
+        <v>17896292.28471316</v>
       </c>
       <c r="J230" s="19">
         <f t="shared" si="17"/>
-        <v>809738.46149999998</v>
+        <v>18741717.215013158</v>
       </c>
       <c r="K230" s="19">
         <f t="shared" si="17"/>
-        <v>831130.30757142871</v>
+        <v>19696180.864413157</v>
       </c>
       <c r="L230" s="19">
         <f t="shared" si="17"/>
-        <v>856403.29478571424</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+        <v>20622139.806450002</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>75</v>
       </c>
@@ -11167,46 +11188,46 @@
       </c>
       <c r="C231" s="2">
         <f t="shared" ref="C231:L231" si="18">$B$231*C230</f>
-        <v>46218378.276661567</v>
+        <v>10881379.640627872</v>
       </c>
       <c r="D231" s="2">
         <f t="shared" si="18"/>
-        <v>77027661.849008575</v>
+        <v>27944426.550254427</v>
       </c>
       <c r="E231" s="2">
         <f t="shared" si="18"/>
-        <v>66427523.549757995</v>
+        <v>12921558.75645804</v>
       </c>
       <c r="F231" s="2">
         <f t="shared" si="18"/>
-        <v>50955890.224169813</v>
+        <v>15686831.634184323</v>
       </c>
       <c r="G231" s="2">
         <f t="shared" si="18"/>
-        <v>63490573.165003248</v>
+        <v>16456042.857465358</v>
       </c>
       <c r="H231" s="2">
         <f t="shared" si="18"/>
-        <v>15422027.118001916</v>
+        <v>15424586.672880145</v>
       </c>
       <c r="I231" s="2">
         <f t="shared" si="18"/>
-        <v>9158574.5249318182</v>
+        <v>14642420.96021986</v>
       </c>
       <c r="J231" s="2">
         <f t="shared" si="18"/>
-        <v>662513.28668181819</v>
+        <v>15334132.266828949</v>
       </c>
       <c r="K231" s="2">
         <f t="shared" si="18"/>
-        <v>680015.70619480533</v>
+        <v>16115057.070883494</v>
       </c>
       <c r="L231" s="2">
         <f t="shared" si="18"/>
-        <v>700693.60482467536</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16872659.841640912</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>118</v>
       </c>
@@ -11215,46 +11236,46 @@
       </c>
       <c r="C232" s="2">
         <f t="shared" ref="C232:L232" si="19">$B$232*C230</f>
-        <v>10270750.728147011</v>
+        <v>2418084.364583971</v>
       </c>
       <c r="D232" s="2">
         <f t="shared" si="19"/>
-        <v>17117258.188668568</v>
+        <v>6209872.5667232042</v>
       </c>
       <c r="E232" s="2">
         <f t="shared" si="19"/>
-        <v>14761671.899946216</v>
+        <v>2871457.5014351192</v>
       </c>
       <c r="F232" s="2">
         <f t="shared" si="19"/>
-        <v>11323531.160926621</v>
+        <v>3485962.5853742929</v>
       </c>
       <c r="G232" s="2">
         <f t="shared" si="19"/>
-        <v>14109016.258889606</v>
+        <v>3656898.4127700785</v>
       </c>
       <c r="H232" s="2">
         <f t="shared" si="19"/>
-        <v>3427117.1373337577</v>
+        <v>3427685.9273066977</v>
       </c>
       <c r="I232" s="2">
         <f t="shared" si="19"/>
-        <v>2035238.7833181811</v>
+        <v>3253871.3244933011</v>
       </c>
       <c r="J232" s="2">
         <f t="shared" si="19"/>
-        <v>147225.17481818178</v>
+        <v>3407584.9481842094</v>
       </c>
       <c r="K232" s="2">
         <f t="shared" si="19"/>
-        <v>151114.60137662335</v>
+        <v>3581123.7935296642</v>
       </c>
       <c r="L232" s="2">
         <f t="shared" si="19"/>
-        <v>155709.68996103891</v>
-      </c>
-    </row>
-    <row r="233" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3749479.9648090904</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="18" t="s">
         <v>57</v>
       </c>
@@ -11299,7 +11320,7 @@
         <v>281591059.86721426</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>75</v>
       </c>
@@ -11347,7 +11368,7 @@
         <v>203910767.49005172</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>119</v>
       </c>
@@ -11395,7 +11416,7 @@
         <v>77680292.377162561</v>
       </c>
     </row>
-    <row r="236" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="18" t="s">
         <v>55</v>
       </c>
@@ -11440,7 +11461,7 @@
         <v>11679892.861385338</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>116</v>
       </c>
@@ -11488,7 +11509,7 @@
         <v>3412103.5325395376</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>117</v>
       </c>
@@ -11536,7 +11557,7 @@
         <v>8267789.3288458008</v>
       </c>
     </row>
-    <row r="239" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="18" t="s">
         <v>71</v>
       </c>
@@ -11581,7 +11602,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>75</v>
       </c>
@@ -11629,7 +11650,7 @@
         <v>2289842.5978235295</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>118</v>
       </c>
@@ -11677,7 +11698,7 @@
         <v>508853.91062745103</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>81</v>
       </c>
@@ -11725,7 +11746,7 @@
         <v>290773.66321568622</v>
       </c>
     </row>
-    <row r="243" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="18" t="s">
         <v>66</v>
       </c>
@@ -11770,7 +11791,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>75</v>
       </c>
@@ -11818,7 +11839,7 @@
         <v>192418894.27384037</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>118</v>
       </c>
@@ -11866,7 +11887,7 @@
         <v>42759754.283075638</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>81</v>
       </c>
@@ -11914,7 +11935,7 @@
         <v>24434145.304614648</v>
       </c>
     </row>
-    <row r="247" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="18" t="s">
         <v>108</v>
       </c>
@@ -11959,7 +11980,7 @@
         <v>6857607.4892368419</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>75</v>
       </c>
@@ -12007,7 +12028,7 @@
         <v>5082697.3155520121</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>118</v>
       </c>
@@ -12055,7 +12076,7 @@
         <v>1129488.2923448917</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>81</v>
       </c>
@@ -12103,7 +12124,7 @@
         <v>645421.88133993803</v>
       </c>
     </row>
-    <row r="251" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="18" t="s">
         <v>109</v>
       </c>
@@ -12148,7 +12169,7 @@
         <v>63356147.769749992</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>75</v>
       </c>
@@ -12196,7 +12217,7 @@
         <v>45878589.764301717</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>119</v>
       </c>
@@ -12244,7 +12265,7 @@
         <v>17477558.005448274</v>
       </c>
     </row>
-    <row r="254" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="18" t="s">
         <v>98</v>
       </c>
@@ -12289,7 +12310,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>75</v>
       </c>
@@ -12337,7 +12358,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="256" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="18" t="s">
         <v>99</v>
       </c>
@@ -12382,7 +12403,7 @@
         <v>297626581.2915132</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>75</v>
       </c>
@@ -12430,7 +12451,7 @@
         <v>165933403.72889677</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>118</v>
       </c>
@@ -12478,7 +12499,7 @@
         <v>36874089.717532612</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>119</v>
       </c>
@@ -12526,7 +12547,7 @@
         <v>63212725.230055898</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>82</v>
       </c>
@@ -12574,7 +12595,7 @@
         <v>21070908.410018638</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>83</v>
       </c>
@@ -12622,12 +12643,12 @@
         <v>10535454.205009319</v>
       </c>
     </row>
-    <row r="262" spans="1:12" s="21" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="23" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="18" t="s">
         <v>101</v>
       </c>
@@ -12672,7 +12693,7 @@
         <v>146251573.40648168</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>82</v>
       </c>
@@ -12720,7 +12741,7 @@
         <v>53182390.329629704</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>84</v>
       </c>
@@ -12768,7 +12789,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>85</v>
       </c>
@@ -12816,7 +12837,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>86</v>
       </c>
@@ -12864,7 +12885,7 @@
         <v>59830189.120833419</v>
       </c>
     </row>
-    <row r="268" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="18" t="s">
         <v>102</v>
       </c>
@@ -12909,7 +12930,7 @@
         <v>404502055.98924994</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>75</v>
       </c>
@@ -12957,7 +12978,7 @@
         <v>172186685.99542397</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="22" t="s">
         <v>76</v>
       </c>
@@ -13005,7 +13026,7 @@
         <v>38263707.998983108</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>77</v>
       </c>
@@ -13053,7 +13074,7 @@
         <v>71061171.998111486</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>80</v>
       </c>
@@ -13101,7 +13122,7 @@
         <v>68328049.998184115</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>83</v>
       </c>
@@ -13149,7 +13170,7 @@
         <v>10932487.999709459</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>87</v>
       </c>
@@ -13197,7 +13218,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>88</v>
       </c>
@@ -13245,7 +13266,7 @@
         <v>27331219.999273647</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -13293,7 +13314,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="277" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="18" t="s">
         <v>103</v>
       </c>
@@ -13338,7 +13359,7 @@
         <v>31534690.498127222</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>77</v>
       </c>
@@ -13386,7 +13407,7 @@
         <v>24845513.725797206</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>79</v>
       </c>
@@ -13434,7 +13455,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>90</v>
       </c>
@@ -13482,7 +13503,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="28" t="s">
         <v>154</v>
       </c>
@@ -13525,7 +13546,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="282" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="18" t="s">
         <v>104</v>
       </c>
@@ -13570,7 +13591,7 @@
         <v>71451386.809868425</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>75</v>
       </c>
@@ -13618,7 +13639,7 @@
         <v>63400526.324249454</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>82</v>
       </c>
@@ -13666,7 +13687,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="285" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="18" t="s">
         <v>105</v>
       </c>
@@ -13711,7 +13732,7 @@
         <v>3954.38333881579</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>75</v>
       </c>
@@ -13759,7 +13780,7 @@
         <v>2737.650003795547</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>80</v>
       </c>
@@ -13807,7 +13828,7 @@
         <v>1086.3690491252169</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>91</v>
       </c>
@@ -13855,7 +13876,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="289" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="29" t="s">
         <v>62</v>
       </c>
@@ -13900,7 +13921,7 @@
         <v>190622554.0397763</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>75</v>
       </c>
@@ -13948,7 +13969,7 @@
         <v>121305261.66167584</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>88</v>
       </c>
@@ -13996,7 +14017,7 @@
         <v>13932545.477990292</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>77</v>
       </c>
@@ -14044,7 +14065,7 @@
         <v>50062488.939739235</v>
       </c>
     </row>
-    <row r="293" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="29" t="s">
         <v>155</v>
       </c>
@@ -14089,7 +14110,7 @@
         <v>242257676.2505697</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>75</v>
       </c>
@@ -14137,7 +14158,7 @@
         <v>165893843.51941183</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>156</v>
       </c>
@@ -14185,7 +14206,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>77</v>
       </c>
@@ -14233,7 +14254,7 @@
         <v>68464125.896900132</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H301" s="16"/>
       <c r="I301" s="16"/>
       <c r="J301" s="16"/>
@@ -14330,17 +14351,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55228539-2602-4D9E-BF99-AB1A3FA50A1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55228539-2602-4D9E-BF99-AB1A3FA50A1F}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -14375,7 +14396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -14410,7 +14431,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -14448,37 +14469,37 @@
         <v>121</v>
       </c>
       <c r="N3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
@@ -14546,7 +14567,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -14614,7 +14635,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -14682,7 +14703,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -14750,7 +14771,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>142</v>
       </c>
@@ -14818,7 +14839,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -14886,7 +14907,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -14954,7 +14975,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
@@ -15022,7 +15043,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>144</v>
       </c>
@@ -15090,7 +15111,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>145</v>
       </c>
@@ -15158,7 +15179,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -15226,7 +15247,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -15294,7 +15315,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -15362,7 +15383,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -15430,7 +15451,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -15498,7 +15519,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -15566,9 +15587,9 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -15634,7 +15655,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>147</v>
       </c>
@@ -15702,7 +15723,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>147</v>
       </c>
@@ -15770,7 +15791,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
@@ -15805,7 +15826,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>148</v>
       </c>
@@ -15840,7 +15861,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -15878,37 +15899,37 @@
         <v>121</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>149</v>
       </c>
@@ -15976,7 +15997,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>156</v>
       </c>
@@ -16044,7 +16065,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>150</v>
       </c>
@@ -16112,7 +16133,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>150</v>
       </c>
@@ -16180,7 +16201,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>150</v>
       </c>
@@ -16248,7 +16269,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>150</v>
       </c>
@@ -16316,7 +16337,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>150</v>
       </c>
@@ -16384,7 +16405,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>150</v>
       </c>
@@ -16452,7 +16473,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -16520,7 +16541,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -16588,7 +16609,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -16656,7 +16677,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>152</v>
       </c>
@@ -16724,7 +16745,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>152</v>
       </c>
@@ -16792,7 +16813,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
@@ -16860,7 +16881,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>152</v>
       </c>
@@ -16928,7 +16949,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
@@ -16996,7 +17017,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
@@ -17064,7 +17085,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -17132,7 +17153,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -17200,7 +17221,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>152</v>
       </c>
@@ -17265,7 +17286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
@@ -17343,7 +17364,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -17421,7 +17442,7 @@
         <v>25400000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -17499,7 +17520,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
@@ -17577,7 +17598,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -17655,7 +17676,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -17733,7 +17754,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M52" t="s">
         <v>145</v>
       </c>
@@ -17778,7 +17799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M53" t="s">
         <v>116</v>
       </c>
@@ -17823,7 +17844,7 @@
         <v>217800000</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M54" t="s">
         <v>146</v>
       </c>
@@ -17868,7 +17889,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M55" t="s">
         <v>154</v>
       </c>
@@ -17913,7 +17934,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M56" t="s">
         <v>147</v>
       </c>
@@ -17958,7 +17979,7 @@
         <v>82300000</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M57" t="s">
         <v>148</v>
       </c>
@@ -18003,7 +18024,7 @@
         <v>5700000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M58" t="s">
         <v>149</v>
       </c>
@@ -18048,7 +18069,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M59" t="s">
         <v>156</v>
       </c>
@@ -18093,7 +18114,7 @@
         <v>7900000</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M60" t="s">
         <v>150</v>
       </c>
@@ -18138,7 +18159,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M61" t="s">
         <v>151</v>
       </c>
@@ -18183,7 +18204,7 @@
         <v>128200000</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M62" t="s">
         <v>152</v>
       </c>
@@ -18228,7 +18249,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M63" t="s">
         <v>153</v>
       </c>
@@ -18275,20 +18296,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{770C77AF-CB50-4854-8654-5465FF2CEF2B}">
   <dimension ref="B2:T19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="217.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>84</v>
       </c>
@@ -18344,7 +18365,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="26" t="s">
         <v>81</v>
       </c>
@@ -18416,7 +18437,7 @@
         <v>"Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B4" s="26" t="s">
         <v>87</v>
       </c>
@@ -18428,7 +18449,7 @@
         <v>"AJ_Vaccines","BB_NCIPD","Beijing_Institute","Bharat_Biotech","Bilthoven","Biological_E","Centro_de","GSK","Haffkine_Bio","LG_Chem","Merck_Sharp","Panacea_Biotec","PT_Bio","Sanofi_Pasteur","Serum_Institute","Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>88</v>
       </c>
@@ -18436,7 +18457,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>85</v>
       </c>
@@ -18444,7 +18465,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>119</v>
       </c>
@@ -18452,7 +18473,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>91</v>
       </c>
@@ -18460,7 +18481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>77</v>
       </c>
@@ -18468,7 +18489,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>89</v>
       </c>
@@ -18476,7 +18497,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>82</v>
       </c>
@@ -18484,7 +18505,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>79</v>
       </c>
@@ -18492,7 +18513,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="26" t="s">
         <v>83</v>
       </c>
@@ -18500,7 +18521,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="26" t="s">
         <v>118</v>
       </c>
@@ -18508,7 +18529,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B15" s="26" t="s">
         <v>80</v>
       </c>
@@ -18516,7 +18537,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
         <v>75</v>
       </c>
@@ -18524,7 +18545,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="26" t="s">
         <v>90</v>
       </c>
@@ -18532,7 +18553,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
         <v>156</v>
       </c>
@@ -18540,12 +18561,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -18556,20 +18577,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
-  <dimension ref="A1:AY44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B1" s="36">
         <v>1</v>
       </c>
@@ -18600,3443 +18615,603 @@
       <c r="K1" s="36">
         <v>10</v>
       </c>
-      <c r="L1" s="36">
-        <v>11</v>
-      </c>
-      <c r="M1" s="36">
-        <v>12</v>
-      </c>
-      <c r="N1" s="36">
-        <v>13</v>
-      </c>
-      <c r="O1" s="36">
-        <v>14</v>
-      </c>
-      <c r="P1" s="36">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="36">
-        <v>16</v>
-      </c>
-      <c r="R1" s="36">
-        <v>17</v>
-      </c>
-      <c r="S1" s="36">
-        <v>18</v>
-      </c>
-      <c r="T1" s="36">
-        <v>19</v>
-      </c>
-      <c r="U1" s="36">
-        <v>20</v>
-      </c>
-      <c r="V1" s="36">
-        <v>21</v>
-      </c>
-      <c r="W1" s="36">
-        <v>22</v>
-      </c>
-      <c r="X1" s="36">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="36">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="36">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="36">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="36">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="36">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="36">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="36">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="36">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="36">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="36">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="36">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="36">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="36">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="36">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="36">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="36">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="36">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="36">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="36">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="36">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="36">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="36">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="36">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="36">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="36">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="36">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="36">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="37">
+        <v>1733000000</v>
+      </c>
+      <c r="C2" s="37">
+        <v>1921000000</v>
+      </c>
+      <c r="D2" s="37">
+        <v>2079000000</v>
+      </c>
+      <c r="E2" s="37">
+        <v>2391000000</v>
+      </c>
+      <c r="F2" s="37">
+        <v>2603000000</v>
+      </c>
+      <c r="G2" s="37">
+        <v>2371000000</v>
+      </c>
+      <c r="H2" s="37">
+        <v>2251000000</v>
+      </c>
+      <c r="I2" s="37">
+        <v>2198000000</v>
+      </c>
+      <c r="J2" s="37">
+        <v>2155000000</v>
+      </c>
+      <c r="K2" s="37">
+        <v>2178000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="37">
+        <v>160100000</v>
+      </c>
+      <c r="C3" s="37">
+        <v>140800000</v>
+      </c>
+      <c r="D3" s="37">
+        <v>154800000</v>
+      </c>
+      <c r="E3" s="37">
+        <v>143800000</v>
+      </c>
+      <c r="F3" s="37">
+        <v>147500000</v>
+      </c>
+      <c r="G3" s="37">
+        <v>171200000</v>
+      </c>
+      <c r="H3" s="37">
+        <v>139700000</v>
+      </c>
+      <c r="I3" s="37">
+        <v>172900000</v>
+      </c>
+      <c r="J3" s="37">
+        <v>149300000</v>
+      </c>
+      <c r="K3" s="37">
+        <v>158400000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="37">
+        <v>248000000</v>
+      </c>
+      <c r="C4" s="37">
+        <v>248000000</v>
+      </c>
+      <c r="D4" s="37">
+        <v>360000000</v>
+      </c>
+      <c r="E4" s="37">
+        <v>952000000</v>
+      </c>
+      <c r="F4" s="37">
+        <v>1216000000</v>
+      </c>
+      <c r="G4" s="37">
+        <v>848000000</v>
+      </c>
+      <c r="H4" s="37">
+        <v>552000000</v>
+      </c>
+      <c r="I4" s="37">
+        <v>552000000</v>
+      </c>
+      <c r="J4" s="37">
+        <v>440000000</v>
+      </c>
+      <c r="K4" s="37">
+        <v>456000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="37">
+        <v>116600000</v>
+      </c>
+      <c r="C5" s="37">
+        <v>129900000</v>
+      </c>
+      <c r="D5" s="37">
+        <v>128200000</v>
+      </c>
+      <c r="E5" s="37">
+        <v>123000000</v>
+      </c>
+      <c r="F5" s="37">
+        <v>123100000</v>
+      </c>
+      <c r="G5" s="37">
+        <v>120400000</v>
+      </c>
+      <c r="H5" s="37">
+        <v>121900000</v>
+      </c>
+      <c r="I5" s="37">
+        <v>121000000</v>
+      </c>
+      <c r="J5" s="37">
+        <v>122400000</v>
+      </c>
+      <c r="K5" s="37">
+        <v>123300000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6">
+        <v>1074100000</v>
+      </c>
+      <c r="C6">
+        <v>1109700000</v>
+      </c>
+      <c r="D6">
+        <v>1160000000</v>
+      </c>
+      <c r="E6">
+        <v>1115800000</v>
+      </c>
+      <c r="F6">
+        <v>1141600000</v>
+      </c>
+      <c r="G6">
+        <v>1191500000</v>
+      </c>
+      <c r="H6">
+        <v>1120400000</v>
+      </c>
+      <c r="I6">
+        <v>1192500000</v>
+      </c>
+      <c r="J6">
+        <v>1139200000</v>
+      </c>
+      <c r="K6">
+        <v>1169600000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B7" s="37">
         <v>12600000</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C7" s="37">
         <v>16800000</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D7" s="37">
         <v>19600000</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E7" s="37">
         <v>19500000</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F7" s="37">
         <v>19500000</v>
       </c>
-      <c r="G2" s="37">
+      <c r="G7" s="37">
         <v>19200000</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H7" s="37">
         <v>19600000</v>
       </c>
-      <c r="I2" s="37">
+      <c r="I7" s="37">
         <v>19300000</v>
       </c>
-      <c r="J2" s="37">
+      <c r="J7" s="37">
         <v>19600000</v>
       </c>
-      <c r="K2" s="37">
+      <c r="K7" s="37">
         <v>19900000</v>
       </c>
-      <c r="L2" s="37">
-        <f>AVERAGE(J2:K2)</f>
-        <v>19750000</v>
-      </c>
-      <c r="M2" s="37">
-        <f t="shared" ref="M2:P2" si="0">AVERAGE(K2:L2)</f>
-        <v>19825000</v>
-      </c>
-      <c r="N2" s="37">
-        <f t="shared" si="0"/>
-        <v>19787500</v>
-      </c>
-      <c r="O2" s="37">
-        <f t="shared" si="0"/>
-        <v>19806250</v>
-      </c>
-      <c r="P2" s="37">
-        <f t="shared" si="0"/>
-        <v>19796875</v>
-      </c>
-      <c r="Q2" s="37">
-        <f t="shared" ref="Q2:Q18" si="1">AVERAGE(O2:P2)</f>
-        <v>19801562.5</v>
-      </c>
-      <c r="R2" s="37">
-        <f t="shared" ref="R2:R18" si="2">AVERAGE(P2:Q2)</f>
-        <v>19799218.75</v>
-      </c>
-      <c r="S2" s="37">
-        <f t="shared" ref="S2:S18" si="3">AVERAGE(Q2:R2)</f>
-        <v>19800390.625</v>
-      </c>
-      <c r="T2" s="37">
-        <f t="shared" ref="T2:T18" si="4">AVERAGE(R2:S2)</f>
-        <v>19799804.6875</v>
-      </c>
-      <c r="U2" s="37">
-        <f t="shared" ref="U2:U18" si="5">AVERAGE(S2:T2)</f>
-        <v>19800097.65625</v>
-      </c>
-      <c r="V2" s="37">
-        <f t="shared" ref="V2:V18" si="6">AVERAGE(T2:U2)</f>
-        <v>19799951.171875</v>
-      </c>
-      <c r="W2" s="37">
-        <f t="shared" ref="W2:W18" si="7">AVERAGE(U2:V2)</f>
-        <v>19800024.4140625</v>
-      </c>
-      <c r="X2" s="37">
-        <f t="shared" ref="X2:X18" si="8">AVERAGE(V2:W2)</f>
-        <v>19799987.79296875</v>
-      </c>
-      <c r="Y2" s="37">
-        <f t="shared" ref="Y2:Y18" si="9">AVERAGE(W2:X2)</f>
-        <v>19800006.103515625</v>
-      </c>
-      <c r="Z2" s="37">
-        <f t="shared" ref="Z2:Z18" si="10">AVERAGE(X2:Y2)</f>
-        <v>19799996.948242188</v>
-      </c>
-      <c r="AA2" s="37">
-        <f t="shared" ref="AA2:AA18" si="11">AVERAGE(Y2:Z2)</f>
-        <v>19800001.525878906</v>
-      </c>
-      <c r="AB2" s="37">
-        <f t="shared" ref="AB2:AB18" si="12">AVERAGE(Z2:AA2)</f>
-        <v>19799999.237060547</v>
-      </c>
-      <c r="AC2" s="37">
-        <f t="shared" ref="AC2:AC18" si="13">AVERAGE(AA2:AB2)</f>
-        <v>19800000.381469727</v>
-      </c>
-      <c r="AD2" s="37">
-        <f t="shared" ref="AD2:AD18" si="14">AVERAGE(AB2:AC2)</f>
-        <v>19799999.809265137</v>
-      </c>
-      <c r="AE2" s="37">
-        <f t="shared" ref="AE2:AE18" si="15">AVERAGE(AC2:AD2)</f>
-        <v>19800000.095367432</v>
-      </c>
-      <c r="AF2" s="37">
-        <f t="shared" ref="AF2:AF18" si="16">AVERAGE(AD2:AE2)</f>
-        <v>19799999.952316284</v>
-      </c>
-      <c r="AG2" s="37">
-        <f t="shared" ref="AG2:AG18" si="17">AVERAGE(AE2:AF2)</f>
-        <v>19800000.023841858</v>
-      </c>
-      <c r="AH2" s="37">
-        <f t="shared" ref="AH2:AH18" si="18">AVERAGE(AF2:AG2)</f>
-        <v>19799999.988079071</v>
-      </c>
-      <c r="AI2" s="37">
-        <f t="shared" ref="AI2:AI18" si="19">AVERAGE(AG2:AH2)</f>
-        <v>19800000.005960464</v>
-      </c>
-      <c r="AJ2" s="37">
-        <f t="shared" ref="AJ2:AJ18" si="20">AVERAGE(AH2:AI2)</f>
-        <v>19799999.997019768</v>
-      </c>
-      <c r="AK2" s="37">
-        <f t="shared" ref="AK2:AK18" si="21">AVERAGE(AI2:AJ2)</f>
-        <v>19800000.001490116</v>
-      </c>
-      <c r="AL2" s="37">
-        <f t="shared" ref="AL2:AL18" si="22">AVERAGE(AJ2:AK2)</f>
-        <v>19799999.999254942</v>
-      </c>
-      <c r="AM2" s="37">
-        <f t="shared" ref="AM2:AM18" si="23">AVERAGE(AK2:AL2)</f>
-        <v>19800000.000372529</v>
-      </c>
-      <c r="AN2" s="37">
-        <f t="shared" ref="AN2:AN18" si="24">AVERAGE(AL2:AM2)</f>
-        <v>19799999.999813735</v>
-      </c>
-      <c r="AO2" s="37">
-        <f t="shared" ref="AO2:AO18" si="25">AVERAGE(AM2:AN2)</f>
-        <v>19800000.000093132</v>
-      </c>
-      <c r="AP2" s="37">
-        <f t="shared" ref="AP2:AP18" si="26">AVERAGE(AN2:AO2)</f>
-        <v>19799999.999953434</v>
-      </c>
-      <c r="AQ2" s="37">
-        <f t="shared" ref="AQ2:AQ18" si="27">AVERAGE(AO2:AP2)</f>
-        <v>19800000.000023283</v>
-      </c>
-      <c r="AR2" s="37">
-        <f t="shared" ref="AR2:AR18" si="28">AVERAGE(AP2:AQ2)</f>
-        <v>19799999.999988358</v>
-      </c>
-      <c r="AS2" s="37">
-        <f t="shared" ref="AS2:AS18" si="29">AVERAGE(AQ2:AR2)</f>
-        <v>19800000.000005819</v>
-      </c>
-      <c r="AT2" s="37">
-        <f t="shared" ref="AT2:AT18" si="30">AVERAGE(AR2:AS2)</f>
-        <v>19799999.999997087</v>
-      </c>
-      <c r="AU2" s="37">
-        <f t="shared" ref="AU2:AU18" si="31">AVERAGE(AS2:AT2)</f>
-        <v>19800000.000001453</v>
-      </c>
-      <c r="AV2" s="37">
-        <f t="shared" ref="AV2:AV18" si="32">AVERAGE(AT2:AU2)</f>
-        <v>19799999.99999927</v>
-      </c>
-      <c r="AW2" s="37">
-        <f t="shared" ref="AW2:AW18" si="33">AVERAGE(AU2:AV2)</f>
-        <v>19800000.000000361</v>
-      </c>
-      <c r="AX2" s="37">
-        <f t="shared" ref="AX2:AX18" si="34">AVERAGE(AV2:AW2)</f>
-        <v>19799999.999999814</v>
-      </c>
-      <c r="AY2" s="37">
-        <f t="shared" ref="AY2:AY18" si="35">AVERAGE(AW2:AX2)</f>
-        <v>19800000.000000089</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="37">
-        <v>24300000</v>
-      </c>
-      <c r="C3" s="37">
-        <v>26300000</v>
-      </c>
-      <c r="D3" s="37">
-        <v>26500000</v>
-      </c>
-      <c r="E3" s="37">
-        <v>25000000</v>
-      </c>
-      <c r="F3" s="37">
-        <v>24900000</v>
-      </c>
-      <c r="G3" s="37">
-        <v>24700000</v>
-      </c>
-      <c r="H3" s="37">
-        <v>25000000</v>
-      </c>
-      <c r="I3" s="37">
-        <v>24800000</v>
-      </c>
-      <c r="J3" s="37">
-        <v>25100000</v>
-      </c>
-      <c r="K3" s="37">
-        <v>25400000</v>
-      </c>
-      <c r="L3" s="37">
-        <f t="shared" ref="L3:L17" si="36">AVERAGE(J3:K3)</f>
-        <v>25250000</v>
-      </c>
-      <c r="M3" s="37">
-        <f t="shared" ref="M3:M18" si="37">AVERAGE(K3:L3)</f>
-        <v>25325000</v>
-      </c>
-      <c r="N3" s="37">
-        <f t="shared" ref="N3:N18" si="38">AVERAGE(L3:M3)</f>
-        <v>25287500</v>
-      </c>
-      <c r="O3" s="37">
-        <f t="shared" ref="O3:O18" si="39">AVERAGE(M3:N3)</f>
-        <v>25306250</v>
-      </c>
-      <c r="P3" s="37">
-        <f t="shared" ref="P3:P18" si="40">AVERAGE(N3:O3)</f>
-        <v>25296875</v>
-      </c>
-      <c r="Q3" s="37">
-        <f t="shared" si="1"/>
-        <v>25301562.5</v>
-      </c>
-      <c r="R3" s="37">
-        <f t="shared" si="2"/>
-        <v>25299218.75</v>
-      </c>
-      <c r="S3" s="37">
-        <f t="shared" si="3"/>
-        <v>25300390.625</v>
-      </c>
-      <c r="T3" s="37">
-        <f t="shared" si="4"/>
-        <v>25299804.6875</v>
-      </c>
-      <c r="U3" s="37">
-        <f t="shared" si="5"/>
-        <v>25300097.65625</v>
-      </c>
-      <c r="V3" s="37">
-        <f t="shared" si="6"/>
-        <v>25299951.171875</v>
-      </c>
-      <c r="W3" s="37">
-        <f t="shared" si="7"/>
-        <v>25300024.4140625</v>
-      </c>
-      <c r="X3" s="37">
-        <f t="shared" si="8"/>
-        <v>25299987.79296875</v>
-      </c>
-      <c r="Y3" s="37">
-        <f t="shared" si="9"/>
-        <v>25300006.103515625</v>
-      </c>
-      <c r="Z3" s="37">
-        <f t="shared" si="10"/>
-        <v>25299996.948242188</v>
-      </c>
-      <c r="AA3" s="37">
-        <f t="shared" si="11"/>
-        <v>25300001.525878906</v>
-      </c>
-      <c r="AB3" s="37">
-        <f t="shared" si="12"/>
-        <v>25299999.237060547</v>
-      </c>
-      <c r="AC3" s="37">
-        <f t="shared" si="13"/>
-        <v>25300000.381469727</v>
-      </c>
-      <c r="AD3" s="37">
-        <f t="shared" si="14"/>
-        <v>25299999.809265137</v>
-      </c>
-      <c r="AE3" s="37">
-        <f t="shared" si="15"/>
-        <v>25300000.095367432</v>
-      </c>
-      <c r="AF3" s="37">
-        <f t="shared" si="16"/>
-        <v>25299999.952316284</v>
-      </c>
-      <c r="AG3" s="37">
-        <f t="shared" si="17"/>
-        <v>25300000.023841858</v>
-      </c>
-      <c r="AH3" s="37">
-        <f t="shared" si="18"/>
-        <v>25299999.988079071</v>
-      </c>
-      <c r="AI3" s="37">
-        <f t="shared" si="19"/>
-        <v>25300000.005960464</v>
-      </c>
-      <c r="AJ3" s="37">
-        <f t="shared" si="20"/>
-        <v>25299999.997019768</v>
-      </c>
-      <c r="AK3" s="37">
-        <f t="shared" si="21"/>
-        <v>25300000.001490116</v>
-      </c>
-      <c r="AL3" s="37">
-        <f t="shared" si="22"/>
-        <v>25299999.999254942</v>
-      </c>
-      <c r="AM3" s="37">
-        <f t="shared" si="23"/>
-        <v>25300000.000372529</v>
-      </c>
-      <c r="AN3" s="37">
-        <f t="shared" si="24"/>
-        <v>25299999.999813735</v>
-      </c>
-      <c r="AO3" s="37">
-        <f t="shared" si="25"/>
-        <v>25300000.000093132</v>
-      </c>
-      <c r="AP3" s="37">
-        <f t="shared" si="26"/>
-        <v>25299999.999953434</v>
-      </c>
-      <c r="AQ3" s="37">
-        <f t="shared" si="27"/>
-        <v>25300000.000023283</v>
-      </c>
-      <c r="AR3" s="37">
-        <f t="shared" si="28"/>
-        <v>25299999.999988358</v>
-      </c>
-      <c r="AS3" s="37">
-        <f t="shared" si="29"/>
-        <v>25300000.000005819</v>
-      </c>
-      <c r="AT3" s="37">
-        <f t="shared" si="30"/>
-        <v>25299999.999997087</v>
-      </c>
-      <c r="AU3" s="37">
-        <f t="shared" si="31"/>
-        <v>25300000.000001453</v>
-      </c>
-      <c r="AV3" s="37">
-        <f t="shared" si="32"/>
-        <v>25299999.99999927</v>
-      </c>
-      <c r="AW3" s="37">
-        <f t="shared" si="33"/>
-        <v>25300000.000000361</v>
-      </c>
-      <c r="AX3" s="37">
-        <f t="shared" si="34"/>
-        <v>25299999.999999814</v>
-      </c>
-      <c r="AY3" s="37">
-        <f t="shared" si="35"/>
-        <v>25300000.000000089</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B8" s="37">
+        <v>243000000</v>
+      </c>
+      <c r="C8" s="37">
+        <v>263000000</v>
+      </c>
+      <c r="D8" s="37">
+        <v>265000000</v>
+      </c>
+      <c r="E8" s="37">
+        <v>250000000</v>
+      </c>
+      <c r="F8" s="37">
+        <v>249000000</v>
+      </c>
+      <c r="G8" s="37">
+        <v>247000000</v>
+      </c>
+      <c r="H8" s="37">
+        <v>250000000</v>
+      </c>
+      <c r="I8" s="37">
+        <v>248000000</v>
+      </c>
+      <c r="J8" s="37">
+        <v>251000000</v>
+      </c>
+      <c r="K8" s="37">
+        <v>254000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B9" s="37">
         <v>8000000</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C9" s="37">
         <v>8600000</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D9" s="37">
         <v>8700000</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E9" s="37">
         <v>8400000</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F9" s="37">
         <v>8400000</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G9" s="37">
         <v>8100000</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H9" s="38">
         <v>8300000</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I9" s="38">
         <v>8200000</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J9" s="38">
         <v>8200000</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K9" s="38">
         <v>8200000</v>
       </c>
-      <c r="L4" s="37">
-        <f t="shared" si="36"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="37">
+        <v>36000000</v>
+      </c>
+      <c r="C10" s="37">
+        <v>39500000</v>
+      </c>
+      <c r="D10" s="37">
+        <v>40500000</v>
+      </c>
+      <c r="E10" s="37">
+        <v>40200000</v>
+      </c>
+      <c r="F10" s="37">
+        <v>41100000</v>
+      </c>
+      <c r="G10" s="37">
+        <v>40500000</v>
+      </c>
+      <c r="H10" s="38">
+        <v>41300000</v>
+      </c>
+      <c r="I10" s="38">
+        <v>40900000</v>
+      </c>
+      <c r="J10" s="38">
+        <v>41200000</v>
+      </c>
+      <c r="K10" s="38">
+        <v>41300000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="37">
+        <v>8400000</v>
+      </c>
+      <c r="C11" s="37">
+        <v>11200000</v>
+      </c>
+      <c r="D11" s="37">
+        <v>13100000</v>
+      </c>
+      <c r="E11" s="37">
+        <v>13000000</v>
+      </c>
+      <c r="F11" s="37">
+        <v>13000000</v>
+      </c>
+      <c r="G11" s="37">
+        <v>12800000</v>
+      </c>
+      <c r="H11" s="37">
+        <v>13100000</v>
+      </c>
+      <c r="I11" s="37">
+        <v>12900000</v>
+      </c>
+      <c r="J11" s="37">
+        <v>13100000</v>
+      </c>
+      <c r="K11" s="37">
+        <v>13300000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="37">
+        <v>30000</v>
+      </c>
+      <c r="C12" s="37">
+        <v>25000</v>
+      </c>
+      <c r="D12" s="37">
+        <v>21000</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="38">
+        <v>0</v>
+      </c>
+      <c r="G12" s="38">
+        <v>0</v>
+      </c>
+      <c r="H12" s="38">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38">
+        <v>0</v>
+      </c>
+      <c r="J12" s="38">
+        <v>0</v>
+      </c>
+      <c r="K12" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="37">
+        <v>8000000</v>
+      </c>
+      <c r="C13" s="37">
+        <v>8600000</v>
+      </c>
+      <c r="D13" s="37">
+        <v>8700000</v>
+      </c>
+      <c r="E13" s="37">
+        <v>8400000</v>
+      </c>
+      <c r="F13" s="37">
+        <v>8400000</v>
+      </c>
+      <c r="G13" s="37">
+        <v>8100000</v>
+      </c>
+      <c r="H13" s="37">
+        <v>8300000</v>
+      </c>
+      <c r="I13" s="37">
         <v>8200000</v>
       </c>
-      <c r="M4" s="37">
-        <f t="shared" si="37"/>
+      <c r="J13" s="37">
         <v>8200000</v>
       </c>
-      <c r="N4" s="37">
-        <f t="shared" si="38"/>
+      <c r="K13" s="37">
         <v>8200000</v>
       </c>
-      <c r="O4" s="37">
-        <f t="shared" si="39"/>
-        <v>8200000</v>
-      </c>
-      <c r="P4" s="37">
-        <f t="shared" si="40"/>
-        <v>8200000</v>
-      </c>
-      <c r="Q4" s="37">
-        <f t="shared" si="1"/>
-        <v>8200000</v>
-      </c>
-      <c r="R4" s="37">
-        <f t="shared" si="2"/>
-        <v>8200000</v>
-      </c>
-      <c r="S4" s="37">
-        <f t="shared" si="3"/>
-        <v>8200000</v>
-      </c>
-      <c r="T4" s="37">
-        <f t="shared" si="4"/>
-        <v>8200000</v>
-      </c>
-      <c r="U4" s="37">
-        <f t="shared" si="5"/>
-        <v>8200000</v>
-      </c>
-      <c r="V4" s="37">
-        <f t="shared" si="6"/>
-        <v>8200000</v>
-      </c>
-      <c r="W4" s="37">
-        <f t="shared" si="7"/>
-        <v>8200000</v>
-      </c>
-      <c r="X4" s="37">
-        <f t="shared" si="8"/>
-        <v>8200000</v>
-      </c>
-      <c r="Y4" s="37">
-        <f t="shared" si="9"/>
-        <v>8200000</v>
-      </c>
-      <c r="Z4" s="37">
-        <f t="shared" si="10"/>
-        <v>8200000</v>
-      </c>
-      <c r="AA4" s="37">
-        <f t="shared" si="11"/>
-        <v>8200000</v>
-      </c>
-      <c r="AB4" s="37">
-        <f t="shared" si="12"/>
-        <v>8200000</v>
-      </c>
-      <c r="AC4" s="37">
-        <f t="shared" si="13"/>
-        <v>8200000</v>
-      </c>
-      <c r="AD4" s="37">
-        <f t="shared" si="14"/>
-        <v>8200000</v>
-      </c>
-      <c r="AE4" s="37">
-        <f t="shared" si="15"/>
-        <v>8200000</v>
-      </c>
-      <c r="AF4" s="37">
-        <f t="shared" si="16"/>
-        <v>8200000</v>
-      </c>
-      <c r="AG4" s="37">
-        <f t="shared" si="17"/>
-        <v>8200000</v>
-      </c>
-      <c r="AH4" s="37">
-        <f t="shared" si="18"/>
-        <v>8200000</v>
-      </c>
-      <c r="AI4" s="37">
-        <f t="shared" si="19"/>
-        <v>8200000</v>
-      </c>
-      <c r="AJ4" s="37">
-        <f t="shared" si="20"/>
-        <v>8200000</v>
-      </c>
-      <c r="AK4" s="37">
-        <f t="shared" si="21"/>
-        <v>8200000</v>
-      </c>
-      <c r="AL4" s="37">
-        <f t="shared" si="22"/>
-        <v>8200000</v>
-      </c>
-      <c r="AM4" s="37">
-        <f t="shared" si="23"/>
-        <v>8200000</v>
-      </c>
-      <c r="AN4" s="37">
-        <f t="shared" si="24"/>
-        <v>8200000</v>
-      </c>
-      <c r="AO4" s="37">
-        <f t="shared" si="25"/>
-        <v>8200000</v>
-      </c>
-      <c r="AP4" s="37">
-        <f t="shared" si="26"/>
-        <v>8200000</v>
-      </c>
-      <c r="AQ4" s="37">
-        <f t="shared" si="27"/>
-        <v>8200000</v>
-      </c>
-      <c r="AR4" s="37">
-        <f t="shared" si="28"/>
-        <v>8200000</v>
-      </c>
-      <c r="AS4" s="37">
-        <f t="shared" si="29"/>
-        <v>8200000</v>
-      </c>
-      <c r="AT4" s="37">
-        <f t="shared" si="30"/>
-        <v>8200000</v>
-      </c>
-      <c r="AU4" s="37">
-        <f t="shared" si="31"/>
-        <v>8200000</v>
-      </c>
-      <c r="AV4" s="37">
-        <f t="shared" si="32"/>
-        <v>8200000</v>
-      </c>
-      <c r="AW4" s="37">
-        <f t="shared" si="33"/>
-        <v>8200000</v>
-      </c>
-      <c r="AX4" s="37">
-        <f t="shared" si="34"/>
-        <v>8200000</v>
-      </c>
-      <c r="AY4" s="37">
-        <f t="shared" si="35"/>
-        <v>8200000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="37">
-        <v>36000000</v>
-      </c>
-      <c r="C5" s="37">
-        <v>39500000</v>
-      </c>
-      <c r="D5" s="37">
-        <v>40500000</v>
-      </c>
-      <c r="E5" s="37">
-        <v>40200000</v>
-      </c>
-      <c r="F5" s="37">
-        <v>41100000</v>
-      </c>
-      <c r="G5" s="37">
-        <v>40500000</v>
-      </c>
-      <c r="H5" s="38">
-        <v>41300000</v>
-      </c>
-      <c r="I5" s="38">
-        <v>40900000</v>
-      </c>
-      <c r="J5" s="38">
-        <v>41200000</v>
-      </c>
-      <c r="K5" s="38">
-        <v>41300000</v>
-      </c>
-      <c r="L5" s="37">
-        <f t="shared" si="36"/>
-        <v>41250000</v>
-      </c>
-      <c r="M5" s="37">
-        <f t="shared" si="37"/>
-        <v>41275000</v>
-      </c>
-      <c r="N5" s="37">
-        <f t="shared" si="38"/>
-        <v>41262500</v>
-      </c>
-      <c r="O5" s="37">
-        <f t="shared" si="39"/>
-        <v>41268750</v>
-      </c>
-      <c r="P5" s="37">
-        <f t="shared" si="40"/>
-        <v>41265625</v>
-      </c>
-      <c r="Q5" s="37">
-        <f t="shared" si="1"/>
-        <v>41267187.5</v>
-      </c>
-      <c r="R5" s="37">
-        <f t="shared" si="2"/>
-        <v>41266406.25</v>
-      </c>
-      <c r="S5" s="37">
-        <f t="shared" si="3"/>
-        <v>41266796.875</v>
-      </c>
-      <c r="T5" s="37">
-        <f t="shared" si="4"/>
-        <v>41266601.5625</v>
-      </c>
-      <c r="U5" s="37">
-        <f t="shared" si="5"/>
-        <v>41266699.21875</v>
-      </c>
-      <c r="V5" s="37">
-        <f t="shared" si="6"/>
-        <v>41266650.390625</v>
-      </c>
-      <c r="W5" s="37">
-        <f t="shared" si="7"/>
-        <v>41266674.8046875</v>
-      </c>
-      <c r="X5" s="37">
-        <f t="shared" si="8"/>
-        <v>41266662.59765625</v>
-      </c>
-      <c r="Y5" s="37">
-        <f t="shared" si="9"/>
-        <v>41266668.701171875</v>
-      </c>
-      <c r="Z5" s="37">
-        <f t="shared" si="10"/>
-        <v>41266665.649414063</v>
-      </c>
-      <c r="AA5" s="37">
-        <f t="shared" si="11"/>
-        <v>41266667.175292969</v>
-      </c>
-      <c r="AB5" s="37">
-        <f t="shared" si="12"/>
-        <v>41266666.412353516</v>
-      </c>
-      <c r="AC5" s="37">
-        <f t="shared" si="13"/>
-        <v>41266666.793823242</v>
-      </c>
-      <c r="AD5" s="37">
-        <f t="shared" si="14"/>
-        <v>41266666.603088379</v>
-      </c>
-      <c r="AE5" s="37">
-        <f t="shared" si="15"/>
-        <v>41266666.698455811</v>
-      </c>
-      <c r="AF5" s="37">
-        <f t="shared" si="16"/>
-        <v>41266666.650772095</v>
-      </c>
-      <c r="AG5" s="37">
-        <f t="shared" si="17"/>
-        <v>41266666.674613953</v>
-      </c>
-      <c r="AH5" s="37">
-        <f t="shared" si="18"/>
-        <v>41266666.662693024</v>
-      </c>
-      <c r="AI5" s="37">
-        <f t="shared" si="19"/>
-        <v>41266666.668653488</v>
-      </c>
-      <c r="AJ5" s="37">
-        <f t="shared" si="20"/>
-        <v>41266666.665673256</v>
-      </c>
-      <c r="AK5" s="37">
-        <f t="shared" si="21"/>
-        <v>41266666.667163372</v>
-      </c>
-      <c r="AL5" s="37">
-        <f t="shared" si="22"/>
-        <v>41266666.666418314</v>
-      </c>
-      <c r="AM5" s="37">
-        <f t="shared" si="23"/>
-        <v>41266666.666790843</v>
-      </c>
-      <c r="AN5" s="37">
-        <f t="shared" si="24"/>
-        <v>41266666.666604578</v>
-      </c>
-      <c r="AO5" s="37">
-        <f t="shared" si="25"/>
-        <v>41266666.666697711</v>
-      </c>
-      <c r="AP5" s="37">
-        <f t="shared" si="26"/>
-        <v>41266666.666651145</v>
-      </c>
-      <c r="AQ5" s="37">
-        <f t="shared" si="27"/>
-        <v>41266666.666674428</v>
-      </c>
-      <c r="AR5" s="37">
-        <f t="shared" si="28"/>
-        <v>41266666.666662782</v>
-      </c>
-      <c r="AS5" s="37">
-        <f t="shared" si="29"/>
-        <v>41266666.666668609</v>
-      </c>
-      <c r="AT5" s="37">
-        <f t="shared" si="30"/>
-        <v>41266666.666665696</v>
-      </c>
-      <c r="AU5" s="37">
-        <f t="shared" si="31"/>
-        <v>41266666.666667148</v>
-      </c>
-      <c r="AV5" s="37">
-        <f t="shared" si="32"/>
-        <v>41266666.666666418</v>
-      </c>
-      <c r="AW5" s="37">
-        <f t="shared" si="33"/>
-        <v>41266666.666666783</v>
-      </c>
-      <c r="AX5" s="37">
-        <f t="shared" si="34"/>
-        <v>41266666.666666597</v>
-      </c>
-      <c r="AY5" s="37">
-        <f t="shared" si="35"/>
-        <v>41266666.666666687</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="37">
-        <v>8400000</v>
-      </c>
-      <c r="C6" s="37">
-        <v>11200000</v>
-      </c>
-      <c r="D6" s="37">
-        <v>13100000</v>
-      </c>
-      <c r="E6" s="37">
-        <v>13000000</v>
-      </c>
-      <c r="F6" s="37">
-        <v>13000000</v>
-      </c>
-      <c r="G6" s="37">
-        <v>12800000</v>
-      </c>
-      <c r="H6" s="37">
-        <v>13100000</v>
-      </c>
-      <c r="I6" s="37">
-        <v>12900000</v>
-      </c>
-      <c r="J6" s="37">
-        <v>13100000</v>
-      </c>
-      <c r="K6" s="37">
-        <v>13300000</v>
-      </c>
-      <c r="L6" s="37">
-        <f t="shared" si="36"/>
-        <v>13200000</v>
-      </c>
-      <c r="M6" s="37">
-        <f t="shared" si="37"/>
-        <v>13250000</v>
-      </c>
-      <c r="N6" s="37">
-        <f t="shared" si="38"/>
-        <v>13225000</v>
-      </c>
-      <c r="O6" s="37">
-        <f t="shared" si="39"/>
-        <v>13237500</v>
-      </c>
-      <c r="P6" s="37">
-        <f t="shared" si="40"/>
-        <v>13231250</v>
-      </c>
-      <c r="Q6" s="37">
-        <f t="shared" si="1"/>
-        <v>13234375</v>
-      </c>
-      <c r="R6" s="37">
-        <f t="shared" si="2"/>
-        <v>13232812.5</v>
-      </c>
-      <c r="S6" s="37">
-        <f t="shared" si="3"/>
-        <v>13233593.75</v>
-      </c>
-      <c r="T6" s="37">
-        <f t="shared" si="4"/>
-        <v>13233203.125</v>
-      </c>
-      <c r="U6" s="37">
-        <f t="shared" si="5"/>
-        <v>13233398.4375</v>
-      </c>
-      <c r="V6" s="37">
-        <f t="shared" si="6"/>
-        <v>13233300.78125</v>
-      </c>
-      <c r="W6" s="37">
-        <f t="shared" si="7"/>
-        <v>13233349.609375</v>
-      </c>
-      <c r="X6" s="37">
-        <f t="shared" si="8"/>
-        <v>13233325.1953125</v>
-      </c>
-      <c r="Y6" s="37">
-        <f t="shared" si="9"/>
-        <v>13233337.40234375</v>
-      </c>
-      <c r="Z6" s="37">
-        <f t="shared" si="10"/>
-        <v>13233331.298828125</v>
-      </c>
-      <c r="AA6" s="37">
-        <f t="shared" si="11"/>
-        <v>13233334.350585938</v>
-      </c>
-      <c r="AB6" s="37">
-        <f t="shared" si="12"/>
-        <v>13233332.824707031</v>
-      </c>
-      <c r="AC6" s="37">
-        <f t="shared" si="13"/>
-        <v>13233333.587646484</v>
-      </c>
-      <c r="AD6" s="37">
-        <f t="shared" si="14"/>
-        <v>13233333.206176758</v>
-      </c>
-      <c r="AE6" s="37">
-        <f t="shared" si="15"/>
-        <v>13233333.396911621</v>
-      </c>
-      <c r="AF6" s="37">
-        <f t="shared" si="16"/>
-        <v>13233333.301544189</v>
-      </c>
-      <c r="AG6" s="37">
-        <f t="shared" si="17"/>
-        <v>13233333.349227905</v>
-      </c>
-      <c r="AH6" s="37">
-        <f t="shared" si="18"/>
-        <v>13233333.325386047</v>
-      </c>
-      <c r="AI6" s="37">
-        <f t="shared" si="19"/>
-        <v>13233333.337306976</v>
-      </c>
-      <c r="AJ6" s="37">
-        <f t="shared" si="20"/>
-        <v>13233333.331346512</v>
-      </c>
-      <c r="AK6" s="37">
-        <f t="shared" si="21"/>
-        <v>13233333.334326744</v>
-      </c>
-      <c r="AL6" s="37">
-        <f t="shared" si="22"/>
-        <v>13233333.332836628</v>
-      </c>
-      <c r="AM6" s="37">
-        <f t="shared" si="23"/>
-        <v>13233333.333581686</v>
-      </c>
-      <c r="AN6" s="37">
-        <f t="shared" si="24"/>
-        <v>13233333.333209157</v>
-      </c>
-      <c r="AO6" s="37">
-        <f t="shared" si="25"/>
-        <v>13233333.333395422</v>
-      </c>
-      <c r="AP6" s="37">
-        <f t="shared" si="26"/>
-        <v>13233333.333302289</v>
-      </c>
-      <c r="AQ6" s="37">
-        <f t="shared" si="27"/>
-        <v>13233333.333348855</v>
-      </c>
-      <c r="AR6" s="37">
-        <f t="shared" si="28"/>
-        <v>13233333.333325572</v>
-      </c>
-      <c r="AS6" s="37">
-        <f t="shared" si="29"/>
-        <v>13233333.333337214</v>
-      </c>
-      <c r="AT6" s="37">
-        <f t="shared" si="30"/>
-        <v>13233333.333331393</v>
-      </c>
-      <c r="AU6" s="37">
-        <f t="shared" si="31"/>
-        <v>13233333.333334304</v>
-      </c>
-      <c r="AV6" s="37">
-        <f t="shared" si="32"/>
-        <v>13233333.333332848</v>
-      </c>
-      <c r="AW6" s="37">
-        <f t="shared" si="33"/>
-        <v>13233333.333333576</v>
-      </c>
-      <c r="AX6" s="37">
-        <f t="shared" si="34"/>
-        <v>13233333.333333213</v>
-      </c>
-      <c r="AY6" s="37">
-        <f t="shared" si="35"/>
-        <v>13233333.333333395</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="37">
-        <v>160100000</v>
-      </c>
-      <c r="C7" s="37">
-        <v>140800000</v>
-      </c>
-      <c r="D7" s="37">
-        <v>154800000</v>
-      </c>
-      <c r="E7" s="37">
-        <v>143800000</v>
-      </c>
-      <c r="F7" s="37">
-        <v>147500000</v>
-      </c>
-      <c r="G7" s="37">
-        <v>171200000</v>
-      </c>
-      <c r="H7" s="37">
-        <v>139700000</v>
-      </c>
-      <c r="I7" s="37">
-        <v>172900000</v>
-      </c>
-      <c r="J7" s="37">
-        <v>149300000</v>
-      </c>
-      <c r="K7" s="37">
-        <v>158400000</v>
-      </c>
-      <c r="L7" s="37">
-        <f t="shared" si="36"/>
-        <v>153850000</v>
-      </c>
-      <c r="M7" s="37">
-        <f t="shared" si="37"/>
-        <v>156125000</v>
-      </c>
-      <c r="N7" s="37">
-        <f t="shared" si="38"/>
-        <v>154987500</v>
-      </c>
-      <c r="O7" s="37">
-        <f t="shared" si="39"/>
-        <v>155556250</v>
-      </c>
-      <c r="P7" s="37">
-        <f t="shared" si="40"/>
-        <v>155271875</v>
-      </c>
-      <c r="Q7" s="37">
-        <f t="shared" si="1"/>
-        <v>155414062.5</v>
-      </c>
-      <c r="R7" s="37">
-        <f t="shared" si="2"/>
-        <v>155342968.75</v>
-      </c>
-      <c r="S7" s="37">
-        <f t="shared" si="3"/>
-        <v>155378515.625</v>
-      </c>
-      <c r="T7" s="37">
-        <f t="shared" si="4"/>
-        <v>155360742.1875</v>
-      </c>
-      <c r="U7" s="37">
-        <f t="shared" si="5"/>
-        <v>155369628.90625</v>
-      </c>
-      <c r="V7" s="37">
-        <f t="shared" si="6"/>
-        <v>155365185.546875</v>
-      </c>
-      <c r="W7" s="37">
-        <f t="shared" si="7"/>
-        <v>155367407.2265625</v>
-      </c>
-      <c r="X7" s="37">
-        <f t="shared" si="8"/>
-        <v>155366296.38671875</v>
-      </c>
-      <c r="Y7" s="37">
-        <f t="shared" si="9"/>
-        <v>155366851.80664063</v>
-      </c>
-      <c r="Z7" s="37">
-        <f t="shared" si="10"/>
-        <v>155366574.09667969</v>
-      </c>
-      <c r="AA7" s="37">
-        <f t="shared" si="11"/>
-        <v>155366712.95166016</v>
-      </c>
-      <c r="AB7" s="37">
-        <f t="shared" si="12"/>
-        <v>155366643.52416992</v>
-      </c>
-      <c r="AC7" s="37">
-        <f t="shared" si="13"/>
-        <v>155366678.23791504</v>
-      </c>
-      <c r="AD7" s="37">
-        <f t="shared" si="14"/>
-        <v>155366660.88104248</v>
-      </c>
-      <c r="AE7" s="37">
-        <f t="shared" si="15"/>
-        <v>155366669.55947876</v>
-      </c>
-      <c r="AF7" s="37">
-        <f t="shared" si="16"/>
-        <v>155366665.22026062</v>
-      </c>
-      <c r="AG7" s="37">
-        <f t="shared" si="17"/>
-        <v>155366667.38986969</v>
-      </c>
-      <c r="AH7" s="37">
-        <f t="shared" si="18"/>
-        <v>155366666.30506516</v>
-      </c>
-      <c r="AI7" s="37">
-        <f t="shared" si="19"/>
-        <v>155366666.84746742</v>
-      </c>
-      <c r="AJ7" s="37">
-        <f t="shared" si="20"/>
-        <v>155366666.57626629</v>
-      </c>
-      <c r="AK7" s="37">
-        <f t="shared" si="21"/>
-        <v>155366666.71186686</v>
-      </c>
-      <c r="AL7" s="37">
-        <f t="shared" si="22"/>
-        <v>155366666.64406657</v>
-      </c>
-      <c r="AM7" s="37">
-        <f t="shared" si="23"/>
-        <v>155366666.67796671</v>
-      </c>
-      <c r="AN7" s="37">
-        <f t="shared" si="24"/>
-        <v>155366666.66101664</v>
-      </c>
-      <c r="AO7" s="37">
-        <f t="shared" si="25"/>
-        <v>155366666.66949168</v>
-      </c>
-      <c r="AP7" s="37">
-        <f t="shared" si="26"/>
-        <v>155366666.66525418</v>
-      </c>
-      <c r="AQ7" s="37">
-        <f t="shared" si="27"/>
-        <v>155366666.66737294</v>
-      </c>
-      <c r="AR7" s="37">
-        <f t="shared" si="28"/>
-        <v>155366666.66631356</v>
-      </c>
-      <c r="AS7" s="37">
-        <f t="shared" si="29"/>
-        <v>155366666.66684324</v>
-      </c>
-      <c r="AT7" s="37">
-        <f t="shared" si="30"/>
-        <v>155366666.66657841</v>
-      </c>
-      <c r="AU7" s="37">
-        <f t="shared" si="31"/>
-        <v>155366666.66671082</v>
-      </c>
-      <c r="AV7" s="37">
-        <f t="shared" si="32"/>
-        <v>155366666.66664463</v>
-      </c>
-      <c r="AW7" s="37">
-        <f t="shared" si="33"/>
-        <v>155366666.66667771</v>
-      </c>
-      <c r="AX7" s="37">
-        <f t="shared" si="34"/>
-        <v>155366666.66666117</v>
-      </c>
-      <c r="AY7" s="37">
-        <f t="shared" si="35"/>
-        <v>155366666.66666943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="37">
-        <v>30000</v>
-      </c>
-      <c r="C8" s="37">
-        <v>25000</v>
-      </c>
-      <c r="D8" s="37">
-        <v>25000</v>
-      </c>
-      <c r="E8" s="38">
-        <v>0</v>
-      </c>
-      <c r="F8" s="38">
-        <v>0</v>
-      </c>
-      <c r="G8" s="38">
-        <v>0</v>
-      </c>
-      <c r="H8" s="38">
-        <v>0</v>
-      </c>
-      <c r="I8" s="38">
-        <v>0</v>
-      </c>
-      <c r="J8" s="38">
-        <v>0</v>
-      </c>
-      <c r="K8" s="38">
-        <v>0</v>
-      </c>
-      <c r="L8" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="37">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="37">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="37">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="37">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="37">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="37">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="37">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="37">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="37">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="37">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="37">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC8" s="37">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="37">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="37">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF8" s="37">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG8" s="37">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH8" s="37">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="37">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="37">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK8" s="37">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL8" s="37">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="37">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN8" s="37">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO8" s="37">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP8" s="37">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="37">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR8" s="37">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS8" s="37">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT8" s="37">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU8" s="37">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV8" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AW8" s="37">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AX8" s="37">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY8" s="37">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="37">
-        <v>1646350000</v>
-      </c>
-      <c r="C9" s="37">
-        <v>1824950000</v>
-      </c>
-      <c r="D9" s="37">
-        <v>1975050000</v>
-      </c>
-      <c r="E9" s="37">
-        <v>2271450000</v>
-      </c>
-      <c r="F9" s="37">
-        <v>2472850000</v>
-      </c>
-      <c r="G9" s="37">
-        <v>2252450000</v>
-      </c>
-      <c r="H9" s="37">
-        <v>2138450000</v>
-      </c>
-      <c r="I9" s="37">
-        <v>2088100000</v>
-      </c>
-      <c r="J9" s="37">
-        <v>2047250000</v>
-      </c>
-      <c r="K9" s="37">
-        <v>2069100000</v>
-      </c>
-      <c r="L9" s="37">
-        <f t="shared" si="36"/>
-        <v>2058175000</v>
-      </c>
-      <c r="M9" s="37">
-        <f t="shared" si="37"/>
-        <v>2063637500</v>
-      </c>
-      <c r="N9" s="37">
-        <f t="shared" si="38"/>
-        <v>2060906250</v>
-      </c>
-      <c r="O9" s="37">
-        <f t="shared" si="39"/>
-        <v>2062271875</v>
-      </c>
-      <c r="P9" s="37">
-        <f t="shared" si="40"/>
-        <v>2061589062.5</v>
-      </c>
-      <c r="Q9" s="37">
-        <f t="shared" si="1"/>
-        <v>2061930468.75</v>
-      </c>
-      <c r="R9" s="37">
-        <f t="shared" si="2"/>
-        <v>2061759765.625</v>
-      </c>
-      <c r="S9" s="37">
-        <f t="shared" si="3"/>
-        <v>2061845117.1875</v>
-      </c>
-      <c r="T9" s="37">
-        <f t="shared" si="4"/>
-        <v>2061802441.40625</v>
-      </c>
-      <c r="U9" s="37">
-        <f t="shared" si="5"/>
-        <v>2061823779.296875</v>
-      </c>
-      <c r="V9" s="37">
-        <f t="shared" si="6"/>
-        <v>2061813110.3515625</v>
-      </c>
-      <c r="W9" s="37">
-        <f t="shared" si="7"/>
-        <v>2061818444.8242188</v>
-      </c>
-      <c r="X9" s="37">
-        <f t="shared" si="8"/>
-        <v>2061815777.5878906</v>
-      </c>
-      <c r="Y9" s="37">
-        <f t="shared" si="9"/>
-        <v>2061817111.2060547</v>
-      </c>
-      <c r="Z9" s="37">
-        <f t="shared" si="10"/>
-        <v>2061816444.3969727</v>
-      </c>
-      <c r="AA9" s="37">
-        <f t="shared" si="11"/>
-        <v>2061816777.8015137</v>
-      </c>
-      <c r="AB9" s="37">
-        <f t="shared" si="12"/>
-        <v>2061816611.0992432</v>
-      </c>
-      <c r="AC9" s="37">
-        <f t="shared" si="13"/>
-        <v>2061816694.4503784</v>
-      </c>
-      <c r="AD9" s="37">
-        <f t="shared" si="14"/>
-        <v>2061816652.7748108</v>
-      </c>
-      <c r="AE9" s="37">
-        <f t="shared" si="15"/>
-        <v>2061816673.6125946</v>
-      </c>
-      <c r="AF9" s="37">
-        <f t="shared" si="16"/>
-        <v>2061816663.1937027</v>
-      </c>
-      <c r="AG9" s="37">
-        <f t="shared" si="17"/>
-        <v>2061816668.4031487</v>
-      </c>
-      <c r="AH9" s="37">
-        <f t="shared" si="18"/>
-        <v>2061816665.7984257</v>
-      </c>
-      <c r="AI9" s="37">
-        <f t="shared" si="19"/>
-        <v>2061816667.1007872</v>
-      </c>
-      <c r="AJ9" s="37">
-        <f t="shared" si="20"/>
-        <v>2061816666.4496064</v>
-      </c>
-      <c r="AK9" s="37">
-        <f t="shared" si="21"/>
-        <v>2061816666.7751968</v>
-      </c>
-      <c r="AL9" s="37">
-        <f t="shared" si="22"/>
-        <v>2061816666.6124015</v>
-      </c>
-      <c r="AM9" s="37">
-        <f t="shared" si="23"/>
-        <v>2061816666.693799</v>
-      </c>
-      <c r="AN9" s="37">
-        <f t="shared" si="24"/>
-        <v>2061816666.6531003</v>
-      </c>
-      <c r="AO9" s="37">
-        <f t="shared" si="25"/>
-        <v>2061816666.6734495</v>
-      </c>
-      <c r="AP9" s="37">
-        <f t="shared" si="26"/>
-        <v>2061816666.6632748</v>
-      </c>
-      <c r="AQ9" s="37">
-        <f t="shared" si="27"/>
-        <v>2061816666.6683621</v>
-      </c>
-      <c r="AR9" s="37">
-        <f t="shared" si="28"/>
-        <v>2061816666.6658185</v>
-      </c>
-      <c r="AS9" s="37">
-        <f t="shared" si="29"/>
-        <v>2061816666.6670904</v>
-      </c>
-      <c r="AT9" s="37">
-        <f t="shared" si="30"/>
-        <v>2061816666.6664543</v>
-      </c>
-      <c r="AU9" s="37">
-        <f t="shared" si="31"/>
-        <v>2061816666.6667724</v>
-      </c>
-      <c r="AV9" s="37">
-        <f t="shared" si="32"/>
-        <v>2061816666.6666133</v>
-      </c>
-      <c r="AW9" s="37">
-        <f t="shared" si="33"/>
-        <v>2061816666.6666927</v>
-      </c>
-      <c r="AX9" s="37">
-        <f t="shared" si="34"/>
-        <v>2061816666.6666532</v>
-      </c>
-      <c r="AY9" s="37">
-        <f t="shared" si="35"/>
-        <v>2061816666.6666729</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="37">
-        <v>8000000</v>
-      </c>
-      <c r="C10" s="37">
-        <v>8600000</v>
-      </c>
-      <c r="D10" s="37">
-        <v>8700000</v>
-      </c>
-      <c r="E10" s="37">
-        <v>8400000</v>
-      </c>
-      <c r="F10" s="37">
-        <v>8400000</v>
-      </c>
-      <c r="G10" s="37">
-        <v>8100000</v>
-      </c>
-      <c r="H10" s="37">
-        <v>8300000</v>
-      </c>
-      <c r="I10" s="37">
-        <v>8200000</v>
-      </c>
-      <c r="J10" s="37">
-        <v>8200000</v>
-      </c>
-      <c r="K10" s="37">
-        <v>8200000</v>
-      </c>
-      <c r="L10" s="37">
-        <f t="shared" si="36"/>
-        <v>8200000</v>
-      </c>
-      <c r="M10" s="37">
-        <f t="shared" si="37"/>
-        <v>8200000</v>
-      </c>
-      <c r="N10" s="37">
-        <f t="shared" si="38"/>
-        <v>8200000</v>
-      </c>
-      <c r="O10" s="37">
-        <f t="shared" si="39"/>
-        <v>8200000</v>
-      </c>
-      <c r="P10" s="37">
-        <f t="shared" si="40"/>
-        <v>8200000</v>
-      </c>
-      <c r="Q10" s="37">
-        <f t="shared" si="1"/>
-        <v>8200000</v>
-      </c>
-      <c r="R10" s="37">
-        <f t="shared" si="2"/>
-        <v>8200000</v>
-      </c>
-      <c r="S10" s="37">
-        <f t="shared" si="3"/>
-        <v>8200000</v>
-      </c>
-      <c r="T10" s="37">
-        <f t="shared" si="4"/>
-        <v>8200000</v>
-      </c>
-      <c r="U10" s="37">
-        <f t="shared" si="5"/>
-        <v>8200000</v>
-      </c>
-      <c r="V10" s="37">
-        <f t="shared" si="6"/>
-        <v>8200000</v>
-      </c>
-      <c r="W10" s="37">
-        <f t="shared" si="7"/>
-        <v>8200000</v>
-      </c>
-      <c r="X10" s="37">
-        <f t="shared" si="8"/>
-        <v>8200000</v>
-      </c>
-      <c r="Y10" s="37">
-        <f t="shared" si="9"/>
-        <v>8200000</v>
-      </c>
-      <c r="Z10" s="37">
-        <f t="shared" si="10"/>
-        <v>8200000</v>
-      </c>
-      <c r="AA10" s="37">
-        <f t="shared" si="11"/>
-        <v>8200000</v>
-      </c>
-      <c r="AB10" s="37">
-        <f t="shared" si="12"/>
-        <v>8200000</v>
-      </c>
-      <c r="AC10" s="37">
-        <f t="shared" si="13"/>
-        <v>8200000</v>
-      </c>
-      <c r="AD10" s="37">
-        <f t="shared" si="14"/>
-        <v>8200000</v>
-      </c>
-      <c r="AE10" s="37">
-        <f t="shared" si="15"/>
-        <v>8200000</v>
-      </c>
-      <c r="AF10" s="37">
-        <f t="shared" si="16"/>
-        <v>8200000</v>
-      </c>
-      <c r="AG10" s="37">
-        <f t="shared" si="17"/>
-        <v>8200000</v>
-      </c>
-      <c r="AH10" s="37">
-        <f t="shared" si="18"/>
-        <v>8200000</v>
-      </c>
-      <c r="AI10" s="37">
-        <f t="shared" si="19"/>
-        <v>8200000</v>
-      </c>
-      <c r="AJ10" s="37">
-        <f t="shared" si="20"/>
-        <v>8200000</v>
-      </c>
-      <c r="AK10" s="37">
-        <f t="shared" si="21"/>
-        <v>8200000</v>
-      </c>
-      <c r="AL10" s="37">
-        <f t="shared" si="22"/>
-        <v>8200000</v>
-      </c>
-      <c r="AM10" s="37">
-        <f t="shared" si="23"/>
-        <v>8200000</v>
-      </c>
-      <c r="AN10" s="37">
-        <f t="shared" si="24"/>
-        <v>8200000</v>
-      </c>
-      <c r="AO10" s="37">
-        <f t="shared" si="25"/>
-        <v>8200000</v>
-      </c>
-      <c r="AP10" s="37">
-        <f t="shared" si="26"/>
-        <v>8200000</v>
-      </c>
-      <c r="AQ10" s="37">
-        <f t="shared" si="27"/>
-        <v>8200000</v>
-      </c>
-      <c r="AR10" s="37">
-        <f t="shared" si="28"/>
-        <v>8200000</v>
-      </c>
-      <c r="AS10" s="37">
-        <f t="shared" si="29"/>
-        <v>8200000</v>
-      </c>
-      <c r="AT10" s="37">
-        <f t="shared" si="30"/>
-        <v>8200000</v>
-      </c>
-      <c r="AU10" s="37">
-        <f t="shared" si="31"/>
-        <v>8200000</v>
-      </c>
-      <c r="AV10" s="37">
-        <f t="shared" si="32"/>
-        <v>8200000</v>
-      </c>
-      <c r="AW10" s="37">
-        <f t="shared" si="33"/>
-        <v>8200000</v>
-      </c>
-      <c r="AX10" s="37">
-        <f t="shared" si="34"/>
-        <v>8200000</v>
-      </c>
-      <c r="AY10" s="37">
-        <f t="shared" si="35"/>
-        <v>8200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="37">
-        <v>60600000</v>
-      </c>
-      <c r="C11" s="37">
-        <v>74600000</v>
-      </c>
-      <c r="D11" s="37">
-        <v>83000000</v>
-      </c>
-      <c r="E11" s="37">
-        <v>81300000</v>
-      </c>
-      <c r="F11" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="G11" s="37">
-        <v>79800000</v>
-      </c>
-      <c r="H11" s="37">
-        <v>81100000</v>
-      </c>
-      <c r="I11" s="37">
-        <v>79900000</v>
-      </c>
-      <c r="J11" s="37">
-        <v>81200000</v>
-      </c>
-      <c r="K11" s="37">
-        <v>82300000</v>
-      </c>
-      <c r="L11" s="37">
-        <f t="shared" si="36"/>
-        <v>81750000</v>
-      </c>
-      <c r="M11" s="37">
-        <f t="shared" si="37"/>
-        <v>82025000</v>
-      </c>
-      <c r="N11" s="37">
-        <f t="shared" si="38"/>
-        <v>81887500</v>
-      </c>
-      <c r="O11" s="37">
-        <f t="shared" si="39"/>
-        <v>81956250</v>
-      </c>
-      <c r="P11" s="37">
-        <f t="shared" si="40"/>
-        <v>81921875</v>
-      </c>
-      <c r="Q11" s="37">
-        <f t="shared" si="1"/>
-        <v>81939062.5</v>
-      </c>
-      <c r="R11" s="37">
-        <f t="shared" si="2"/>
-        <v>81930468.75</v>
-      </c>
-      <c r="S11" s="37">
-        <f t="shared" si="3"/>
-        <v>81934765.625</v>
-      </c>
-      <c r="T11" s="37">
-        <f t="shared" si="4"/>
-        <v>81932617.1875</v>
-      </c>
-      <c r="U11" s="37">
-        <f t="shared" si="5"/>
-        <v>81933691.40625</v>
-      </c>
-      <c r="V11" s="37">
-        <f t="shared" si="6"/>
-        <v>81933154.296875</v>
-      </c>
-      <c r="W11" s="37">
-        <f t="shared" si="7"/>
-        <v>81933422.8515625</v>
-      </c>
-      <c r="X11" s="37">
-        <f t="shared" si="8"/>
-        <v>81933288.57421875</v>
-      </c>
-      <c r="Y11" s="37">
-        <f t="shared" si="9"/>
-        <v>81933355.712890625</v>
-      </c>
-      <c r="Z11" s="37">
-        <f t="shared" si="10"/>
-        <v>81933322.143554688</v>
-      </c>
-      <c r="AA11" s="37">
-        <f t="shared" si="11"/>
-        <v>81933338.928222656</v>
-      </c>
-      <c r="AB11" s="37">
-        <f t="shared" si="12"/>
-        <v>81933330.535888672</v>
-      </c>
-      <c r="AC11" s="37">
-        <f t="shared" si="13"/>
-        <v>81933334.732055664</v>
-      </c>
-      <c r="AD11" s="37">
-        <f t="shared" si="14"/>
-        <v>81933332.633972168</v>
-      </c>
-      <c r="AE11" s="37">
-        <f t="shared" si="15"/>
-        <v>81933333.683013916</v>
-      </c>
-      <c r="AF11" s="37">
-        <f t="shared" si="16"/>
-        <v>81933333.158493042</v>
-      </c>
-      <c r="AG11" s="37">
-        <f t="shared" si="17"/>
-        <v>81933333.420753479</v>
-      </c>
-      <c r="AH11" s="37">
-        <f t="shared" si="18"/>
-        <v>81933333.28962326</v>
-      </c>
-      <c r="AI11" s="37">
-        <f t="shared" si="19"/>
-        <v>81933333.35518837</v>
-      </c>
-      <c r="AJ11" s="37">
-        <f t="shared" si="20"/>
-        <v>81933333.322405815</v>
-      </c>
-      <c r="AK11" s="37">
-        <f t="shared" si="21"/>
-        <v>81933333.338797092</v>
-      </c>
-      <c r="AL11" s="37">
-        <f t="shared" si="22"/>
-        <v>81933333.330601454</v>
-      </c>
-      <c r="AM11" s="37">
-        <f t="shared" si="23"/>
-        <v>81933333.334699273</v>
-      </c>
-      <c r="AN11" s="37">
-        <f t="shared" si="24"/>
-        <v>81933333.332650363</v>
-      </c>
-      <c r="AO11" s="37">
-        <f t="shared" si="25"/>
-        <v>81933333.333674818</v>
-      </c>
-      <c r="AP11" s="37">
-        <f t="shared" si="26"/>
-        <v>81933333.333162591</v>
-      </c>
-      <c r="AQ11" s="37">
-        <f t="shared" si="27"/>
-        <v>81933333.333418697</v>
-      </c>
-      <c r="AR11" s="37">
-        <f t="shared" si="28"/>
-        <v>81933333.333290637</v>
-      </c>
-      <c r="AS11" s="37">
-        <f t="shared" si="29"/>
-        <v>81933333.333354667</v>
-      </c>
-      <c r="AT11" s="37">
-        <f t="shared" si="30"/>
-        <v>81933333.333322644</v>
-      </c>
-      <c r="AU11" s="37">
-        <f t="shared" si="31"/>
-        <v>81933333.333338648</v>
-      </c>
-      <c r="AV11" s="37">
-        <f t="shared" si="32"/>
-        <v>81933333.333330646</v>
-      </c>
-      <c r="AW11" s="37">
-        <f t="shared" si="33"/>
-        <v>81933333.333334655</v>
-      </c>
-      <c r="AX11" s="37">
-        <f t="shared" si="34"/>
-        <v>81933333.333332658</v>
-      </c>
-      <c r="AY11" s="37">
-        <f t="shared" si="35"/>
-        <v>81933333.333333656</v>
-      </c>
-    </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="37">
-        <v>3100000</v>
-      </c>
-      <c r="C12" s="37">
-        <v>3100000</v>
-      </c>
-      <c r="D12" s="37">
-        <v>4500000</v>
-      </c>
-      <c r="E12" s="37">
-        <v>11900000</v>
-      </c>
-      <c r="F12" s="37">
-        <v>15200000</v>
-      </c>
-      <c r="G12" s="37">
-        <v>10600000</v>
-      </c>
-      <c r="H12" s="37">
-        <v>6900000</v>
-      </c>
-      <c r="I12" s="37">
-        <v>6900000</v>
-      </c>
-      <c r="J12" s="37">
-        <v>5500000</v>
-      </c>
-      <c r="K12" s="37">
-        <v>5700000</v>
-      </c>
-      <c r="L12" s="37">
-        <f t="shared" si="36"/>
-        <v>5600000</v>
-      </c>
-      <c r="M12" s="37">
-        <f t="shared" si="37"/>
-        <v>5650000</v>
-      </c>
-      <c r="N12" s="37">
-        <f t="shared" si="38"/>
-        <v>5625000</v>
-      </c>
-      <c r="O12" s="37">
-        <f t="shared" si="39"/>
-        <v>5637500</v>
-      </c>
-      <c r="P12" s="37">
-        <f t="shared" si="40"/>
-        <v>5631250</v>
-      </c>
-      <c r="Q12" s="37">
-        <f t="shared" si="1"/>
-        <v>5634375</v>
-      </c>
-      <c r="R12" s="37">
-        <f t="shared" si="2"/>
-        <v>5632812.5</v>
-      </c>
-      <c r="S12" s="37">
-        <f t="shared" si="3"/>
-        <v>5633593.75</v>
-      </c>
-      <c r="T12" s="37">
-        <f t="shared" si="4"/>
-        <v>5633203.125</v>
-      </c>
-      <c r="U12" s="37">
-        <f t="shared" si="5"/>
-        <v>5633398.4375</v>
-      </c>
-      <c r="V12" s="37">
-        <f t="shared" si="6"/>
-        <v>5633300.78125</v>
-      </c>
-      <c r="W12" s="37">
-        <f t="shared" si="7"/>
-        <v>5633349.609375</v>
-      </c>
-      <c r="X12" s="37">
-        <f t="shared" si="8"/>
-        <v>5633325.1953125</v>
-      </c>
-      <c r="Y12" s="37">
-        <f t="shared" si="9"/>
-        <v>5633337.40234375</v>
-      </c>
-      <c r="Z12" s="37">
-        <f t="shared" si="10"/>
-        <v>5633331.298828125</v>
-      </c>
-      <c r="AA12" s="37">
-        <f t="shared" si="11"/>
-        <v>5633334.3505859375</v>
-      </c>
-      <c r="AB12" s="37">
-        <f t="shared" si="12"/>
-        <v>5633332.8247070313</v>
-      </c>
-      <c r="AC12" s="37">
-        <f t="shared" si="13"/>
-        <v>5633333.5876464844</v>
-      </c>
-      <c r="AD12" s="37">
-        <f t="shared" si="14"/>
-        <v>5633333.2061767578</v>
-      </c>
-      <c r="AE12" s="37">
-        <f t="shared" si="15"/>
-        <v>5633333.3969116211</v>
-      </c>
-      <c r="AF12" s="37">
-        <f t="shared" si="16"/>
-        <v>5633333.3015441895</v>
-      </c>
-      <c r="AG12" s="37">
-        <f t="shared" si="17"/>
-        <v>5633333.3492279053</v>
-      </c>
-      <c r="AH12" s="37">
-        <f t="shared" si="18"/>
-        <v>5633333.3253860474</v>
-      </c>
-      <c r="AI12" s="37">
-        <f t="shared" si="19"/>
-        <v>5633333.3373069763</v>
-      </c>
-      <c r="AJ12" s="37">
-        <f t="shared" si="20"/>
-        <v>5633333.3313465118</v>
-      </c>
-      <c r="AK12" s="37">
-        <f t="shared" si="21"/>
-        <v>5633333.3343267441</v>
-      </c>
-      <c r="AL12" s="37">
-        <f t="shared" si="22"/>
-        <v>5633333.332836628</v>
-      </c>
-      <c r="AM12" s="37">
-        <f t="shared" si="23"/>
-        <v>5633333.333581686</v>
-      </c>
-      <c r="AN12" s="37">
-        <f t="shared" si="24"/>
-        <v>5633333.333209157</v>
-      </c>
-      <c r="AO12" s="37">
-        <f t="shared" si="25"/>
-        <v>5633333.3333954215</v>
-      </c>
-      <c r="AP12" s="37">
-        <f t="shared" si="26"/>
-        <v>5633333.3333022892</v>
-      </c>
-      <c r="AQ12" s="37">
-        <f t="shared" si="27"/>
-        <v>5633333.3333488554</v>
-      </c>
-      <c r="AR12" s="37">
-        <f t="shared" si="28"/>
-        <v>5633333.3333255723</v>
-      </c>
-      <c r="AS12" s="37">
-        <f t="shared" si="29"/>
-        <v>5633333.3333372138</v>
-      </c>
-      <c r="AT12" s="37">
-        <f t="shared" si="30"/>
-        <v>5633333.3333313931</v>
-      </c>
-      <c r="AU12" s="37">
-        <f t="shared" si="31"/>
-        <v>5633333.3333343035</v>
-      </c>
-      <c r="AV12" s="37">
-        <f t="shared" si="32"/>
-        <v>5633333.3333328478</v>
-      </c>
-      <c r="AW12" s="37">
-        <f t="shared" si="33"/>
-        <v>5633333.3333335761</v>
-      </c>
-      <c r="AX12" s="37">
-        <f t="shared" si="34"/>
-        <v>5633333.333333212</v>
-      </c>
-      <c r="AY12" s="37">
-        <f t="shared" si="35"/>
-        <v>5633333.3333333936</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B14" s="25">
+        <v>1030200000</v>
+      </c>
+      <c r="C14" s="25">
+        <v>1268200000</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1411000000</v>
+      </c>
+      <c r="E14" s="25">
+        <v>1382100000</v>
+      </c>
+      <c r="F14" s="25">
+        <v>1378700000</v>
+      </c>
+      <c r="G14" s="25">
+        <v>1356600000</v>
+      </c>
+      <c r="H14" s="25">
+        <v>1378700000</v>
+      </c>
+      <c r="I14" s="25">
+        <v>1358300000</v>
+      </c>
+      <c r="J14" s="25">
+        <v>1380400000</v>
+      </c>
+      <c r="K14" s="25">
+        <v>1399100000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B15" s="37">
         <v>20500000</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C15" s="37">
         <v>22200000</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D15" s="37">
         <v>22600000</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E15" s="37">
         <v>21600000</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F15" s="37">
         <v>21700000</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G15" s="37">
         <v>21100000</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H15" s="37">
         <v>21400000</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I15" s="37">
         <v>21200000</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J15" s="37">
         <v>21400000</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K15" s="37">
         <v>21500000</v>
       </c>
-      <c r="L13" s="37">
-        <f t="shared" si="36"/>
-        <v>21450000</v>
-      </c>
-      <c r="M13" s="37">
-        <f t="shared" si="37"/>
-        <v>21475000</v>
-      </c>
-      <c r="N13" s="37">
-        <f t="shared" si="38"/>
-        <v>21462500</v>
-      </c>
-      <c r="O13" s="37">
-        <f t="shared" si="39"/>
-        <v>21468750</v>
-      </c>
-      <c r="P13" s="37">
-        <f t="shared" si="40"/>
-        <v>21465625</v>
-      </c>
-      <c r="Q13" s="37">
-        <f t="shared" si="1"/>
-        <v>21467187.5</v>
-      </c>
-      <c r="R13" s="37">
-        <f t="shared" si="2"/>
-        <v>21466406.25</v>
-      </c>
-      <c r="S13" s="37">
-        <f t="shared" si="3"/>
-        <v>21466796.875</v>
-      </c>
-      <c r="T13" s="37">
-        <f t="shared" si="4"/>
-        <v>21466601.5625</v>
-      </c>
-      <c r="U13" s="37">
-        <f t="shared" si="5"/>
-        <v>21466699.21875</v>
-      </c>
-      <c r="V13" s="37">
-        <f t="shared" si="6"/>
-        <v>21466650.390625</v>
-      </c>
-      <c r="W13" s="37">
-        <f t="shared" si="7"/>
-        <v>21466674.8046875</v>
-      </c>
-      <c r="X13" s="37">
-        <f t="shared" si="8"/>
-        <v>21466662.59765625</v>
-      </c>
-      <c r="Y13" s="37">
-        <f t="shared" si="9"/>
-        <v>21466668.701171875</v>
-      </c>
-      <c r="Z13" s="37">
-        <f t="shared" si="10"/>
-        <v>21466665.649414063</v>
-      </c>
-      <c r="AA13" s="37">
-        <f t="shared" si="11"/>
-        <v>21466667.175292969</v>
-      </c>
-      <c r="AB13" s="37">
-        <f t="shared" si="12"/>
-        <v>21466666.412353516</v>
-      </c>
-      <c r="AC13" s="37">
-        <f t="shared" si="13"/>
-        <v>21466666.793823242</v>
-      </c>
-      <c r="AD13" s="37">
-        <f t="shared" si="14"/>
-        <v>21466666.603088379</v>
-      </c>
-      <c r="AE13" s="37">
-        <f t="shared" si="15"/>
-        <v>21466666.698455811</v>
-      </c>
-      <c r="AF13" s="37">
-        <f t="shared" si="16"/>
-        <v>21466666.650772095</v>
-      </c>
-      <c r="AG13" s="37">
-        <f t="shared" si="17"/>
-        <v>21466666.674613953</v>
-      </c>
-      <c r="AH13" s="37">
-        <f t="shared" si="18"/>
-        <v>21466666.662693024</v>
-      </c>
-      <c r="AI13" s="37">
-        <f t="shared" si="19"/>
-        <v>21466666.668653488</v>
-      </c>
-      <c r="AJ13" s="37">
-        <f t="shared" si="20"/>
-        <v>21466666.665673256</v>
-      </c>
-      <c r="AK13" s="37">
-        <f t="shared" si="21"/>
-        <v>21466666.667163372</v>
-      </c>
-      <c r="AL13" s="37">
-        <f t="shared" si="22"/>
-        <v>21466666.666418314</v>
-      </c>
-      <c r="AM13" s="37">
-        <f t="shared" si="23"/>
-        <v>21466666.666790843</v>
-      </c>
-      <c r="AN13" s="37">
-        <f t="shared" si="24"/>
-        <v>21466666.666604578</v>
-      </c>
-      <c r="AO13" s="37">
-        <f t="shared" si="25"/>
-        <v>21466666.666697711</v>
-      </c>
-      <c r="AP13" s="37">
-        <f t="shared" si="26"/>
-        <v>21466666.666651145</v>
-      </c>
-      <c r="AQ13" s="37">
-        <f t="shared" si="27"/>
-        <v>21466666.666674428</v>
-      </c>
-      <c r="AR13" s="37">
-        <f t="shared" si="28"/>
-        <v>21466666.666662786</v>
-      </c>
-      <c r="AS13" s="37">
-        <f t="shared" si="29"/>
-        <v>21466666.666668609</v>
-      </c>
-      <c r="AT13" s="37">
-        <f t="shared" si="30"/>
-        <v>21466666.666665696</v>
-      </c>
-      <c r="AU13" s="37">
-        <f t="shared" si="31"/>
-        <v>21466666.666667152</v>
-      </c>
-      <c r="AV13" s="37">
-        <f t="shared" si="32"/>
-        <v>21466666.666666426</v>
-      </c>
-      <c r="AW13" s="37">
-        <f t="shared" si="33"/>
-        <v>21466666.666666791</v>
-      </c>
-      <c r="AX13" s="37">
-        <f t="shared" si="34"/>
-        <v>21466666.666666608</v>
-      </c>
-      <c r="AY13" s="37">
-        <f t="shared" si="35"/>
-        <v>21466666.666666701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="37">
-        <v>5800000</v>
-      </c>
-      <c r="C14" s="37">
-        <v>6700000</v>
-      </c>
-      <c r="D14" s="37">
-        <v>7500000</v>
-      </c>
-      <c r="E14" s="37">
-        <v>7400000</v>
-      </c>
-      <c r="F14" s="37">
-        <v>7900000</v>
-      </c>
-      <c r="G14" s="37">
-        <v>7900000</v>
-      </c>
-      <c r="H14" s="37">
-        <v>8000000</v>
-      </c>
-      <c r="I14" s="37">
-        <v>7800000</v>
-      </c>
-      <c r="J14" s="37">
-        <v>7800000</v>
-      </c>
-      <c r="K14" s="37">
-        <v>7900000</v>
-      </c>
-      <c r="L14" s="37">
-        <f t="shared" si="36"/>
-        <v>7850000</v>
-      </c>
-      <c r="M14" s="37">
-        <f t="shared" si="37"/>
-        <v>7875000</v>
-      </c>
-      <c r="N14" s="37">
-        <f t="shared" si="38"/>
-        <v>7862500</v>
-      </c>
-      <c r="O14" s="37">
-        <f t="shared" si="39"/>
-        <v>7868750</v>
-      </c>
-      <c r="P14" s="37">
-        <f t="shared" si="40"/>
-        <v>7865625</v>
-      </c>
-      <c r="Q14" s="37">
-        <f t="shared" si="1"/>
-        <v>7867187.5</v>
-      </c>
-      <c r="R14" s="37">
-        <f t="shared" si="2"/>
-        <v>7866406.25</v>
-      </c>
-      <c r="S14" s="37">
-        <f t="shared" si="3"/>
-        <v>7866796.875</v>
-      </c>
-      <c r="T14" s="37">
-        <f t="shared" si="4"/>
-        <v>7866601.5625</v>
-      </c>
-      <c r="U14" s="37">
-        <f t="shared" si="5"/>
-        <v>7866699.21875</v>
-      </c>
-      <c r="V14" s="37">
-        <f t="shared" si="6"/>
-        <v>7866650.390625</v>
-      </c>
-      <c r="W14" s="37">
-        <f t="shared" si="7"/>
-        <v>7866674.8046875</v>
-      </c>
-      <c r="X14" s="37">
-        <f t="shared" si="8"/>
-        <v>7866662.59765625</v>
-      </c>
-      <c r="Y14" s="37">
-        <f t="shared" si="9"/>
-        <v>7866668.701171875</v>
-      </c>
-      <c r="Z14" s="37">
-        <f t="shared" si="10"/>
-        <v>7866665.6494140625</v>
-      </c>
-      <c r="AA14" s="37">
-        <f t="shared" si="11"/>
-        <v>7866667.1752929688</v>
-      </c>
-      <c r="AB14" s="37">
-        <f t="shared" si="12"/>
-        <v>7866666.4123535156</v>
-      </c>
-      <c r="AC14" s="37">
-        <f t="shared" si="13"/>
-        <v>7866666.7938232422</v>
-      </c>
-      <c r="AD14" s="37">
-        <f t="shared" si="14"/>
-        <v>7866666.6030883789</v>
-      </c>
-      <c r="AE14" s="37">
-        <f t="shared" si="15"/>
-        <v>7866666.6984558105</v>
-      </c>
-      <c r="AF14" s="37">
-        <f t="shared" si="16"/>
-        <v>7866666.6507720947</v>
-      </c>
-      <c r="AG14" s="37">
-        <f t="shared" si="17"/>
-        <v>7866666.6746139526</v>
-      </c>
-      <c r="AH14" s="37">
-        <f t="shared" si="18"/>
-        <v>7866666.6626930237</v>
-      </c>
-      <c r="AI14" s="37">
-        <f t="shared" si="19"/>
-        <v>7866666.6686534882</v>
-      </c>
-      <c r="AJ14" s="37">
-        <f t="shared" si="20"/>
-        <v>7866666.6656732559</v>
-      </c>
-      <c r="AK14" s="37">
-        <f t="shared" si="21"/>
-        <v>7866666.667163372</v>
-      </c>
-      <c r="AL14" s="37">
-        <f t="shared" si="22"/>
-        <v>7866666.666418314</v>
-      </c>
-      <c r="AM14" s="37">
-        <f t="shared" si="23"/>
-        <v>7866666.666790843</v>
-      </c>
-      <c r="AN14" s="37">
-        <f t="shared" si="24"/>
-        <v>7866666.6666045785</v>
-      </c>
-      <c r="AO14" s="37">
-        <f t="shared" si="25"/>
-        <v>7866666.6666977108</v>
-      </c>
-      <c r="AP14" s="37">
-        <f t="shared" si="26"/>
-        <v>7866666.6666511446</v>
-      </c>
-      <c r="AQ14" s="37">
-        <f t="shared" si="27"/>
-        <v>7866666.6666744277</v>
-      </c>
-      <c r="AR14" s="37">
-        <f t="shared" si="28"/>
-        <v>7866666.6666627862</v>
-      </c>
-      <c r="AS14" s="37">
-        <f t="shared" si="29"/>
-        <v>7866666.6666686069</v>
-      </c>
-      <c r="AT14" s="37">
-        <f t="shared" si="30"/>
-        <v>7866666.6666656965</v>
-      </c>
-      <c r="AU14" s="37">
-        <f t="shared" si="31"/>
-        <v>7866666.6666671522</v>
-      </c>
-      <c r="AV14" s="37">
-        <f t="shared" si="32"/>
-        <v>7866666.6666664239</v>
-      </c>
-      <c r="AW14" s="37">
-        <f t="shared" si="33"/>
-        <v>7866666.666666788</v>
-      </c>
-      <c r="AX14" s="37">
-        <f t="shared" si="34"/>
-        <v>7866666.6666666064</v>
-      </c>
-      <c r="AY14" s="37">
-        <f t="shared" si="35"/>
-        <v>7866666.6666666977</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="37">
-        <v>116600000</v>
-      </c>
-      <c r="C15" s="37">
-        <v>129900000</v>
-      </c>
-      <c r="D15" s="37">
-        <v>128200000</v>
-      </c>
-      <c r="E15" s="37">
-        <v>123000000</v>
-      </c>
-      <c r="F15" s="37">
-        <v>123100000</v>
-      </c>
-      <c r="G15" s="37">
-        <v>120400000</v>
-      </c>
-      <c r="H15" s="37">
-        <v>121900000</v>
-      </c>
-      <c r="I15" s="37">
-        <v>121000000</v>
-      </c>
-      <c r="J15" s="37">
-        <v>122400000</v>
-      </c>
-      <c r="K15" s="37">
-        <v>123300000</v>
-      </c>
-      <c r="L15" s="37">
-        <f t="shared" si="36"/>
-        <v>122850000</v>
-      </c>
-      <c r="M15" s="37">
-        <f t="shared" si="37"/>
-        <v>123075000</v>
-      </c>
-      <c r="N15" s="37">
-        <f t="shared" si="38"/>
-        <v>122962500</v>
-      </c>
-      <c r="O15" s="37">
-        <f t="shared" si="39"/>
-        <v>123018750</v>
-      </c>
-      <c r="P15" s="37">
-        <f t="shared" si="40"/>
-        <v>122990625</v>
-      </c>
-      <c r="Q15" s="37">
-        <f t="shared" si="1"/>
-        <v>123004687.5</v>
-      </c>
-      <c r="R15" s="37">
-        <f t="shared" si="2"/>
-        <v>122997656.25</v>
-      </c>
-      <c r="S15" s="37">
-        <f t="shared" si="3"/>
-        <v>123001171.875</v>
-      </c>
-      <c r="T15" s="37">
-        <f t="shared" si="4"/>
-        <v>122999414.0625</v>
-      </c>
-      <c r="U15" s="37">
-        <f t="shared" si="5"/>
-        <v>123000292.96875</v>
-      </c>
-      <c r="V15" s="37">
-        <f t="shared" si="6"/>
-        <v>122999853.515625</v>
-      </c>
-      <c r="W15" s="37">
-        <f t="shared" si="7"/>
-        <v>123000073.2421875</v>
-      </c>
-      <c r="X15" s="37">
-        <f t="shared" si="8"/>
-        <v>122999963.37890625</v>
-      </c>
-      <c r="Y15" s="37">
-        <f t="shared" si="9"/>
-        <v>123000018.31054688</v>
-      </c>
-      <c r="Z15" s="37">
-        <f t="shared" si="10"/>
-        <v>122999990.84472656</v>
-      </c>
-      <c r="AA15" s="37">
-        <f t="shared" si="11"/>
-        <v>123000004.57763672</v>
-      </c>
-      <c r="AB15" s="37">
-        <f t="shared" si="12"/>
-        <v>122999997.71118164</v>
-      </c>
-      <c r="AC15" s="37">
-        <f t="shared" si="13"/>
-        <v>123000001.14440918</v>
-      </c>
-      <c r="AD15" s="37">
-        <f t="shared" si="14"/>
-        <v>122999999.42779541</v>
-      </c>
-      <c r="AE15" s="37">
-        <f t="shared" si="15"/>
-        <v>123000000.28610229</v>
-      </c>
-      <c r="AF15" s="37">
-        <f t="shared" si="16"/>
-        <v>122999999.85694885</v>
-      </c>
-      <c r="AG15" s="37">
-        <f t="shared" si="17"/>
-        <v>123000000.07152557</v>
-      </c>
-      <c r="AH15" s="37">
-        <f t="shared" si="18"/>
-        <v>122999999.96423721</v>
-      </c>
-      <c r="AI15" s="37">
-        <f t="shared" si="19"/>
-        <v>123000000.01788139</v>
-      </c>
-      <c r="AJ15" s="37">
-        <f t="shared" si="20"/>
-        <v>122999999.9910593</v>
-      </c>
-      <c r="AK15" s="37">
-        <f t="shared" si="21"/>
-        <v>123000000.00447035</v>
-      </c>
-      <c r="AL15" s="37">
-        <f t="shared" si="22"/>
-        <v>122999999.99776483</v>
-      </c>
-      <c r="AM15" s="37">
-        <f t="shared" si="23"/>
-        <v>123000000.00111759</v>
-      </c>
-      <c r="AN15" s="37">
-        <f t="shared" si="24"/>
-        <v>122999999.99944121</v>
-      </c>
-      <c r="AO15" s="37">
-        <f t="shared" si="25"/>
-        <v>123000000.0002794</v>
-      </c>
-      <c r="AP15" s="37">
-        <f t="shared" si="26"/>
-        <v>122999999.9998603</v>
-      </c>
-      <c r="AQ15" s="37">
-        <f t="shared" si="27"/>
-        <v>123000000.00006986</v>
-      </c>
-      <c r="AR15" s="37">
-        <f t="shared" si="28"/>
-        <v>122999999.99996507</v>
-      </c>
-      <c r="AS15" s="37">
-        <f t="shared" si="29"/>
-        <v>123000000.00001746</v>
-      </c>
-      <c r="AT15" s="37">
-        <f t="shared" si="30"/>
-        <v>122999999.99999127</v>
-      </c>
-      <c r="AU15" s="37">
-        <f t="shared" si="31"/>
-        <v>123000000.00000437</v>
-      </c>
-      <c r="AV15" s="37">
-        <f t="shared" si="32"/>
-        <v>122999999.99999782</v>
-      </c>
-      <c r="AW15" s="37">
-        <f t="shared" si="33"/>
-        <v>123000000.0000011</v>
-      </c>
-      <c r="AX15" s="37">
-        <f t="shared" si="34"/>
-        <v>122999999.99999946</v>
-      </c>
-      <c r="AY15" s="37">
-        <f t="shared" si="35"/>
-        <v>123000000.00000028</v>
-      </c>
-    </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" s="37">
+        <v>58000000</v>
+      </c>
+      <c r="C16" s="37">
+        <v>67000000</v>
+      </c>
+      <c r="D16" s="37">
+        <v>75000000</v>
+      </c>
+      <c r="E16" s="37">
+        <v>74000000</v>
+      </c>
+      <c r="F16" s="37">
+        <v>79000000</v>
+      </c>
+      <c r="G16" s="37">
+        <v>79000000</v>
+      </c>
+      <c r="H16" s="37">
+        <v>80000000</v>
+      </c>
+      <c r="I16" s="37">
+        <v>78000000</v>
+      </c>
+      <c r="J16" s="37">
+        <v>78000000</v>
+      </c>
+      <c r="K16" s="37">
+        <v>79000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="37">
-        <v>104600000</v>
-      </c>
-      <c r="C16" s="37">
-        <v>122100000</v>
-      </c>
-      <c r="D16" s="37">
-        <v>131700000</v>
-      </c>
-      <c r="E16" s="37">
-        <v>128600000</v>
-      </c>
-      <c r="F16" s="37">
-        <v>128700000</v>
-      </c>
-      <c r="G16" s="37">
-        <v>125200000</v>
-      </c>
-      <c r="H16" s="37">
-        <v>127600000</v>
-      </c>
-      <c r="I16" s="37">
-        <v>126000000</v>
-      </c>
-      <c r="J16" s="37">
-        <v>127400000</v>
-      </c>
-      <c r="K16" s="37">
-        <v>128200000</v>
-      </c>
-      <c r="L16" s="37">
-        <f t="shared" si="36"/>
-        <v>127800000</v>
-      </c>
-      <c r="M16" s="37">
-        <f t="shared" si="37"/>
-        <v>128000000</v>
-      </c>
-      <c r="N16" s="37">
-        <f t="shared" si="38"/>
-        <v>127900000</v>
-      </c>
-      <c r="O16" s="37">
-        <f t="shared" si="39"/>
-        <v>127950000</v>
-      </c>
-      <c r="P16" s="37">
-        <f t="shared" si="40"/>
-        <v>127925000</v>
-      </c>
-      <c r="Q16" s="37">
-        <f t="shared" si="1"/>
-        <v>127937500</v>
-      </c>
-      <c r="R16" s="37">
-        <f t="shared" si="2"/>
-        <v>127931250</v>
-      </c>
-      <c r="S16" s="37">
-        <f t="shared" si="3"/>
-        <v>127934375</v>
-      </c>
-      <c r="T16" s="37">
-        <f t="shared" si="4"/>
-        <v>127932812.5</v>
-      </c>
-      <c r="U16" s="37">
-        <f t="shared" si="5"/>
-        <v>127933593.75</v>
-      </c>
-      <c r="V16" s="37">
-        <f t="shared" si="6"/>
-        <v>127933203.125</v>
-      </c>
-      <c r="W16" s="37">
-        <f t="shared" si="7"/>
-        <v>127933398.4375</v>
-      </c>
-      <c r="X16" s="37">
-        <f t="shared" si="8"/>
-        <v>127933300.78125</v>
-      </c>
-      <c r="Y16" s="37">
-        <f t="shared" si="9"/>
-        <v>127933349.609375</v>
-      </c>
-      <c r="Z16" s="37">
-        <f t="shared" si="10"/>
-        <v>127933325.1953125</v>
-      </c>
-      <c r="AA16" s="37">
-        <f t="shared" si="11"/>
-        <v>127933337.40234375</v>
-      </c>
-      <c r="AB16" s="37">
-        <f t="shared" si="12"/>
-        <v>127933331.29882813</v>
-      </c>
-      <c r="AC16" s="37">
-        <f t="shared" si="13"/>
-        <v>127933334.35058594</v>
-      </c>
-      <c r="AD16" s="37">
-        <f t="shared" si="14"/>
-        <v>127933332.82470703</v>
-      </c>
-      <c r="AE16" s="37">
-        <f t="shared" si="15"/>
-        <v>127933333.58764648</v>
-      </c>
-      <c r="AF16" s="37">
-        <f t="shared" si="16"/>
-        <v>127933333.20617676</v>
-      </c>
-      <c r="AG16" s="37">
-        <f t="shared" si="17"/>
-        <v>127933333.39691162</v>
-      </c>
-      <c r="AH16" s="37">
-        <f t="shared" si="18"/>
-        <v>127933333.30154419</v>
-      </c>
-      <c r="AI16" s="37">
-        <f t="shared" si="19"/>
-        <v>127933333.34922791</v>
-      </c>
-      <c r="AJ16" s="37">
-        <f t="shared" si="20"/>
-        <v>127933333.32538605</v>
-      </c>
-      <c r="AK16" s="37">
-        <f t="shared" si="21"/>
-        <v>127933333.33730698</v>
-      </c>
-      <c r="AL16" s="37">
-        <f t="shared" si="22"/>
-        <v>127933333.33134651</v>
-      </c>
-      <c r="AM16" s="37">
-        <f t="shared" si="23"/>
-        <v>127933333.33432674</v>
-      </c>
-      <c r="AN16" s="37">
-        <f t="shared" si="24"/>
-        <v>127933333.33283663</v>
-      </c>
-      <c r="AO16" s="37">
-        <f t="shared" si="25"/>
-        <v>127933333.33358169</v>
-      </c>
-      <c r="AP16" s="37">
-        <f t="shared" si="26"/>
-        <v>127933333.33320916</v>
-      </c>
-      <c r="AQ16" s="37">
-        <f t="shared" si="27"/>
-        <v>127933333.33339542</v>
-      </c>
-      <c r="AR16" s="37">
-        <f t="shared" si="28"/>
-        <v>127933333.33330229</v>
-      </c>
-      <c r="AS16" s="37">
-        <f t="shared" si="29"/>
-        <v>127933333.33334886</v>
-      </c>
-      <c r="AT16" s="37">
-        <f t="shared" si="30"/>
-        <v>127933333.33332556</v>
-      </c>
-      <c r="AU16" s="37">
-        <f t="shared" si="31"/>
-        <v>127933333.33333722</v>
-      </c>
-      <c r="AV16" s="37">
-        <f t="shared" si="32"/>
-        <v>127933333.33333139</v>
-      </c>
-      <c r="AW16" s="37">
-        <f t="shared" si="33"/>
-        <v>127933333.3333343</v>
-      </c>
-      <c r="AX16" s="37">
-        <f t="shared" si="34"/>
-        <v>127933333.33333284</v>
-      </c>
-      <c r="AY16" s="37">
-        <f t="shared" si="35"/>
-        <v>127933333.33333357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="41">
-        <v>969375250</v>
-      </c>
-      <c r="C17">
-        <v>1001504250</v>
-      </c>
-      <c r="D17">
-        <v>1046900000</v>
-      </c>
-      <c r="E17">
-        <v>1007009500</v>
-      </c>
-      <c r="F17">
-        <v>1030294000</v>
-      </c>
-      <c r="G17">
-        <v>1075328750</v>
-      </c>
-      <c r="H17">
-        <v>1011161000</v>
-      </c>
-      <c r="I17">
-        <v>1076231250</v>
-      </c>
-      <c r="J17">
-        <v>1028128000</v>
-      </c>
-      <c r="K17">
-        <v>1055564000</v>
-      </c>
-      <c r="L17" s="37">
-        <f t="shared" si="36"/>
-        <v>1041846000</v>
-      </c>
-      <c r="M17" s="37">
-        <f t="shared" si="37"/>
-        <v>1048705000</v>
-      </c>
-      <c r="N17" s="37">
-        <f t="shared" si="38"/>
-        <v>1045275500</v>
-      </c>
-      <c r="O17" s="37">
-        <f t="shared" si="39"/>
-        <v>1046990250</v>
-      </c>
-      <c r="P17" s="37">
-        <f t="shared" si="40"/>
-        <v>1046132875</v>
-      </c>
-      <c r="Q17" s="37">
-        <f t="shared" si="1"/>
-        <v>1046561562.5</v>
-      </c>
-      <c r="R17" s="37">
-        <f t="shared" si="2"/>
-        <v>1046347218.75</v>
-      </c>
-      <c r="S17" s="37">
-        <f t="shared" si="3"/>
-        <v>1046454390.625</v>
-      </c>
-      <c r="T17" s="37">
-        <f t="shared" si="4"/>
-        <v>1046400804.6875</v>
-      </c>
-      <c r="U17" s="37">
-        <f t="shared" si="5"/>
-        <v>1046427597.65625</v>
-      </c>
-      <c r="V17" s="37">
-        <f t="shared" si="6"/>
-        <v>1046414201.171875</v>
-      </c>
-      <c r="W17" s="37">
-        <f t="shared" si="7"/>
-        <v>1046420899.4140625</v>
-      </c>
-      <c r="X17" s="37">
-        <f t="shared" si="8"/>
-        <v>1046417550.2929688</v>
-      </c>
-      <c r="Y17" s="37">
-        <f t="shared" si="9"/>
-        <v>1046419224.8535156</v>
-      </c>
-      <c r="Z17" s="37">
-        <f t="shared" si="10"/>
-        <v>1046418387.5732422</v>
-      </c>
-      <c r="AA17" s="37">
-        <f t="shared" si="11"/>
-        <v>1046418806.2133789</v>
-      </c>
-      <c r="AB17" s="37">
-        <f t="shared" si="12"/>
-        <v>1046418596.8933105</v>
-      </c>
-      <c r="AC17" s="37">
-        <f t="shared" si="13"/>
-        <v>1046418701.5533447</v>
-      </c>
-      <c r="AD17" s="37">
-        <f t="shared" si="14"/>
-        <v>1046418649.2233276</v>
-      </c>
-      <c r="AE17" s="37">
-        <f t="shared" si="15"/>
-        <v>1046418675.3883362</v>
-      </c>
-      <c r="AF17" s="37">
-        <f t="shared" si="16"/>
-        <v>1046418662.3058319</v>
-      </c>
-      <c r="AG17" s="37">
-        <f t="shared" si="17"/>
-        <v>1046418668.847084</v>
-      </c>
-      <c r="AH17" s="37">
-        <f t="shared" si="18"/>
-        <v>1046418665.576458</v>
-      </c>
-      <c r="AI17" s="37">
-        <f t="shared" si="19"/>
-        <v>1046418667.211771</v>
-      </c>
-      <c r="AJ17" s="37">
-        <f t="shared" si="20"/>
-        <v>1046418666.3941145</v>
-      </c>
-      <c r="AK17" s="37">
-        <f t="shared" si="21"/>
-        <v>1046418666.8029428</v>
-      </c>
-      <c r="AL17" s="37">
-        <f t="shared" si="22"/>
-        <v>1046418666.5985286</v>
-      </c>
-      <c r="AM17" s="37">
-        <f t="shared" si="23"/>
-        <v>1046418666.7007357</v>
-      </c>
-      <c r="AN17" s="37">
-        <f t="shared" si="24"/>
-        <v>1046418666.6496322</v>
-      </c>
-      <c r="AO17" s="37">
-        <f t="shared" si="25"/>
-        <v>1046418666.675184</v>
-      </c>
-      <c r="AP17" s="37">
-        <f t="shared" si="26"/>
-        <v>1046418666.6624081</v>
-      </c>
-      <c r="AQ17" s="37">
-        <f t="shared" si="27"/>
-        <v>1046418666.6687961</v>
-      </c>
-      <c r="AR17" s="37">
-        <f t="shared" si="28"/>
-        <v>1046418666.6656021</v>
-      </c>
-      <c r="AS17" s="37">
-        <f t="shared" si="29"/>
-        <v>1046418666.6671991</v>
-      </c>
-      <c r="AT17" s="37">
-        <f t="shared" si="30"/>
-        <v>1046418666.6664007</v>
-      </c>
-      <c r="AU17" s="37">
-        <f t="shared" si="31"/>
-        <v>1046418666.6667999</v>
-      </c>
-      <c r="AV17" s="37">
-        <f t="shared" si="32"/>
-        <v>1046418666.6666002</v>
-      </c>
-      <c r="AW17" s="37">
-        <f t="shared" si="33"/>
-        <v>1046418666.6667001</v>
-      </c>
-      <c r="AX17" s="37">
-        <f t="shared" si="34"/>
-        <v>1046418666.6666502</v>
-      </c>
-      <c r="AY17" s="37">
-        <f t="shared" si="35"/>
-        <v>1046418666.6666751</v>
-      </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="B17" s="37">
+        <v>1046000000</v>
+      </c>
+      <c r="C17" s="37">
+        <v>1221000000</v>
+      </c>
+      <c r="D17" s="37">
+        <v>1317000000</v>
+      </c>
+      <c r="E17" s="37">
+        <v>1286000000</v>
+      </c>
+      <c r="F17" s="37">
+        <v>1287000000</v>
+      </c>
+      <c r="G17" s="37">
+        <v>1252000000</v>
+      </c>
+      <c r="H17" s="37">
+        <v>1276000000</v>
+      </c>
+      <c r="I17" s="37">
+        <v>1260000000</v>
+      </c>
+      <c r="J17" s="37">
+        <v>1274000000</v>
+      </c>
+      <c r="K17" s="37">
+        <v>1282000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>153</v>
       </c>
       <c r="B18" s="25">
-        <v>500000</v>
+        <v>50000000</v>
       </c>
       <c r="C18" s="25">
-        <v>500000</v>
+        <v>50000000</v>
       </c>
       <c r="D18" s="25">
-        <v>700000</v>
+        <v>70000000</v>
       </c>
       <c r="E18" s="25">
-        <v>2000000</v>
+        <v>200000000</v>
       </c>
       <c r="F18" s="25">
-        <v>2500000</v>
+        <v>250000000</v>
       </c>
       <c r="G18" s="25">
-        <v>1800000</v>
+        <v>180000000</v>
       </c>
       <c r="H18" s="25">
-        <v>1200000</v>
+        <v>120000000</v>
       </c>
       <c r="I18" s="25">
-        <v>1200000</v>
+        <v>120000000</v>
       </c>
       <c r="J18" s="25">
-        <v>900000</v>
+        <v>90000000</v>
       </c>
       <c r="K18" s="25">
-        <v>1000000</v>
-      </c>
-      <c r="L18" s="37">
-        <f>AVERAGE(I18:K18)</f>
-        <v>1033333.3333333334</v>
-      </c>
-      <c r="M18" s="37">
-        <f t="shared" si="37"/>
-        <v>1016666.6666666667</v>
-      </c>
-      <c r="N18" s="37">
-        <f t="shared" si="38"/>
-        <v>1025000</v>
-      </c>
-      <c r="O18" s="37">
-        <f t="shared" si="39"/>
-        <v>1020833.3333333334</v>
-      </c>
-      <c r="P18" s="37">
-        <f t="shared" si="40"/>
-        <v>1022916.6666666667</v>
-      </c>
-      <c r="Q18" s="37">
-        <f t="shared" si="1"/>
-        <v>1021875</v>
-      </c>
-      <c r="R18" s="37">
-        <f t="shared" si="2"/>
-        <v>1022395.8333333334</v>
-      </c>
-      <c r="S18" s="37">
-        <f t="shared" si="3"/>
-        <v>1022135.4166666667</v>
-      </c>
-      <c r="T18" s="37">
-        <f t="shared" si="4"/>
-        <v>1022265.625</v>
-      </c>
-      <c r="U18" s="37">
-        <f t="shared" si="5"/>
-        <v>1022200.5208333334</v>
-      </c>
-      <c r="V18" s="37">
-        <f t="shared" si="6"/>
-        <v>1022233.0729166667</v>
-      </c>
-      <c r="W18" s="37">
-        <f t="shared" si="7"/>
-        <v>1022216.796875</v>
-      </c>
-      <c r="X18" s="37">
-        <f t="shared" si="8"/>
-        <v>1022224.9348958334</v>
-      </c>
-      <c r="Y18" s="37">
-        <f t="shared" si="9"/>
-        <v>1022220.8658854167</v>
-      </c>
-      <c r="Z18" s="37">
-        <f t="shared" si="10"/>
-        <v>1022222.900390625</v>
-      </c>
-      <c r="AA18" s="37">
-        <f t="shared" si="11"/>
-        <v>1022221.8831380209</v>
-      </c>
-      <c r="AB18" s="37">
-        <f t="shared" si="12"/>
-        <v>1022222.391764323</v>
-      </c>
-      <c r="AC18" s="37">
-        <f t="shared" si="13"/>
-        <v>1022222.1374511719</v>
-      </c>
-      <c r="AD18" s="37">
-        <f t="shared" si="14"/>
-        <v>1022222.2646077474</v>
-      </c>
-      <c r="AE18" s="37">
-        <f t="shared" si="15"/>
-        <v>1022222.2010294597</v>
-      </c>
-      <c r="AF18" s="37">
-        <f t="shared" si="16"/>
-        <v>1022222.2328186035</v>
-      </c>
-      <c r="AG18" s="37">
-        <f t="shared" si="17"/>
-        <v>1022222.2169240316</v>
-      </c>
-      <c r="AH18" s="37">
-        <f t="shared" si="18"/>
-        <v>1022222.2248713176</v>
-      </c>
-      <c r="AI18" s="37">
-        <f t="shared" si="19"/>
-        <v>1022222.2208976746</v>
-      </c>
-      <c r="AJ18" s="37">
-        <f t="shared" si="20"/>
-        <v>1022222.2228844961</v>
-      </c>
-      <c r="AK18" s="37">
-        <f t="shared" si="21"/>
-        <v>1022222.2218910854</v>
-      </c>
-      <c r="AL18" s="37">
-        <f t="shared" si="22"/>
-        <v>1022222.2223877907</v>
-      </c>
-      <c r="AM18" s="37">
-        <f t="shared" si="23"/>
-        <v>1022222.222139438</v>
-      </c>
-      <c r="AN18" s="37">
-        <f t="shared" si="24"/>
-        <v>1022222.2222636144</v>
-      </c>
-      <c r="AO18" s="37">
-        <f t="shared" si="25"/>
-        <v>1022222.2222015262</v>
-      </c>
-      <c r="AP18" s="37">
-        <f t="shared" si="26"/>
-        <v>1022222.2222325703</v>
-      </c>
-      <c r="AQ18" s="37">
-        <f t="shared" si="27"/>
-        <v>1022222.2222170483</v>
-      </c>
-      <c r="AR18" s="37">
-        <f t="shared" si="28"/>
-        <v>1022222.2222248092</v>
-      </c>
-      <c r="AS18" s="37">
-        <f t="shared" si="29"/>
-        <v>1022222.2222209288</v>
-      </c>
-      <c r="AT18" s="37">
-        <f t="shared" si="30"/>
-        <v>1022222.2222228691</v>
-      </c>
-      <c r="AU18" s="37">
-        <f t="shared" si="31"/>
-        <v>1022222.2222218988</v>
-      </c>
-      <c r="AV18" s="37">
-        <f t="shared" si="32"/>
-        <v>1022222.2222223839</v>
-      </c>
-      <c r="AW18" s="37">
-        <f t="shared" si="33"/>
-        <v>1022222.2222221415</v>
-      </c>
-      <c r="AX18" s="37">
-        <f t="shared" si="34"/>
-        <v>1022222.2222222628</v>
-      </c>
-      <c r="AY18" s="37">
-        <f t="shared" si="35"/>
-        <v>1022222.2222222021</v>
-      </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -22046,42 +19221,46 @@
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
-    </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-    </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="40"/>
@@ -22092,7 +19271,7 @@
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -22104,7 +19283,7 @@
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -22116,7 +19295,7 @@
       <c r="J25" s="25"/>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -22128,7 +19307,7 @@
       <c r="J26" s="25"/>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -22140,7 +19319,7 @@
       <c r="J27" s="25"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -22152,7 +19331,7 @@
       <c r="J28" s="25"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -22164,7 +19343,7 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -22176,7 +19355,7 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -22188,7 +19367,7 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -22200,7 +19379,7 @@
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -22212,7 +19391,7 @@
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -22224,7 +19403,7 @@
       <c r="J34" s="25"/>
       <c r="K34" s="25"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -22236,7 +19415,7 @@
       <c r="J35" s="25"/>
       <c r="K35" s="25"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -22248,7 +19427,7 @@
       <c r="J36" s="25"/>
       <c r="K36" s="25"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -22260,7 +19439,7 @@
       <c r="J37" s="25"/>
       <c r="K37" s="25"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -22272,7 +19451,7 @@
       <c r="J38" s="25"/>
       <c r="K38" s="25"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -22284,7 +19463,7 @@
       <c r="J39" s="25"/>
       <c r="K39" s="25"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -22296,7 +19475,7 @@
       <c r="J40" s="25"/>
       <c r="K40" s="25"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -22308,7 +19487,7 @@
       <c r="J41" s="25"/>
       <c r="K41" s="25"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -22320,7 +19499,7 @@
       <c r="J42" s="25"/>
       <c r="K42" s="25"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -22332,7 +19511,7 @@
       <c r="J43" s="25"/>
       <c r="K43" s="25"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -22345,16 +19524,11 @@
       <c r="K44" s="25"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEDCBEC-A12F-4CB4-BD24-1D1201B71C25}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <autoFilter ref="A1:K18" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
+      <sortCondition ref="A1:A18"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/production_capacity_updated.xlsx
+++ b/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\L-shaped method\Using_deterministic_model_from_IISE_paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC75AC5-5DFF-42F9-8F6A-B58AA24898A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{5BC75AC5-5DFF-42F9-8F6A-B58AA24898A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F05F723-1F5A-44BE-88C1-976EE0EDEB3A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -2319,14 +2319,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3694F37-B2B5-4F9D-9ACD-67519624FADB}">
   <dimension ref="A1:T54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="91.109375" customWidth="1"/>
-    <col min="2" max="18" width="15.6640625" customWidth="1"/>
-    <col min="20" max="20" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="91.140625" customWidth="1"/>
+    <col min="2" max="18" width="15.7109375" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="S2" s="34"/>
       <c r="T2" s="34"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>92</v>
       </c>
@@ -2444,7 +2444,7 @@
       <c r="S3" s="34"/>
       <c r="T3" s="34"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>93</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="S4" s="34"/>
       <c r="T4" s="34"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>94</v>
       </c>
@@ -2502,7 +2502,7 @@
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>95</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="S6" s="34"/>
       <c r="T6" s="34"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>96</v>
       </c>
@@ -2562,7 +2562,7 @@
       <c r="S7" s="34"/>
       <c r="T7" s="34"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>157</v>
       </c>
@@ -2596,7 +2596,7 @@
       <c r="S8" s="34"/>
       <c r="T8" s="34"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>97</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="S9" s="34"/>
       <c r="T9" s="34"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>98</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="S10" s="34"/>
       <c r="T10" s="34"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>99</v>
       </c>
@@ -2684,7 +2684,7 @@
       <c r="S11" s="34"/>
       <c r="T11" s="34"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>100</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="S12" s="34"/>
       <c r="T12" s="34"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>101</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="S13" s="34"/>
       <c r="T13" s="34"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>102</v>
       </c>
@@ -2782,7 +2782,7 @@
       <c r="S14" s="34"/>
       <c r="T14" s="34"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>103</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>104</v>
       </c>
@@ -2842,7 +2842,7 @@
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>105</v>
       </c>
@@ -2872,7 +2872,7 @@
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>158</v>
       </c>
@@ -2902,7 +2902,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>155</v>
       </c>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="T19" s="10"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2952,7 +2952,7 @@
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2971,7 +2971,7 @@
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2990,7 +2990,7 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -3009,7 +3009,7 @@
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3028,7 +3028,7 @@
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -3047,7 +3047,7 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -3066,7 +3066,7 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -3085,7 +3085,7 @@
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -3104,7 +3104,7 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3123,7 +3123,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -3142,7 +3142,7 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3161,7 +3161,7 @@
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3180,7 +3180,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3199,7 +3199,7 @@
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3218,7 +3218,7 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3237,7 +3237,7 @@
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3256,7 +3256,7 @@
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3275,7 +3275,7 @@
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3294,7 +3294,7 @@
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3313,7 +3313,7 @@
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3332,7 +3332,7 @@
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3351,7 +3351,7 @@
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3370,7 +3370,7 @@
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3389,7 +3389,7 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3408,7 +3408,7 @@
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3427,7 +3427,7 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3446,7 +3446,7 @@
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3465,7 +3465,7 @@
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3484,7 +3484,7 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3503,7 +3503,7 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3522,7 +3522,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -3541,7 +3541,7 @@
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -3560,7 +3560,7 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3579,7 +3579,7 @@
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3630,17 +3630,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7054496A-AF4B-4EC1-B368-49C550220A1C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L301"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="94.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="12" width="18" style="2" customWidth="1"/>
     <col min="13" max="13" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
@@ -3696,7 +3696,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>12</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>26819200.996155463</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>12</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>56018232.597976193</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>12</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>170565705.92964286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
         <v>12</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>79877180.657261893</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="43" t="s">
         <v>18</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
         <v>18</v>
       </c>
@@ -3908,7 +3908,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>18</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>18</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
         <v>19</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>1403270410.0475006</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
         <v>19</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>43232783.299999997</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
         <v>19</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>789204932.27500033</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
         <v>19</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>500814543.58749998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -4156,7 +4156,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="43" t="s">
         <v>22</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
         <v>22</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>12788293.736842105</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
         <v>22</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>863986.71500000008</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
         <v>22</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>5370201.9115789467</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>22</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>4313357.7878842624</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>23</v>
       </c>
@@ -4344,7 +4344,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>23</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>44326790.909789473</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>23</v>
       </c>
@@ -4400,7 +4400,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>23</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>430931.20894736843</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -4486,7 +4486,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
         <v>25</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>24359.106315789475</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="43" t="s">
         <v>25</v>
       </c>
@@ -4554,7 +4554,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="43" t="s">
         <v>25</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>29653.105263157893</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>26</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>22700002.013999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>26</v>
       </c>
@@ -4644,7 +4644,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>26</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>9708542.1121710539</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>27</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>2385352.0408421056</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
@@ -4750,7 +4750,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>27</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>6987.9032894736847</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>28</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>3753257.1406578948</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>28</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
         <v>29</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>17711618.430631582</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>29</v>
       </c>
@@ -4904,7 +4904,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
         <v>29</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>8274488.3427631576</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="43" t="s">
         <v>30</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>12708293.497763159</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
         <v>30</v>
       </c>
@@ -4998,7 +4998,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
         <v>30</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>129709.70407894738</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>31</v>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
         <v>31</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>4366498.504999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
         <v>31</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>924903.77499999991</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
         <v>31</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>56671594.19749999</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
         <v>31</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>28451376.886823118</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
         <v>32</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="43" t="s">
         <v>32</v>
       </c>
@@ -5242,7 +5242,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>32</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>32</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>1371371.7111111111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="43" t="s">
         <v>33</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>4588112.7602708973</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>33</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>68258991.188157901</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="43" t="s">
         <v>33</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>202310628.16776317</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>33</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>61534344.793815792</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>34</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>99151.439999999988</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
         <v>34</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>3781590.8850000007</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
         <v>34</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>2364272.5157894739</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
         <v>34</v>
       </c>
@@ -5584,7 +5584,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
         <v>35</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>42709218.048947372</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>585519.70234210533</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>35</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>6391844.9436842091</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>36</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>36</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>71135570.336828187</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>36</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>8918362.7869736832</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>36</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>56037443.403815791</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>36</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>26078721.471578948</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>37</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>37</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>13285092.037631579</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>37</v>
       </c>
@@ -5942,7 +5942,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>37</v>
       </c>
@@ -5972,7 +5972,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
         <v>37</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>7212690.1784210531</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
         <v>38</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>3143161.6294736844</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>38</v>
       </c>
@@ -6066,7 +6066,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>694846.97368421056</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="43" t="s">
         <v>40</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>31169164.653893046</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>40</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>9024207.2250826061</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
         <v>40</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>26014337.772836529</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
         <v>40</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>21218834.523721006</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>41</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>24485113.215146199</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="43" t="s">
         <v>41</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>42986086.185204685</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>41</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>89969889.638869569</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>41</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>43092807.72445029</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>42</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>26223826.190433443</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
         <v>42</v>
       </c>
@@ -6464,7 +6464,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
         <v>42</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>38913109.206510134</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
         <v>42</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>8318128.2670879252</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="s">
         <v>43</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
         <v>43</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>593298.1894736843</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
         <v>43</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>882693.01642857143</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="45" t="s">
         <v>43</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>68866.200000000012</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="46" t="s">
         <v>43</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>9727462.9341666661</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="43" t="s">
         <v>44</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="43" t="s">
         <v>44</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>16995032.578833334</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
         <v>44</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>22529845.132500004</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="43" t="s">
         <v>45</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>11652763.552941177</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="43" t="s">
         <v>45</v>
       </c>
@@ -6872,7 +6872,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="43" t="s">
         <v>45</v>
       </c>
@@ -6898,7 +6898,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="43" t="s">
         <v>46</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>3129137.4496973683</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
         <v>46</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
         <v>46</v>
       </c>
@@ -6980,7 +6980,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="43" t="s">
         <v>47</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>19439134.578947369</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="43" t="s">
         <v>47</v>
       </c>
@@ -7038,7 +7038,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="43" t="s">
         <v>47</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>12278482.1775</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
         <v>48</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="43" t="s">
         <v>48</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>428081.60342105263</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
         <v>48</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="43" t="s">
         <v>49</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="43" t="s">
         <v>49</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>15938780.685739476</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="43" t="s">
         <v>49</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>7463.7629999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
         <v>49</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>6024488.8079210529</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
         <v>50</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
         <v>50</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>3357564.5291447369</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
         <v>50</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>277375.88714868418</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="43" t="s">
         <v>50</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>48463.652665350877</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="43" t="s">
         <v>50</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>962589.57300000009</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>51</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>4199871.1182460524</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
         <v>52</v>
       </c>
@@ -7562,7 +7562,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
         <v>52</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>8001.5255263157915</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
         <v>52</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>196251.34736842106</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
         <v>53</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
         <v>53</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>3969424.3796421057</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
         <v>53</v>
       </c>
@@ -7746,7 +7746,7 @@
         <v>8895367.3138157893</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="43" t="s">
         <v>54</v>
       </c>
@@ -7764,7 +7764,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="43" t="s">
         <v>54</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="43" t="s">
         <v>54</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="43" t="s">
         <v>54</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="43" t="s">
         <v>55</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
         <v>55</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>44666553.82686425</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
         <v>55</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>2148068.0935714287</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
         <v>55</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>10829590.64130117</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
         <v>55</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>53816727.563368849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="43" t="s">
         <v>56</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>5366204.9252105262</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
         <v>56</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>1918456.0949999997</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="43" t="s">
         <v>57</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>2456094.4891353385</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
         <v>57</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>84871745.658650786</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
         <v>57</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>228007209.74936509</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
         <v>57</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>32273220.97396826</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>58</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>1012182.5810526316</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
         <v>59</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
         <v>59</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>19377207.360228568</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="43" t="s">
         <v>59</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>123225959.44543454</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
         <v>59</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>9816494.2557882406</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
         <v>60</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>85488520.6669323</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="43" t="s">
         <v>60</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>57292565.508875743</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
         <v>60</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>162941685.62800577</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
         <v>60</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>66591452.998300254</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
         <v>61</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>6418700.4964842089</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="43" t="s">
         <v>61</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>657.72019736842117</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
         <v>61</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>38980.994268421055</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
         <v>62</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>57668115.752105266</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
         <v>62</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>48207996.665438592</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="43" t="s">
         <v>62</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>163594841.15653506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="43" t="s">
         <v>62</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>51145121.535921052</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="43" t="s">
         <v>63</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>1140116.518780523</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="43" t="s">
         <v>63</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>3095533.6346984911</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="43" t="s">
         <v>63</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>24073104.668296658</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="43" t="s">
         <v>63</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>8249515.7360912031</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="43" t="s">
         <v>64</v>
       </c>
@@ -8942,7 +8942,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="43" t="s">
         <v>64</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
         <v>64</v>
       </c>
@@ -8980,7 +8980,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="43" t="s">
         <v>65</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>524620.18888888881</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="43" t="s">
         <v>65</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>11686619.239444446</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="43" t="s">
         <v>65</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>67230835.707277775</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="43" t="s">
         <v>65</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>8927850.3513888884</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
         <v>66</v>
       </c>
@@ -9140,7 +9140,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="43" t="s">
         <v>66</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>11586096.10842105</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="43" t="s">
         <v>66</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>61286058.379432946</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="43" t="s">
         <v>66</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>198326735.48209769</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="43" t="s">
         <v>66</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>74368544.324421823</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="43" t="s">
         <v>67</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>37434.968421052632</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="43" t="s">
         <v>67</v>
       </c>
@@ -9348,7 +9348,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="43" t="s">
         <v>67</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="43" t="s">
         <v>68</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>14085732.501447368</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="43" t="s">
         <v>68</v>
       </c>
@@ -9436,7 +9436,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="43" t="s">
         <v>68</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>2658726.6143421056</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="43" t="s">
         <v>69</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>5274066.9230263159</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="43" t="s">
         <v>69</v>
       </c>
@@ -9538,7 +9538,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="43" t="s">
         <v>69</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>109338.78881578946</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="43" t="s">
         <v>70</v>
       </c>
@@ -9594,7 +9594,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="43" t="s">
         <v>70</v>
       </c>
@@ -9612,7 +9612,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="43" t="s">
         <v>70</v>
       </c>
@@ -9630,7 +9630,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="43" t="s">
         <v>70</v>
       </c>
@@ -9648,7 +9648,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="43" t="s">
         <v>70</v>
       </c>
@@ -9666,7 +9666,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="43" t="s">
         <v>71</v>
       </c>
@@ -9684,7 +9684,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="43" t="s">
         <v>71</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>1602020.15372807</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="43" t="s">
         <v>71</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="43" t="s">
         <v>71</v>
       </c>
@@ -9786,7 +9786,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="43" t="s">
         <v>71</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>8435990.8228508774</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="43" t="s">
         <v>72</v>
       </c>
@@ -9842,7 +9842,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="43" t="s">
         <v>72</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>41053.861588892236</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="43" t="s">
         <v>72</v>
       </c>
@@ -9910,7 +9910,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="43" t="s">
         <v>72</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>361138.98097679514</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="43" t="s">
         <v>73</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>21801576.347789474</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="43" t="s">
         <v>73</v>
       </c>
@@ -10004,7 +10004,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="43" t="s">
         <v>73</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>4773371.973289473</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="43" t="s">
         <v>74</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="43" t="s">
         <v>74</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>95686.964999999997</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="43" t="s">
         <v>74</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>19427327.223125003</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="43" t="s">
         <v>74</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>28291617.551274512</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="43" t="s">
         <v>74</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>21470697.767319441</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
@@ -10244,7 +10244,7 @@
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
-    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
@@ -10256,7 +10256,7 @@
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
@@ -10268,7 +10268,7 @@
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>43</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>22913488.673833333</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>57</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>312878955.40801585</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>55</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>12977658.734872598</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>71</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>66</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>108</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>6234188.6265789466</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>109</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>57596497.972499989</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>98</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>99</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>270569619.35592109</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="16" t="s">
         <v>100</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>101</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>132955975.82407425</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>102</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>103</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>35038544.997919135</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>104</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>64955806.190789476</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>105</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>62</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>211802837.82197365</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>60</v>
       </c>
@@ -11084,10 +11084,10 @@
         <v>220234251.13688153</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C224" s="8"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>113</v>
       </c>
@@ -11100,7 +11100,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>114</v>
       </c>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="C226" s="8"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>106</v>
       </c>
@@ -11117,14 +11117,14 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
       <c r="J228" s="15"/>
       <c r="K228" s="15"/>
       <c r="L228" s="15"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B229" s="2" t="s">
         <v>115</v>
       </c>
@@ -11134,7 +11134,7 @@
       <c r="K229" s="27"/>
       <c r="L229" s="27"/>
     </row>
-    <row r="230" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="18" t="s">
         <v>43</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>20622139.806450002</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>75</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>16872659.841640912</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>118</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>3749479.9648090904</v>
       </c>
     </row>
-    <row r="233" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="18" t="s">
         <v>57</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>281591059.86721426</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>75</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>203910767.49005172</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>119</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>77680292.377162561</v>
       </c>
     </row>
-    <row r="236" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="18" t="s">
         <v>55</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>11679892.861385338</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>116</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>3412103.5325395376</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>117</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>8267789.3288458008</v>
       </c>
     </row>
-    <row r="239" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="18" t="s">
         <v>71</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>75</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>2289842.5978235295</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>118</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>508853.91062745103</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>81</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>290773.66321568622</v>
       </c>
     </row>
-    <row r="243" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="18" t="s">
         <v>66</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>75</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>192418894.27384037</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>118</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>42759754.283075638</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>81</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>24434145.304614648</v>
       </c>
     </row>
-    <row r="247" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="18" t="s">
         <v>108</v>
       </c>
@@ -11980,7 +11980,7 @@
         <v>6857607.4892368419</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>75</v>
       </c>
@@ -12028,7 +12028,7 @@
         <v>5082697.3155520121</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>118</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>1129488.2923448917</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>81</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>645421.88133993803</v>
       </c>
     </row>
-    <row r="251" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="18" t="s">
         <v>109</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>63356147.769749992</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>75</v>
       </c>
@@ -12217,7 +12217,7 @@
         <v>45878589.764301717</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>119</v>
       </c>
@@ -12265,7 +12265,7 @@
         <v>17477558.005448274</v>
       </c>
     </row>
-    <row r="254" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="18" t="s">
         <v>98</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>75</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="256" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="18" t="s">
         <v>99</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>297626581.2915132</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>75</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>165933403.72889677</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>118</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>36874089.717532612</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>119</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>63212725.230055898</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>82</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>21070908.410018638</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>83</v>
       </c>
@@ -12643,12 +12643,12 @@
         <v>10535454.205009319</v>
       </c>
     </row>
-    <row r="262" spans="1:12" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" s="21" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="23" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="18" t="s">
         <v>101</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>146251573.40648168</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>82</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>53182390.329629704</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>84</v>
       </c>
@@ -12789,7 +12789,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>85</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>86</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>59830189.120833419</v>
       </c>
     </row>
-    <row r="268" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="18" t="s">
         <v>102</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>404502055.98924994</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>75</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>172186685.99542397</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="22" t="s">
         <v>76</v>
       </c>
@@ -13026,7 +13026,7 @@
         <v>38263707.998983108</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>77</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>71061171.998111486</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>80</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>68328049.998184115</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>83</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>10932487.999709459</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>87</v>
       </c>
@@ -13218,7 +13218,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>88</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>27331219.999273647</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -13314,7 +13314,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="277" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="18" t="s">
         <v>103</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>31534690.498127222</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>77</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>24845513.725797206</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>79</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>90</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="28" t="s">
         <v>154</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="282" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
         <v>104</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>71451386.809868425</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>75</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>63400526.324249454</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>82</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="285" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="18" t="s">
         <v>105</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>3954.38333881579</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>75</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>2737.650003795547</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>80</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>1086.3690491252169</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>91</v>
       </c>
@@ -13876,7 +13876,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="289" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="29" t="s">
         <v>62</v>
       </c>
@@ -13921,7 +13921,7 @@
         <v>190622554.0397763</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>75</v>
       </c>
@@ -13969,7 +13969,7 @@
         <v>121305261.66167584</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>88</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>13932545.477990292</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>77</v>
       </c>
@@ -14065,7 +14065,7 @@
         <v>50062488.939739235</v>
       </c>
     </row>
-    <row r="293" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="29" t="s">
         <v>155</v>
       </c>
@@ -14110,7 +14110,7 @@
         <v>242257676.2505697</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>75</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>165893843.51941183</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>156</v>
       </c>
@@ -14206,7 +14206,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>77</v>
       </c>
@@ -14254,7 +14254,7 @@
         <v>68464125.896900132</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H301" s="16"/>
       <c r="I301" s="16"/>
       <c r="J301" s="16"/>
@@ -14291,16 +14291,36 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A70:A74"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A161:A163"/>
     <mergeCell ref="A120:A122"/>
     <mergeCell ref="A123:A125"/>
@@ -14313,36 +14333,16 @@
     <mergeCell ref="A150:A152"/>
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A70:A74"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14353,15 +14353,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55228539-2602-4D9E-BF99-AB1A3FA50A1F}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -14396,7 +14396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -14771,7 +14771,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>142</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>144</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>145</v>
       </c>
@@ -15179,7 +15179,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -15383,7 +15383,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -15519,7 +15519,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>154</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>147</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>147</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
@@ -15826,7 +15826,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>148</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>149</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>156</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>150</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>150</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>150</v>
       </c>
@@ -16269,7 +16269,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>150</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>150</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>150</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>152</v>
       </c>
@@ -16745,7 +16745,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>152</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>152</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>152</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -17442,7 +17442,7 @@
         <v>25400000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -17520,7 +17520,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
@@ -17598,7 +17598,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -17676,7 +17676,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M52" t="s">
         <v>145</v>
       </c>
@@ -17799,7 +17799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
         <v>116</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>217800000</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
         <v>146</v>
       </c>
@@ -17889,7 +17889,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M55" t="s">
         <v>154</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
         <v>147</v>
       </c>
@@ -17979,7 +17979,7 @@
         <v>82300000</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
         <v>148</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>5700000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M58" t="s">
         <v>149</v>
       </c>
@@ -18069,7 +18069,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M59" t="s">
         <v>156</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>7900000</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M60" t="s">
         <v>150</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M61" t="s">
         <v>151</v>
       </c>
@@ -18204,7 +18204,7 @@
         <v>128200000</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M62" t="s">
         <v>152</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M63" t="s">
         <v>153</v>
       </c>
@@ -18303,13 +18303,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{770C77AF-CB50-4854-8654-5465FF2CEF2B}">
   <dimension ref="B2:T19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
         <v>84</v>
       </c>
@@ -18365,7 +18365,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
         <v>81</v>
       </c>
@@ -18437,7 +18437,7 @@
         <v>"Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>87</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>"AJ_Vaccines","BB_NCIPD","Beijing_Institute","Bharat_Biotech","Bilthoven","Biological_E","Centro_de","GSK","Haffkine_Bio","LG_Chem","Merck_Sharp","Panacea_Biotec","PT_Bio","Sanofi_Pasteur","Serum_Institute","Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>88</v>
       </c>
@@ -18457,7 +18457,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>85</v>
       </c>
@@ -18465,7 +18465,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
         <v>119</v>
       </c>
@@ -18473,7 +18473,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
         <v>91</v>
       </c>
@@ -18481,7 +18481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
         <v>77</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="26" t="s">
         <v>89</v>
       </c>
@@ -18497,7 +18497,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="26" t="s">
         <v>82</v>
       </c>
@@ -18505,7 +18505,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
         <v>79</v>
       </c>
@@ -18513,7 +18513,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
         <v>83</v>
       </c>
@@ -18521,7 +18521,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
         <v>118</v>
       </c>
@@ -18529,7 +18529,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
         <v>80</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>75</v>
       </c>
@@ -18545,7 +18545,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
         <v>90</v>
       </c>
@@ -18553,7 +18553,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
         <v>156</v>
       </c>
@@ -18561,7 +18561,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
         <v>154</v>
       </c>
@@ -18578,13 +18578,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="36">
         <v>1</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -18651,7 +18651,7 @@
         <v>2178000000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -18686,7 +18686,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>148</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>456000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>152</v>
       </c>
@@ -18791,7 +18791,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -18826,7 +18826,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -18861,7 +18861,7 @@
         <v>254000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -18931,7 +18931,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -18966,7 +18966,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -19036,7 +19036,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>147</v>
       </c>
@@ -19071,7 +19071,7 @@
         <v>1399100000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>149</v>
       </c>
@@ -19106,7 +19106,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>79000000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>1282000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -19211,7 +19211,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -19223,7 +19223,7 @@
       <c r="J19" s="25"/>
       <c r="K19" s="25"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -19235,7 +19235,7 @@
       <c r="J20" s="37"/>
       <c r="K20" s="37"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -19247,7 +19247,7 @@
       <c r="J21" s="42"/>
       <c r="K21" s="42"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -19259,7 +19259,7 @@
       <c r="J22" s="42"/>
       <c r="K22" s="42"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="37"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -19271,7 +19271,7 @@
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -19283,7 +19283,7 @@
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -19295,7 +19295,7 @@
       <c r="J25" s="25"/>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -19307,7 +19307,7 @@
       <c r="J26" s="25"/>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -19319,7 +19319,7 @@
       <c r="J27" s="25"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -19331,7 +19331,7 @@
       <c r="J28" s="25"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -19343,7 +19343,7 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -19355,7 +19355,7 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -19367,7 +19367,7 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -19379,7 +19379,7 @@
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -19391,7 +19391,7 @@
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -19403,7 +19403,7 @@
       <c r="J34" s="25"/>
       <c r="K34" s="25"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -19415,7 +19415,7 @@
       <c r="J35" s="25"/>
       <c r="K35" s="25"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -19427,7 +19427,7 @@
       <c r="J36" s="25"/>
       <c r="K36" s="25"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -19439,7 +19439,7 @@
       <c r="J37" s="25"/>
       <c r="K37" s="25"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -19451,7 +19451,7 @@
       <c r="J38" s="25"/>
       <c r="K38" s="25"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -19463,7 +19463,7 @@
       <c r="J39" s="25"/>
       <c r="K39" s="25"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -19475,7 +19475,7 @@
       <c r="J40" s="25"/>
       <c r="K40" s="25"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -19487,7 +19487,7 @@
       <c r="J41" s="25"/>
       <c r="K41" s="25"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -19499,7 +19499,7 @@
       <c r="J42" s="25"/>
       <c r="K42" s="25"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -19511,7 +19511,7 @@
       <c r="J43" s="25"/>
       <c r="K43" s="25"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
